--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\entshare3\JS-Data\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C44EBC3E-62D9-4DB9-983F-1C5E29F52F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{693E3200-4D33-462B-A562-8625EDCF6BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5486" uniqueCount="1859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5731" uniqueCount="1946">
   <si>
     <t>County/Parish</t>
   </si>
@@ -5645,6 +5645,135 @@
     <t>475 Anton Blvd.  Costa Mesa CA 92626</t>
   </si>
   <si>
+    <t>Sanitation Specialists</t>
+  </si>
+  <si>
+    <t>14490 Catalina Street  San Leandro CA 94577</t>
+  </si>
+  <si>
+    <t>Union of Pan Asian Communities (Neighborhood Enterprise Center)</t>
+  </si>
+  <si>
+    <t>5296 University Avenue  San Diego CA 92105</t>
+  </si>
+  <si>
+    <t>Atlassian US, Inc.</t>
+  </si>
+  <si>
+    <t>350 Bush Street, Floor 13  San Francisco CA 94104</t>
+  </si>
+  <si>
+    <t>320B Shaw Road  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>American Eagle Flights (Santa Maria Airport)</t>
+  </si>
+  <si>
+    <t>3217 Terminal Dr.  Santa Maria CA 93455</t>
+  </si>
+  <si>
+    <t>Westside Equipment Co. (OXBO)</t>
+  </si>
+  <si>
+    <t>18 Fink Road  Crows Landing CA 95313</t>
+  </si>
+  <si>
+    <t>Blue Shield of California</t>
+  </si>
+  <si>
+    <t>Blue Shield of California (Building C)</t>
+  </si>
+  <si>
+    <t>4203 Town Center Blvd., Building C  El Dorado Hills CA 95762</t>
+  </si>
+  <si>
+    <t>Blue Shield of California (Building B)</t>
+  </si>
+  <si>
+    <t>4203 Town Center Blvd., Building B  El Dorado Hills CA 95762</t>
+  </si>
+  <si>
+    <t>Calvary Murrieta Christian School</t>
+  </si>
+  <si>
+    <t>2475 Monroe Avenue  Murrieta CA 92562</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (Livermore)</t>
+  </si>
+  <si>
+    <t>1987 First Street  Livermore CA 94550</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (Oakland)</t>
+  </si>
+  <si>
+    <t>1111 Broadway, Suite 1650  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (Danville)</t>
+  </si>
+  <si>
+    <t>387 Diable Blvd.  Danville CA 94526</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (Walnut Creek)</t>
+  </si>
+  <si>
+    <t>1990 N. California Blvd, Suite 100  Walnut Creek CA 94596</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (San Rafael)</t>
+  </si>
+  <si>
+    <t>999 Fifth Ave., Suite 100  San Rafael CA 94901</t>
+  </si>
+  <si>
+    <t>San Benito County</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (Hollister)</t>
+  </si>
+  <si>
+    <t>351 Tres Pinos Road, Suite 102A  Hollister CA 95023</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (San Francisco)</t>
+  </si>
+  <si>
+    <t>120 Kearney St., Suite 2300  San Francisco CA 94108</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (Mateo)</t>
+  </si>
+  <si>
+    <t>400 S. El Camino Real, Suite 150  Mateo CA 94402</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (Los Altos)</t>
+  </si>
+  <si>
+    <t>419 South San Antonio Road  Los Altos CA 94022</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (Morgan Hill)</t>
+  </si>
+  <si>
+    <t>18625 Sutter Blvd. Suite 100  Morgan Hill CA 95037</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (Remote-San Jose)</t>
+  </si>
+  <si>
+    <t>224 Airport Parkway  San Jose CA 95110</t>
+  </si>
+  <si>
+    <t>Heritage Bank of Commerce (San Jose)</t>
+  </si>
+  <si>
+    <t>Experian (Experian Health and Experian Information Solutions)</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -5664,7 +5793,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 03/16/2026
+01/01/2023 - 03/23/2026
 </t>
     </r>
     <r>
@@ -5678,58 +5807,190 @@
     </r>
   </si>
   <si>
-    <t>Sanitation Specialists</t>
-  </si>
-  <si>
-    <t>14490 Catalina Street  San Leandro CA 94577</t>
-  </si>
-  <si>
-    <t>Union of Pan Asian Communities (Neighborhood Enterprise Center)</t>
-  </si>
-  <si>
-    <t>5296 University Avenue  San Diego CA 92105</t>
-  </si>
-  <si>
-    <t>Atlassian US, Inc.</t>
-  </si>
-  <si>
-    <t>350 Bush Street, Floor 13  San Francisco CA 94104</t>
-  </si>
-  <si>
-    <t>320B Shaw Road  South San Francisco CA 94080</t>
-  </si>
-  <si>
-    <t>American Eagle Flights (Santa Maria Airport)</t>
-  </si>
-  <si>
-    <t>3217 Terminal Dr.  Santa Maria CA 93455</t>
-  </si>
-  <si>
-    <t>Westside Equipment Co. (OXBO)</t>
-  </si>
-  <si>
-    <t>18 Fink Road  Crows Landing CA 95313</t>
-  </si>
-  <si>
-    <t>Blue Shield of California</t>
-  </si>
-  <si>
-    <t>Blue Shield of California (Building C)</t>
-  </si>
-  <si>
-    <t>4203 Town Center Blvd., Building C  El Dorado Hills CA 95762</t>
-  </si>
-  <si>
-    <t>Blue Shield of California (Building B)</t>
-  </si>
-  <si>
-    <t>4203 Town Center Blvd., Building B  El Dorado Hills CA 95762</t>
-  </si>
-  <si>
-    <t>Calvary Murrieta Christian School</t>
-  </si>
-  <si>
-    <t>2475 Monroe Avenue  Murrieta CA 92562</t>
+    <t>Total Storage Solutions (Best RV &amp; Self Storage)</t>
+  </si>
+  <si>
+    <t>5900 Esperanza Ave.  Whittier CA 90606</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Crenshaw Self Storage)</t>
+  </si>
+  <si>
+    <t>6725 Crenshaw Blvd.  Los Angeles CA 90043</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (El Monte Stor It Now)</t>
+  </si>
+  <si>
+    <t>10212 Valley Blvd.  El Monte CA 91731</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Studebaker Self Storage)</t>
+  </si>
+  <si>
+    <t>698 N. Studebaker Rd.  Long Beach CA 90803</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Arcadia 210 Self Storage)</t>
+  </si>
+  <si>
+    <t>324 N. 2nd Ave.  Arcadia CA 91006</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (All Size Self Storage)</t>
+  </si>
+  <si>
+    <t>911 Calle Amanecer  San Clemente CA 92673</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (All Size Laguna Niguel)</t>
+  </si>
+  <si>
+    <t>27872 Crown Valley Parkway  Laguna Niguel CA 92677</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Garden Grove Secured Storage)</t>
+  </si>
+  <si>
+    <t>13632 S. Euclid St.  Garden Grove CA 92843</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Townsend Self Storage)</t>
+  </si>
+  <si>
+    <t>308 N. Townsend St.  Santa Ana CA 92703</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Airport Mini Storage)</t>
+  </si>
+  <si>
+    <t>7044 Arlington Ave.  Riverside CA 92503</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Aware Self Storage)</t>
+  </si>
+  <si>
+    <t>5021 W. Ramsey St.  Banning CA 92220</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Beaumont RV &amp; Self Storage)</t>
+  </si>
+  <si>
+    <t>251 W. 1st St.  Beaumont CA 92223</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Beaumont Self Storage)</t>
+  </si>
+  <si>
+    <t>190 E. First St.  Beaumont CA 92223</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Jefferson Self Storage)</t>
+  </si>
+  <si>
+    <t>25435 Jefferson Ave.  Murrieta CA 92562</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Sun City Mini Storage)</t>
+  </si>
+  <si>
+    <t>27460 McCall Blvd.  Sun City CA 92585</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Tri-City Self Storage)</t>
+  </si>
+  <si>
+    <t>485 W. LaCadena  Riverside CA 92501</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Western States Self Storage)</t>
+  </si>
+  <si>
+    <t>23190 Hemlock Ave.  Moreno Valley CA 92557</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Riverside Self Storage)</t>
+  </si>
+  <si>
+    <t>7200 Indiana Ave.  Riverside CA 92504</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (E Street Self Storage)</t>
+  </si>
+  <si>
+    <t>1723 S. E St.  San Bernardino CA 92408</t>
+  </si>
+  <si>
+    <t>Total Storage Solutions (Citrus Plaza Self Storage)</t>
+  </si>
+  <si>
+    <t>202 W. College St., Suite 100  Fallbrook CA 92028</t>
+  </si>
+  <si>
+    <t>Lodging Dynamics Hospitality Group, LLC (Courtyard &amp; TownePlace Suites)</t>
+  </si>
+  <si>
+    <t>4427 West El Segundo  Hawthorne CA 90250</t>
+  </si>
+  <si>
+    <t>Lodging Dynamics Hospitality Group, LLC (Midici Restaurant)</t>
+  </si>
+  <si>
+    <t>Lodging Dynamics Hospitality Group, LLC (Hilton Garden Inn)</t>
+  </si>
+  <si>
+    <t>2410 Marine Avenue  Redondo Beach CA 90278</t>
+  </si>
+  <si>
+    <t>Lodging Dynamics Hospitality Group, LLC (Residence Inn)</t>
+  </si>
+  <si>
+    <t>2420 Marine Avenue  Redondo Beach CA 90278</t>
+  </si>
+  <si>
+    <t>Lodging Dynamics Hospitality Group, LLC (Homewood Suites)</t>
+  </si>
+  <si>
+    <t>2430 Marine Avenue  Redondo Beach CA 90278</t>
+  </si>
+  <si>
+    <t>NSI-Lynn Electronics</t>
+  </si>
+  <si>
+    <t>3162 East La Palma Avenue  Anaheim CA 92806</t>
+  </si>
+  <si>
+    <t>ERN Services, Inc.</t>
+  </si>
+  <si>
+    <t>5757 Century Bl. Suite 752  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Waymakers</t>
+  </si>
+  <si>
+    <t>440 Exchange, Ste. 250 and 200  Irvine CA 92602</t>
+  </si>
+  <si>
+    <t>16580 Harbor Blvd., Unit O  Fountain Valley CA 92708</t>
+  </si>
+  <si>
+    <t>City National Bank (555 S. Flower Street)</t>
+  </si>
+  <si>
+    <t>555 S. Flower Street  Los Angeles CA 90071</t>
+  </si>
+  <si>
+    <t>City National Bank (350 S. Grand Ave.)</t>
+  </si>
+  <si>
+    <t>675 Almanor Ave  Sunnyvale CA 94085</t>
+  </si>
+  <si>
+    <t>Summit Funding, Inc.</t>
+  </si>
+  <si>
+    <t>2135 Butano Drive, #150  Sacramento CA 95825</t>
   </si>
   <si>
     <r>
@@ -5743,7 +6004,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/25 to 03/16/2026</t>
+      <t>07/01/25 to 03/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -5763,7 +6024,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1085.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1134.</t>
     </r>
   </si>
 </sst>
@@ -6113,7 +6374,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6270,6 +6531,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -7062,7 +7326,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1085" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1134" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="28"/>
@@ -7458,7 +7722,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
@@ -7480,7 +7744,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>59245</v>
+        <v>60159</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7514,7 +7778,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -7545,7 +7809,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I1085"/>
+  <dimension ref="A1:I1134"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -7561,7 +7825,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>1858</v>
+        <v>1945</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -38551,7 +38815,7 @@
         <v>46164</v>
       </c>
       <c r="E1070" s="37" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="F1070" s="37" t="s">
         <v>54</v>
@@ -38560,7 +38824,7 @@
         <v>21</v>
       </c>
       <c r="H1070" s="34" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="I1070" s="26" t="s">
         <v>43</v>
@@ -38580,7 +38844,7 @@
         <v>46152</v>
       </c>
       <c r="E1071" s="37" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="F1071" s="37" t="s">
         <v>54</v>
@@ -38589,7 +38853,7 @@
         <v>16</v>
       </c>
       <c r="H1071" s="34" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I1071" s="26" t="s">
         <v>45</v>
@@ -38609,7 +38873,7 @@
         <v>46094</v>
       </c>
       <c r="E1072" s="37" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="F1072" s="37" t="s">
         <v>6</v>
@@ -38618,7 +38882,7 @@
         <v>252</v>
       </c>
       <c r="H1072" s="34" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="I1072" s="26" t="s">
         <v>41</v>
@@ -38638,7 +38902,7 @@
         <v>46164</v>
       </c>
       <c r="E1073" s="37" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="F1073" s="37" t="s">
         <v>54</v>
@@ -38647,7 +38911,7 @@
         <v>15</v>
       </c>
       <c r="H1073" s="34" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="I1073" s="26" t="s">
         <v>43</v>
@@ -38667,7 +38931,7 @@
         <v>46148</v>
       </c>
       <c r="E1074" s="37" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="F1074" s="37" t="s">
         <v>54</v>
@@ -38676,7 +38940,7 @@
         <v>20</v>
       </c>
       <c r="H1074" s="34" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="I1074" s="26" t="s">
         <v>37</v>
@@ -38696,7 +38960,7 @@
         <v>46153</v>
       </c>
       <c r="E1075" s="37" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F1075" s="37" t="s">
         <v>54</v>
@@ -38705,7 +38969,7 @@
         <v>2</v>
       </c>
       <c r="H1075" s="34" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="I1075" s="26" t="s">
         <v>34</v>
@@ -38725,7 +38989,7 @@
         <v>46120</v>
       </c>
       <c r="E1076" s="37" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="F1076" s="37" t="s">
         <v>6</v>
@@ -38754,7 +39018,7 @@
         <v>46120</v>
       </c>
       <c r="E1077" s="37" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="F1077" s="37" t="s">
         <v>6</v>
@@ -38763,7 +39027,7 @@
         <v>5</v>
       </c>
       <c r="H1077" s="34" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="I1077" s="26" t="s">
         <v>39</v>
@@ -38783,7 +39047,7 @@
         <v>46120</v>
       </c>
       <c r="E1078" s="37" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="F1078" s="37" t="s">
         <v>6</v>
@@ -38792,7 +39056,7 @@
         <v>7</v>
       </c>
       <c r="H1078" s="34" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="I1078" s="26" t="s">
         <v>39</v>
@@ -38812,7 +39076,7 @@
         <v>46120</v>
       </c>
       <c r="E1079" s="37" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="F1079" s="37" t="s">
         <v>6</v>
@@ -38841,7 +39105,7 @@
         <v>46120</v>
       </c>
       <c r="E1080" s="37" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="F1080" s="37" t="s">
         <v>6</v>
@@ -38870,7 +39134,7 @@
         <v>46120</v>
       </c>
       <c r="E1081" s="37" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="F1081" s="37" t="s">
         <v>6</v>
@@ -38899,7 +39163,7 @@
         <v>46120</v>
       </c>
       <c r="E1082" s="37" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="F1082" s="37" t="s">
         <v>6</v>
@@ -38928,7 +39192,7 @@
         <v>46120</v>
       </c>
       <c r="E1083" s="37" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="F1083" s="37" t="s">
         <v>6</v>
@@ -38957,7 +39221,7 @@
         <v>46120</v>
       </c>
       <c r="E1084" s="37" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="F1084" s="37" t="s">
         <v>6</v>
@@ -38986,7 +39250,7 @@
         <v>46171</v>
       </c>
       <c r="E1085" s="41" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="F1085" s="41" t="s">
         <v>54</v>
@@ -38995,10 +39259,1431 @@
         <v>74</v>
       </c>
       <c r="H1085" s="34" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="I1085" s="26" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1086" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1086" s="36">
+        <v>46098</v>
+      </c>
+      <c r="C1086" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1086" s="48">
+        <v>46178</v>
+      </c>
+      <c r="E1086" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="F1086" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1086" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1086" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="I1086" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1087" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1087" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1087" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1087" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1087" s="32" t="s">
+        <v>1857</v>
+      </c>
+      <c r="F1087" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1087" s="34">
+        <v>1</v>
+      </c>
+      <c r="H1087" s="34" t="s">
+        <v>1858</v>
+      </c>
+      <c r="I1087" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1088" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1088" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1088" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1088" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1088" s="32" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F1088" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1088" s="34">
+        <v>1</v>
+      </c>
+      <c r="H1088" s="34" t="s">
+        <v>1860</v>
+      </c>
+      <c r="I1088" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1089" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1089" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1089" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1089" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1089" s="32" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F1089" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1089" s="34">
+        <v>4</v>
+      </c>
+      <c r="H1089" s="34" t="s">
+        <v>1862</v>
+      </c>
+      <c r="I1089" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1090" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1090" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1090" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1090" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1090" s="32" t="s">
+        <v>1863</v>
+      </c>
+      <c r="F1090" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1090" s="34">
+        <v>4</v>
+      </c>
+      <c r="H1090" s="34" t="s">
+        <v>1864</v>
+      </c>
+      <c r="I1090" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1091" s="35" t="s">
+        <v>285</v>
+      </c>
+      <c r="B1091" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1091" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1091" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1091" s="32" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F1091" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1091" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1091" s="34" t="s">
+        <v>1866</v>
+      </c>
+      <c r="I1091" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1092" s="35" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B1092" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1092" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1092" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1092" s="32" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F1092" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1092" s="34">
+        <v>1</v>
+      </c>
+      <c r="H1092" s="34" t="s">
+        <v>1869</v>
+      </c>
+      <c r="I1092" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1093" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1093" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1093" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1093" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1093" s="32" t="s">
+        <v>1870</v>
+      </c>
+      <c r="F1093" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1093" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1093" s="34" t="s">
+        <v>1871</v>
+      </c>
+      <c r="I1093" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1094" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1094" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1094" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1094" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1094" s="32" t="s">
+        <v>1872</v>
+      </c>
+      <c r="F1094" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1094" s="34">
+        <v>5</v>
+      </c>
+      <c r="H1094" s="34" t="s">
+        <v>1873</v>
+      </c>
+      <c r="I1094" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1095" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1095" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1095" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1095" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1095" s="32" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F1095" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1095" s="34">
+        <v>1</v>
+      </c>
+      <c r="H1095" s="34" t="s">
+        <v>1875</v>
+      </c>
+      <c r="I1095" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1096" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1096" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1096" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1096" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1096" s="32" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F1096" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1096" s="34">
+        <v>1</v>
+      </c>
+      <c r="H1096" s="34" t="s">
+        <v>1877</v>
+      </c>
+      <c r="I1096" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1097" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1097" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1097" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1097" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1097" s="32" t="s">
+        <v>1878</v>
+      </c>
+      <c r="F1097" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1097" s="34">
+        <v>12</v>
+      </c>
+      <c r="H1097" s="34" t="s">
+        <v>1879</v>
+      </c>
+      <c r="I1097" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1098" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1098" s="36">
+        <v>46080</v>
+      </c>
+      <c r="C1098" s="36">
+        <v>46098</v>
+      </c>
+      <c r="D1098" s="48">
+        <v>46129</v>
+      </c>
+      <c r="E1098" s="32" t="s">
+        <v>1880</v>
+      </c>
+      <c r="F1098" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1098" s="34">
+        <v>85</v>
+      </c>
+      <c r="H1098" s="34" t="s">
+        <v>1879</v>
+      </c>
+      <c r="I1098" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1099" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1099" s="40">
+        <v>46098</v>
+      </c>
+      <c r="C1099" s="40">
+        <v>46098</v>
+      </c>
+      <c r="D1099" s="55">
+        <v>46160</v>
+      </c>
+      <c r="E1099" s="32" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F1099" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1099" s="34">
+        <v>5</v>
+      </c>
+      <c r="H1099" s="34" t="s">
+        <v>1838</v>
+      </c>
+      <c r="I1099" s="26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1100" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1100" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1100" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1100" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1100" s="32" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F1100" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1100" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1100" s="34" t="s">
+        <v>1884</v>
+      </c>
+      <c r="I1100" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1101" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1101" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1101" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1101" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1101" s="32" t="s">
+        <v>1885</v>
+      </c>
+      <c r="F1101" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1101" s="34">
+        <v>2</v>
+      </c>
+      <c r="H1101" s="34" t="s">
+        <v>1886</v>
+      </c>
+      <c r="I1101" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1102" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1102" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1102" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1102" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1102" s="32" t="s">
+        <v>1887</v>
+      </c>
+      <c r="F1102" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1102" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1102" s="34" t="s">
+        <v>1888</v>
+      </c>
+      <c r="I1102" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1103" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1103" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1103" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1103" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1103" s="32" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F1103" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1103" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1103" s="34" t="s">
+        <v>1890</v>
+      </c>
+      <c r="I1103" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1104" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1104" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1104" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1104" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1104" s="32" t="s">
+        <v>1891</v>
+      </c>
+      <c r="F1104" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1104" s="34">
+        <v>1</v>
+      </c>
+      <c r="H1104" s="34" t="s">
+        <v>1892</v>
+      </c>
+      <c r="I1104" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1105" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1105" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1105" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1105" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1105" s="32" t="s">
+        <v>1893</v>
+      </c>
+      <c r="F1105" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1105" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1105" s="34" t="s">
+        <v>1894</v>
+      </c>
+      <c r="I1105" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1106" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1106" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1106" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1106" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1106" s="32" t="s">
+        <v>1895</v>
+      </c>
+      <c r="F1106" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1106" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1106" s="34" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I1106" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1107" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1107" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1107" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1107" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1107" s="32" t="s">
+        <v>1897</v>
+      </c>
+      <c r="F1107" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1107" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1107" s="34" t="s">
+        <v>1898</v>
+      </c>
+      <c r="I1107" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1108" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1108" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1108" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1108" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1108" s="32" t="s">
+        <v>1899</v>
+      </c>
+      <c r="F1108" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1108" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1108" s="34" t="s">
+        <v>1900</v>
+      </c>
+      <c r="I1108" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1109" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1109" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1109" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1109" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1109" s="32" t="s">
+        <v>1901</v>
+      </c>
+      <c r="F1109" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1109" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1109" s="34" t="s">
+        <v>1902</v>
+      </c>
+      <c r="I1109" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1110" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1110" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1110" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1110" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1110" s="32" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F1110" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1110" s="34">
+        <v>2</v>
+      </c>
+      <c r="H1110" s="34" t="s">
+        <v>1904</v>
+      </c>
+      <c r="I1110" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1111" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1111" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1111" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1111" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1111" s="32" t="s">
+        <v>1905</v>
+      </c>
+      <c r="F1111" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1111" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1111" s="34" t="s">
+        <v>1906</v>
+      </c>
+      <c r="I1111" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1112" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1112" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1112" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1112" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1112" s="32" t="s">
+        <v>1907</v>
+      </c>
+      <c r="F1112" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1112" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1112" s="34" t="s">
+        <v>1908</v>
+      </c>
+      <c r="I1112" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1113" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1113" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1113" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1113" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1113" s="32" t="s">
+        <v>1909</v>
+      </c>
+      <c r="F1113" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1113" s="34">
+        <v>4</v>
+      </c>
+      <c r="H1113" s="34" t="s">
+        <v>1910</v>
+      </c>
+      <c r="I1113" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1114" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1114" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1114" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1114" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1114" s="32" t="s">
+        <v>1911</v>
+      </c>
+      <c r="F1114" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1114" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1114" s="34" t="s">
+        <v>1912</v>
+      </c>
+      <c r="I1114" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1115" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1115" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1115" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1115" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1115" s="32" t="s">
+        <v>1913</v>
+      </c>
+      <c r="F1115" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1115" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1115" s="34" t="s">
+        <v>1914</v>
+      </c>
+      <c r="I1115" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1116" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1116" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1116" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1116" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1116" s="32" t="s">
+        <v>1915</v>
+      </c>
+      <c r="F1116" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1116" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1116" s="34" t="s">
+        <v>1916</v>
+      </c>
+      <c r="I1116" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1117" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1117" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1117" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1117" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1117" s="32" t="s">
+        <v>1917</v>
+      </c>
+      <c r="F1117" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1117" s="34">
+        <v>4</v>
+      </c>
+      <c r="H1117" s="34" t="s">
+        <v>1918</v>
+      </c>
+      <c r="I1117" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1118" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1118" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1118" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1118" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1118" s="32" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F1118" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1118" s="34">
+        <v>2</v>
+      </c>
+      <c r="H1118" s="34" t="s">
+        <v>1920</v>
+      </c>
+      <c r="I1118" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1119" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1119" s="36">
+        <v>46093</v>
+      </c>
+      <c r="C1119" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1119" s="48">
+        <v>46160</v>
+      </c>
+      <c r="E1119" s="32" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F1119" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1119" s="34">
+        <v>2</v>
+      </c>
+      <c r="H1119" s="34" t="s">
+        <v>1922</v>
+      </c>
+      <c r="I1119" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1120" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1120" s="36">
+        <v>46099</v>
+      </c>
+      <c r="C1120" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1120" s="48">
+        <v>46162</v>
+      </c>
+      <c r="E1120" s="32" t="s">
+        <v>1923</v>
+      </c>
+      <c r="F1120" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1120" s="34">
+        <v>97</v>
+      </c>
+      <c r="H1120" s="34" t="s">
+        <v>1924</v>
+      </c>
+      <c r="I1120" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1121" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1121" s="36">
+        <v>46099</v>
+      </c>
+      <c r="C1121" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1121" s="48">
+        <v>46162</v>
+      </c>
+      <c r="E1121" s="32" t="s">
+        <v>1925</v>
+      </c>
+      <c r="F1121" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1121" s="34">
+        <v>9</v>
+      </c>
+      <c r="H1121" s="34" t="s">
+        <v>1924</v>
+      </c>
+      <c r="I1121" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1122" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1122" s="36">
+        <v>46099</v>
+      </c>
+      <c r="C1122" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1122" s="48">
+        <v>46162</v>
+      </c>
+      <c r="E1122" s="32" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F1122" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1122" s="34">
+        <v>36</v>
+      </c>
+      <c r="H1122" s="34" t="s">
+        <v>1927</v>
+      </c>
+      <c r="I1122" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1123" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1123" s="36">
+        <v>46099</v>
+      </c>
+      <c r="C1123" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1123" s="48">
+        <v>46162</v>
+      </c>
+      <c r="E1123" s="32" t="s">
+        <v>1928</v>
+      </c>
+      <c r="F1123" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1123" s="34">
+        <v>43</v>
+      </c>
+      <c r="H1123" s="34" t="s">
+        <v>1929</v>
+      </c>
+      <c r="I1123" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1124" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1124" s="36">
+        <v>46099</v>
+      </c>
+      <c r="C1124" s="36">
+        <v>46100</v>
+      </c>
+      <c r="D1124" s="48">
+        <v>46162</v>
+      </c>
+      <c r="E1124" s="32" t="s">
+        <v>1930</v>
+      </c>
+      <c r="F1124" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1124" s="34">
+        <v>51</v>
+      </c>
+      <c r="H1124" s="34" t="s">
+        <v>1931</v>
+      </c>
+      <c r="I1124" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1125" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1125" s="36">
+        <v>46101</v>
+      </c>
+      <c r="C1125" s="36">
+        <v>46101</v>
+      </c>
+      <c r="D1125" s="48">
+        <v>46164</v>
+      </c>
+      <c r="E1125" s="32" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F1125" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1125" s="34">
+        <v>52</v>
+      </c>
+      <c r="H1125" s="34" t="s">
+        <v>1933</v>
+      </c>
+      <c r="I1125" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1126" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1126" s="36">
+        <v>46099</v>
+      </c>
+      <c r="C1126" s="36">
+        <v>46101</v>
+      </c>
+      <c r="D1126" s="48">
+        <v>46136</v>
+      </c>
+      <c r="E1126" s="32" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F1126" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1126" s="34">
+        <v>74</v>
+      </c>
+      <c r="H1126" s="34" t="s">
+        <v>1935</v>
+      </c>
+      <c r="I1126" s="26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1127" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1127" s="36">
+        <v>46100</v>
+      </c>
+      <c r="C1127" s="36">
+        <v>46101</v>
+      </c>
+      <c r="D1127" s="48">
+        <v>46203</v>
+      </c>
+      <c r="E1127" s="32" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F1127" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1127" s="34">
+        <v>67</v>
+      </c>
+      <c r="H1127" s="34" t="s">
+        <v>1937</v>
+      </c>
+      <c r="I1127" s="26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1128" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1128" s="36">
+        <v>46100</v>
+      </c>
+      <c r="C1128" s="36">
+        <v>46101</v>
+      </c>
+      <c r="D1128" s="48">
+        <v>46203</v>
+      </c>
+      <c r="E1128" s="32" t="s">
+        <v>1936</v>
+      </c>
+      <c r="F1128" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1128" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1128" s="34" t="s">
+        <v>1938</v>
+      </c>
+      <c r="I1128" s="26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1129" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1129" s="36">
+        <v>46100</v>
+      </c>
+      <c r="C1129" s="36">
+        <v>46101</v>
+      </c>
+      <c r="D1129" s="48">
+        <v>46161</v>
+      </c>
+      <c r="E1129" s="32" t="s">
+        <v>282</v>
+      </c>
+      <c r="F1129" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1129" s="34">
+        <v>44</v>
+      </c>
+      <c r="H1129" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="I1129" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1130" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1130" s="36">
+        <v>46101</v>
+      </c>
+      <c r="C1130" s="36">
+        <v>46101</v>
+      </c>
+      <c r="D1130" s="48">
+        <v>46204</v>
+      </c>
+      <c r="E1130" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="F1130" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1130" s="34">
+        <v>23</v>
+      </c>
+      <c r="H1130" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1130" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1131" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1131" s="36">
+        <v>46101</v>
+      </c>
+      <c r="C1131" s="36">
+        <v>46104</v>
+      </c>
+      <c r="D1131" s="48">
+        <v>46171</v>
+      </c>
+      <c r="E1131" s="32" t="s">
+        <v>1939</v>
+      </c>
+      <c r="F1131" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1131" s="34">
+        <v>9</v>
+      </c>
+      <c r="H1131" s="34" t="s">
+        <v>1940</v>
+      </c>
+      <c r="I1131" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1132" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1132" s="36">
+        <v>46101</v>
+      </c>
+      <c r="C1132" s="36">
+        <v>46104</v>
+      </c>
+      <c r="D1132" s="48">
+        <v>46171</v>
+      </c>
+      <c r="E1132" s="32" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F1132" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1132" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1132" s="34" t="s">
+        <v>1633</v>
+      </c>
+      <c r="I1132" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1133" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1133" s="36">
+        <v>46104</v>
+      </c>
+      <c r="C1133" s="36">
+        <v>46104</v>
+      </c>
+      <c r="D1133" s="48">
+        <v>46168</v>
+      </c>
+      <c r="E1133" s="32" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F1133" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1133" s="34">
+        <v>55</v>
+      </c>
+      <c r="H1133" s="34" t="s">
+        <v>1942</v>
+      </c>
+      <c r="I1133" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1134" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1134" s="40">
+        <v>46100</v>
+      </c>
+      <c r="C1134" s="40">
+        <v>46104</v>
+      </c>
+      <c r="D1134" s="55">
+        <v>46159</v>
+      </c>
+      <c r="E1134" s="32" t="s">
+        <v>1943</v>
+      </c>
+      <c r="F1134" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1134" s="34">
+        <v>163</v>
+      </c>
+      <c r="H1134" s="34" t="s">
+        <v>1944</v>
+      </c>
+      <c r="I1134" s="26" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -39015,7 +40700,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I1085</xm:sqref>
+          <xm:sqref>I3:I1134</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -39136,7 +40821,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>1839</v>
+        <v>1882</v>
       </c>
       <c r="E1"/>
     </row>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\entshare3\JS-Data\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B107AAA8-D70C-4CF3-AAE0-D8C24309EB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0126B506-3368-4F22-AB5F-AD31DE7A763A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5771" uniqueCount="1961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5956" uniqueCount="2009">
   <si>
     <t>County/Parish</t>
   </si>
@@ -5960,6 +5960,51 @@
     <t>2135 Butano Drive, #150  Sacramento CA 95825</t>
   </si>
   <si>
+    <t>Supernal, LLC (15555 Laguna Canyon Road)</t>
+  </si>
+  <si>
+    <t>Supernal, LLC. (117 Waterworks Way)</t>
+  </si>
+  <si>
+    <t>224 Airport  Parkway  San Jose CA 95110</t>
+  </si>
+  <si>
+    <t>Pernod Ricard Kenwood Holding LLC</t>
+  </si>
+  <si>
+    <t>9592 Sonoma Highway  Kenwood CA 95452</t>
+  </si>
+  <si>
+    <t>333 Continental Boulevard  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>MAG Brand Group, LLC</t>
+  </si>
+  <si>
+    <t>13861 Rosecrans Avenue  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>Nob Hill Foods</t>
+  </si>
+  <si>
+    <t>1250 Grant Road  Mountain View CA 94040</t>
+  </si>
+  <si>
+    <t>Bedabox, LLC (dba ShipMonk)</t>
+  </si>
+  <si>
+    <t>6010 Cajon Blvd.  San Bernardino CA 92407</t>
+  </si>
+  <si>
+    <t>Comprehensive Autism Center</t>
+  </si>
+  <si>
+    <t>3600 Lime St, Suite 612  Riverside CA 92501</t>
+  </si>
+  <si>
+    <t>3655 Ruffin Rd, Suite 100  San Diego CA 92123</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -5979,7 +6024,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 03/25/2026
+01/01/2023 - 04/01/2026
 </t>
     </r>
     <r>
@@ -5993,49 +6038,148 @@
     </r>
   </si>
   <si>
-    <t>Supernal, LLC (15555 Laguna Canyon Road)</t>
-  </si>
-  <si>
-    <t>Supernal, LLC. (117 Waterworks Way)</t>
-  </si>
-  <si>
-    <t>224 Airport  Parkway  San Jose CA 95110</t>
-  </si>
-  <si>
-    <t>Pernod Ricard Kenwood Holding LLC</t>
-  </si>
-  <si>
-    <t>9592 Sonoma Highway  Kenwood CA 95452</t>
-  </si>
-  <si>
-    <t>333 Continental Boulevard  El Segundo CA 90245</t>
-  </si>
-  <si>
-    <t>MAG Brand Group, LLC</t>
-  </si>
-  <si>
-    <t>13861 Rosecrans Avenue  Santa Fe Springs CA 90670</t>
-  </si>
-  <si>
-    <t>Nob Hill Foods</t>
-  </si>
-  <si>
-    <t>1250 Grant Road  Mountain View CA 94040</t>
-  </si>
-  <si>
-    <t>Bedabox, LLC (dba ShipMonk)</t>
-  </si>
-  <si>
-    <t>6010 Cajon Blvd.  San Bernardino CA 92407</t>
-  </si>
-  <si>
-    <t>Comprehensive Autism Center</t>
-  </si>
-  <si>
-    <t>3600 Lime St, Suite 612  Riverside CA 92501</t>
-  </si>
-  <si>
-    <t>3655 Ruffin Rd, Suite 100  San Diego CA 92123</t>
+    <t>333 Lakeside Drive  San Mateo CA 94404</t>
+  </si>
+  <si>
+    <t>DASH Industries</t>
+  </si>
+  <si>
+    <t>4500 Pell Drive  Sacramento CA 95838</t>
+  </si>
+  <si>
+    <t>Kay and Associates, Inc.</t>
+  </si>
+  <si>
+    <t>HMLAT-303, Building 2360, Hangar 3  Camp Pendleton CA 92055</t>
+  </si>
+  <si>
+    <t>Welcome Palm Springs LLC dba Riviera Resort &amp; Spa Palm Springs</t>
+  </si>
+  <si>
+    <t>1600 N. Indian Canyon Drive  Palm Springs CA 92262</t>
+  </si>
+  <si>
+    <t>Rb Wine Associates LLC dba Rack &amp; Riddle</t>
+  </si>
+  <si>
+    <t>1 Winemaster Way, Suite D  Lodi CA 95240</t>
+  </si>
+  <si>
+    <t>Sentinel Transportation, LLC</t>
+  </si>
+  <si>
+    <t>310 Nord Ave  Chico CA 95926</t>
+  </si>
+  <si>
+    <t>Calaveras County</t>
+  </si>
+  <si>
+    <t>746 Pool Station Rd  San Andreas CA 95249</t>
+  </si>
+  <si>
+    <t>Colusa County</t>
+  </si>
+  <si>
+    <t>1802 Old Hwy 99W  Williams CA 95987</t>
+  </si>
+  <si>
+    <t>3050 Wilbur Ave  Antioch CA 94509</t>
+  </si>
+  <si>
+    <t>2891 Mosquito Rd  Placerville CA 95667</t>
+  </si>
+  <si>
+    <t>245 Garden St  Willows CA 95988</t>
+  </si>
+  <si>
+    <t>13601 S. Broadway  Los Angeles CA 90061</t>
+  </si>
+  <si>
+    <t>2249 Atwater Blvd  Atwater CA 95301</t>
+  </si>
+  <si>
+    <t>Nevada County</t>
+  </si>
+  <si>
+    <t>720 S Auburn St  Grass Valley CA 95945</t>
+  </si>
+  <si>
+    <t>188 Crescent St  Quincy CA 95971</t>
+  </si>
+  <si>
+    <t>5725 Alder Ave  Sacramento CA 95828</t>
+  </si>
+  <si>
+    <t>14972 CA-160  Isleton CA 95641</t>
+  </si>
+  <si>
+    <t>3515 Navy Dr  Stockton CA 95203</t>
+  </si>
+  <si>
+    <t>6001 Rossi Ln  Gilroy CA 95020</t>
+  </si>
+  <si>
+    <t>2050 Oakland Rd  San Jose CA 95131</t>
+  </si>
+  <si>
+    <t>4990 Mountain Lakes Blvd  Redding CA 96003</t>
+  </si>
+  <si>
+    <t>1900 N 1st St  Dixon CA 95620</t>
+  </si>
+  <si>
+    <t>744 N Texas St  Fairfield CA 94533</t>
+  </si>
+  <si>
+    <t>720 B St  Modesto CA 95354</t>
+  </si>
+  <si>
+    <t>746 Merced St  Newman CA 95360</t>
+  </si>
+  <si>
+    <t>Sutter County</t>
+  </si>
+  <si>
+    <t>937 Von Geldern Way  Yuba City CA 95991</t>
+  </si>
+  <si>
+    <t>2155 Main St  Red Bluff CA 96080</t>
+  </si>
+  <si>
+    <t>13079 Sanguinetti Rd  Sonora CA 95370</t>
+  </si>
+  <si>
+    <t>1515 S River Rd  West Sacramento CA 95691</t>
+  </si>
+  <si>
+    <t>Yuba County</t>
+  </si>
+  <si>
+    <t>418 13th St  Marysville CA 95901</t>
+  </si>
+  <si>
+    <t>F10 Oceanside LLC</t>
+  </si>
+  <si>
+    <t>201 N Myers St  Oceanside CA 92054</t>
+  </si>
+  <si>
+    <t>John Adams Academy - El Dorado</t>
+  </si>
+  <si>
+    <t>1102 Investment Blvd.  El Dorado Hills CA 95762</t>
+  </si>
+  <si>
+    <t>John Adams Academy</t>
+  </si>
+  <si>
+    <t>1797 Bella Breeze Dr.  Lincoln CA 95648</t>
+  </si>
+  <si>
+    <t>John Adams academy</t>
+  </si>
+  <si>
+    <t>1 Sierra Gate Plaza  Roseville CA 95678</t>
   </si>
   <si>
     <r>
@@ -6049,7 +6193,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/25 to 03/25/2026</t>
+      <t>07/01/25 to 04/01/2026</t>
     </r>
     <r>
       <rPr>
@@ -6069,7 +6213,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1142.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1179.</t>
     </r>
   </si>
 </sst>
@@ -7371,7 +7515,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1142" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1179" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="28"/>
@@ -7789,7 +7933,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>60562</v>
+        <v>61514</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -7823,7 +7967,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -7854,7 +7998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I1142"/>
+  <dimension ref="A1:I1179"/>
   <sheetFormatPr defaultColWidth="161.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.90625" style="3" bestFit="1" customWidth="1"/>
@@ -7870,7 +8014,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="100" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>1960</v>
+        <v>2008</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -38251,7 +38395,7 @@
         <v>46140</v>
       </c>
       <c r="E1049" s="37" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="F1049" s="37" t="s">
         <v>6</v>
@@ -38280,7 +38424,7 @@
         <v>46140</v>
       </c>
       <c r="E1050" s="41" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F1050" s="41" t="s">
         <v>6</v>
@@ -39681,7 +39825,7 @@
         <v>12</v>
       </c>
       <c r="H1098" s="34" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="I1098" s="26" t="s">
         <v>39</v>
@@ -40745,7 +40889,7 @@
         <v>46112</v>
       </c>
       <c r="E1135" s="37" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="F1135" s="37" t="s">
         <v>54</v>
@@ -40754,7 +40898,7 @@
         <v>14</v>
       </c>
       <c r="H1135" s="34" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="I1135" s="26" t="s">
         <v>34</v>
@@ -40783,7 +40927,7 @@
         <v>65</v>
       </c>
       <c r="H1136" s="34" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="I1136" s="26" t="s">
         <v>38</v>
@@ -40803,7 +40947,7 @@
         <v>46235</v>
       </c>
       <c r="E1137" s="37" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="F1137" s="37" t="s">
         <v>54</v>
@@ -40812,7 +40956,7 @@
         <v>53</v>
       </c>
       <c r="H1137" s="34" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="I1137" s="26" t="s">
         <v>34</v>
@@ -40832,7 +40976,7 @@
         <v>46171</v>
       </c>
       <c r="E1138" s="37" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="F1138" s="37" t="s">
         <v>54</v>
@@ -40841,7 +40985,7 @@
         <v>50</v>
       </c>
       <c r="H1138" s="34" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="I1138" s="26" t="s">
         <v>36</v>
@@ -40890,7 +41034,7 @@
         <v>46203</v>
       </c>
       <c r="E1140" s="37" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="F1140" s="37" t="s">
         <v>54</v>
@@ -40899,7 +41043,7 @@
         <v>124</v>
       </c>
       <c r="H1140" s="34" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="I1140" s="26" t="s">
         <v>37</v>
@@ -40919,7 +41063,7 @@
         <v>46173</v>
       </c>
       <c r="E1141" s="37" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="F1141" s="37" t="s">
         <v>54</v>
@@ -40928,7 +41072,7 @@
         <v>27</v>
       </c>
       <c r="H1141" s="34" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="I1141" s="26" t="s">
         <v>45</v>
@@ -40948,7 +41092,7 @@
         <v>46173</v>
       </c>
       <c r="E1142" s="41" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="F1142" s="41" t="s">
         <v>54</v>
@@ -40957,10 +41101,1083 @@
         <v>35</v>
       </c>
       <c r="H1142" s="34" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="I1142" s="26" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1143" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1143" s="36">
+        <v>46106</v>
+      </c>
+      <c r="C1143" s="36">
+        <v>46107</v>
+      </c>
+      <c r="D1143" s="36">
+        <v>46171</v>
+      </c>
+      <c r="E1143" s="37" t="s">
+        <v>391</v>
+      </c>
+      <c r="F1143" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1143" s="43">
+        <v>51</v>
+      </c>
+      <c r="H1143" s="34" t="s">
+        <v>1960</v>
+      </c>
+      <c r="I1143" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1144" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1144" s="36">
+        <v>46107</v>
+      </c>
+      <c r="C1144" s="36">
+        <v>46107</v>
+      </c>
+      <c r="D1144" s="36">
+        <v>46112</v>
+      </c>
+      <c r="E1144" s="37" t="s">
+        <v>1961</v>
+      </c>
+      <c r="F1144" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1144" s="43">
+        <v>80</v>
+      </c>
+      <c r="H1144" s="34" t="s">
+        <v>1962</v>
+      </c>
+      <c r="I1144" s="26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1145" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1145" s="36">
+        <v>46107</v>
+      </c>
+      <c r="C1145" s="36">
+        <v>46107</v>
+      </c>
+      <c r="D1145" s="36">
+        <v>46142</v>
+      </c>
+      <c r="E1145" s="37" t="s">
+        <v>1963</v>
+      </c>
+      <c r="F1145" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1145" s="43">
+        <v>103</v>
+      </c>
+      <c r="H1145" s="34" t="s">
+        <v>1964</v>
+      </c>
+      <c r="I1145" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1146" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1146" s="36">
+        <v>46107</v>
+      </c>
+      <c r="C1146" s="36">
+        <v>46108</v>
+      </c>
+      <c r="D1146" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1146" s="37" t="s">
+        <v>1965</v>
+      </c>
+      <c r="F1146" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1146" s="43">
+        <v>233</v>
+      </c>
+      <c r="H1146" s="34" t="s">
+        <v>1966</v>
+      </c>
+      <c r="I1146" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1147" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1147" s="36">
+        <v>46108</v>
+      </c>
+      <c r="C1147" s="36">
+        <v>46108</v>
+      </c>
+      <c r="D1147" s="36">
+        <v>46171</v>
+      </c>
+      <c r="E1147" s="37" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F1147" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1147" s="43">
+        <v>32</v>
+      </c>
+      <c r="H1147" s="34" t="s">
+        <v>1968</v>
+      </c>
+      <c r="I1147" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1148" s="35" t="s">
+        <v>492</v>
+      </c>
+      <c r="B1148" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1148" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1148" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1148" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1148" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1148" s="43">
+        <v>10</v>
+      </c>
+      <c r="H1148" s="34" t="s">
+        <v>1970</v>
+      </c>
+      <c r="I1148" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1149" s="35" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B1149" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1149" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1149" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1149" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1149" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1149" s="43">
+        <v>3</v>
+      </c>
+      <c r="H1149" s="34" t="s">
+        <v>1972</v>
+      </c>
+      <c r="I1149" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1150" s="35" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B1150" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1150" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1150" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1150" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1150" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1150" s="43">
+        <v>3</v>
+      </c>
+      <c r="H1150" s="34" t="s">
+        <v>1974</v>
+      </c>
+      <c r="I1150" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1151" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1151" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1151" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1151" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1151" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1151" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1151" s="43">
+        <v>7</v>
+      </c>
+      <c r="H1151" s="34" t="s">
+        <v>1975</v>
+      </c>
+      <c r="I1151" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1152" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1152" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1152" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1152" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1152" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1152" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1152" s="43">
+        <v>2</v>
+      </c>
+      <c r="H1152" s="34" t="s">
+        <v>1976</v>
+      </c>
+      <c r="I1152" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1153" s="35" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1153" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1153" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1153" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1153" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1153" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1153" s="43">
+        <v>3</v>
+      </c>
+      <c r="H1153" s="34" t="s">
+        <v>1977</v>
+      </c>
+      <c r="I1153" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1154" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1154" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1154" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1154" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1154" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1154" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1154" s="43">
+        <v>2</v>
+      </c>
+      <c r="H1154" s="34" t="s">
+        <v>1978</v>
+      </c>
+      <c r="I1154" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1155" s="35" t="s">
+        <v>339</v>
+      </c>
+      <c r="B1155" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1155" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1155" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1155" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1155" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1155" s="43">
+        <v>1</v>
+      </c>
+      <c r="H1155" s="34" t="s">
+        <v>1979</v>
+      </c>
+      <c r="I1155" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1156" s="35" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B1156" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1156" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1156" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1156" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1156" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1156" s="43">
+        <v>3</v>
+      </c>
+      <c r="H1156" s="34" t="s">
+        <v>1981</v>
+      </c>
+      <c r="I1156" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1157" s="35" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B1157" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1157" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1157" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1157" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1157" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1157" s="43">
+        <v>3</v>
+      </c>
+      <c r="H1157" s="34" t="s">
+        <v>1982</v>
+      </c>
+      <c r="I1157" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1158" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1158" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1158" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1158" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1158" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1158" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1158" s="43">
+        <v>24</v>
+      </c>
+      <c r="H1158" s="34" t="s">
+        <v>1983</v>
+      </c>
+      <c r="I1158" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1159" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1159" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1159" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1159" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1159" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1159" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1159" s="43">
+        <v>3</v>
+      </c>
+      <c r="H1159" s="34" t="s">
+        <v>1984</v>
+      </c>
+      <c r="I1159" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1160" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1160" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1160" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1160" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1160" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1160" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1160" s="43">
+        <v>2</v>
+      </c>
+      <c r="H1160" s="34" t="s">
+        <v>1985</v>
+      </c>
+      <c r="I1160" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1161" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1161" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1161" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1161" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1161" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1161" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1161" s="43">
+        <v>2</v>
+      </c>
+      <c r="H1161" s="34" t="s">
+        <v>1986</v>
+      </c>
+      <c r="I1161" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1162" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1162" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1162" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1162" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1162" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1162" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1162" s="43">
+        <v>2</v>
+      </c>
+      <c r="H1162" s="34" t="s">
+        <v>1987</v>
+      </c>
+      <c r="I1162" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1163" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1163" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1163" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1163" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1163" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1163" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1163" s="43">
+        <v>5</v>
+      </c>
+      <c r="H1163" s="34" t="s">
+        <v>1988</v>
+      </c>
+      <c r="I1163" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1164" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1164" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1164" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1164" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1164" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1164" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1164" s="43">
+        <v>5</v>
+      </c>
+      <c r="H1164" s="34" t="s">
+        <v>1989</v>
+      </c>
+      <c r="I1164" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1165" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1165" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1165" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1165" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1165" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1165" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1165" s="43">
+        <v>4</v>
+      </c>
+      <c r="H1165" s="34" t="s">
+        <v>1990</v>
+      </c>
+      <c r="I1165" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1166" s="35" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1166" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1166" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1166" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1166" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1166" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1166" s="43">
+        <v>24</v>
+      </c>
+      <c r="H1166" s="34" t="s">
+        <v>1991</v>
+      </c>
+      <c r="I1166" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1167" s="35" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1167" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1167" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1167" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1167" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1167" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1167" s="43">
+        <v>1</v>
+      </c>
+      <c r="H1167" s="34" t="s">
+        <v>1992</v>
+      </c>
+      <c r="I1167" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1168" s="35" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B1168" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1168" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1168" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1168" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1168" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1168" s="43">
+        <v>1</v>
+      </c>
+      <c r="H1168" s="34" t="s">
+        <v>1994</v>
+      </c>
+      <c r="I1168" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1169" s="35" t="s">
+        <v>394</v>
+      </c>
+      <c r="B1169" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1169" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1169" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1169" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1169" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1169" s="43">
+        <v>1</v>
+      </c>
+      <c r="H1169" s="34" t="s">
+        <v>1995</v>
+      </c>
+      <c r="I1169" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1170" s="35" t="s">
+        <v>749</v>
+      </c>
+      <c r="B1170" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1170" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1170" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1170" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1170" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1170" s="43">
+        <v>3</v>
+      </c>
+      <c r="H1170" s="34" t="s">
+        <v>1996</v>
+      </c>
+      <c r="I1170" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1171" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1171" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1171" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1171" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1171" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1171" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1171" s="43">
+        <v>8</v>
+      </c>
+      <c r="H1171" s="34" t="s">
+        <v>1997</v>
+      </c>
+      <c r="I1171" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1172" s="35" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B1172" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1172" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1172" s="36">
+        <v>46173</v>
+      </c>
+      <c r="E1172" s="37" t="s">
+        <v>1969</v>
+      </c>
+      <c r="F1172" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1172" s="43">
+        <v>4</v>
+      </c>
+      <c r="H1172" s="34" t="s">
+        <v>1999</v>
+      </c>
+      <c r="I1172" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1173" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1173" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1173" s="36">
+        <v>46111</v>
+      </c>
+      <c r="D1173" s="36">
+        <v>46156</v>
+      </c>
+      <c r="E1173" s="37" t="s">
+        <v>2000</v>
+      </c>
+      <c r="F1173" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1173" s="43">
+        <v>58</v>
+      </c>
+      <c r="H1173" s="34" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I1173" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1174" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="B1174" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1174" s="36">
+        <v>46113</v>
+      </c>
+      <c r="D1174" s="36">
+        <v>46174</v>
+      </c>
+      <c r="E1174" s="37" t="s">
+        <v>2002</v>
+      </c>
+      <c r="F1174" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1174" s="43">
+        <v>6</v>
+      </c>
+      <c r="H1174" s="34" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I1174" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1175" s="35" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1175" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1175" s="36">
+        <v>46113</v>
+      </c>
+      <c r="D1175" s="36">
+        <v>46174</v>
+      </c>
+      <c r="E1175" s="37" t="s">
+        <v>2004</v>
+      </c>
+      <c r="F1175" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1175" s="43">
+        <v>13</v>
+      </c>
+      <c r="H1175" s="34" t="s">
+        <v>2005</v>
+      </c>
+      <c r="I1175" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1176" s="35" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1176" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1176" s="36">
+        <v>46113</v>
+      </c>
+      <c r="D1176" s="36">
+        <v>46174</v>
+      </c>
+      <c r="E1176" s="37" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F1176" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1176" s="43">
+        <v>49</v>
+      </c>
+      <c r="H1176" s="34" t="s">
+        <v>2007</v>
+      </c>
+      <c r="I1176" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1177" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1177" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1177" s="36">
+        <v>46113</v>
+      </c>
+      <c r="D1177" s="36">
+        <v>46164</v>
+      </c>
+      <c r="E1177" s="37" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F1177" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1177" s="43">
+        <v>124</v>
+      </c>
+      <c r="H1177" s="34" t="s">
+        <v>1485</v>
+      </c>
+      <c r="I1177" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1178" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1178" s="36">
+        <v>46111</v>
+      </c>
+      <c r="C1178" s="36">
+        <v>46113</v>
+      </c>
+      <c r="D1178" s="36">
+        <v>46171</v>
+      </c>
+      <c r="E1178" s="37" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F1178" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1178" s="43">
+        <v>74</v>
+      </c>
+      <c r="H1178" s="34" t="s">
+        <v>1643</v>
+      </c>
+      <c r="I1178" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1179" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1179" s="40">
+        <v>46111</v>
+      </c>
+      <c r="C1179" s="40">
+        <v>46113</v>
+      </c>
+      <c r="D1179" s="40">
+        <v>46164</v>
+      </c>
+      <c r="E1179" s="41" t="s">
+        <v>1837</v>
+      </c>
+      <c r="F1179" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1179" s="44">
+        <v>3</v>
+      </c>
+      <c r="H1179" s="34" t="s">
+        <v>1838</v>
+      </c>
+      <c r="I1179" s="26" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -40977,7 +42194,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I1142</xm:sqref>
+          <xm:sqref>I3:I1179</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -41098,7 +42315,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="98.5" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
-        <v>1944</v>
+        <v>1959</v>
       </c>
       <c r="E1"/>
     </row>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\entshare3\JS-Data\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\5. WARN (Worker Adjustment and Retraining Notification) Updates\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\entshare3\JS-Data\WSB-CO\BPAC\Policy &amp; Program Communications Group\Communications Unit\Website Management\4. WARN (Worker Adjustment and Retraining Notification) Updates\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0461B108-51DA-4E24-A052-C39D819C4415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44CA0E53-4A17-4362-BED4-6F935937FE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6211" uniqueCount="2103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6311" uniqueCount="2124">
   <si>
     <t>County/Parish</t>
   </si>
@@ -6464,6 +6464,69 @@
     <t>3115 Merryfield Row, Suite 120  San Diego CA 92121</t>
   </si>
   <si>
+    <t>Sony Pictures Entertainment Inc.</t>
+  </si>
+  <si>
+    <t>Sumisho Air Lease Corporation</t>
+  </si>
+  <si>
+    <t>Mills College Children's School at Northwestern University</t>
+  </si>
+  <si>
+    <t>Boeing Company</t>
+  </si>
+  <si>
+    <t>10202 W. Washington Boulevard  Culver City CA 90232</t>
+  </si>
+  <si>
+    <t>5750 Wilshire Boulevard  Los Angeles CA 90036</t>
+  </si>
+  <si>
+    <t>6007 Sepulveda Boulevard  Van Nuys CA 91411</t>
+  </si>
+  <si>
+    <t>2150 Colorado Avenue  Santa Monica CA 90404</t>
+  </si>
+  <si>
+    <t>5525 Morehouse Drive  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>5665 Morehouse Drive  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>10145 Pacific Heights Blvd.  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>6455 Lusk Blvd.  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>10185 McKellar Ct.  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>5745 Pacific Center Blvd.  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>10160 Pacific Mesa Blvd.  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>10445 Pacific Center Court  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>2000 Avenue of the Stars, Suite 1000N  Los Angeles CA 90067</t>
+  </si>
+  <si>
+    <t>5000 MacArthur Blvd.  Oakland CA 94613</t>
+  </si>
+  <si>
+    <t>300 Mission Street, 19th Floor  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>1500 Columbia Way (E. Ave. M) USAF Plant 42  Palmdale CA 93550</t>
+  </si>
+  <si>
+    <t>Qualcomm Incorporated</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -6475,7 +6538,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/25 to 04/08/2026</t>
+      <t>07/01/25 to 04/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -6495,7 +6558,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1230.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1250.</t>
     </r>
   </si>
 </sst>
@@ -6845,7 +6908,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7005,6 +7068,9 @@
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -7797,7 +7863,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1230" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1250" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="28"/>
@@ -8193,7 +8259,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
@@ -8215,7 +8281,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>63344</v>
+        <v>63841</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -8249,7 +8315,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -8280,23 +8346,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I1230"/>
+  <dimension ref="A1:I1250"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="72.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="61.7109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="76.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="63" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="55" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>2102</v>
+        <v>2123</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -17928,7 +17994,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A334" s="32" t="s">
         <v>5</v>
       </c>
@@ -18566,7 +18632,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A356" s="32" t="s">
         <v>52</v>
       </c>
@@ -18595,7 +18661,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A357" s="32" t="s">
         <v>97</v>
       </c>
@@ -18653,7 +18719,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A359" s="32" t="s">
         <v>90</v>
       </c>
@@ -18682,7 +18748,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A360" s="32" t="s">
         <v>90</v>
       </c>
@@ -18740,7 +18806,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A362" s="32" t="s">
         <v>90</v>
       </c>
@@ -22423,7 +22489,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A489" s="32" t="s">
         <v>492</v>
       </c>
@@ -31732,7 +31798,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A810" s="52" t="s">
         <v>5</v>
       </c>
@@ -43042,7 +43108,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="1200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1200" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A1200" s="35" t="s">
         <v>74</v>
       </c>
@@ -43939,6 +44005,586 @@
       </c>
       <c r="I1230" s="26" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1231" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1231" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1231" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1231" s="56">
+        <v>46185</v>
+      </c>
+      <c r="E1231" s="32" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F1231" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1231" s="34">
+        <v>111</v>
+      </c>
+      <c r="H1231" s="34" t="s">
+        <v>2106</v>
+      </c>
+      <c r="I1231" s="26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1232" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1232" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1232" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1232" s="56">
+        <v>46185</v>
+      </c>
+      <c r="E1232" s="32" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F1232" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1232" s="34">
+        <v>6</v>
+      </c>
+      <c r="H1232" s="34" t="s">
+        <v>2107</v>
+      </c>
+      <c r="I1232" s="26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1233" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1233" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1233" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1233" s="56">
+        <v>46185</v>
+      </c>
+      <c r="E1233" s="32" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F1233" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1233" s="34">
+        <v>7</v>
+      </c>
+      <c r="H1233" s="34" t="s">
+        <v>2108</v>
+      </c>
+      <c r="I1233" s="26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1234" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1234" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1234" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1234" s="56">
+        <v>46185</v>
+      </c>
+      <c r="E1234" s="32" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F1234" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1234" s="34">
+        <v>9</v>
+      </c>
+      <c r="H1234" s="34" t="s">
+        <v>2109</v>
+      </c>
+      <c r="I1234" s="26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1235" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1235" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1235" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1235" s="56">
+        <v>46181</v>
+      </c>
+      <c r="E1235" s="32" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F1235" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1235" s="34">
+        <v>10</v>
+      </c>
+      <c r="H1235" s="34" t="s">
+        <v>2021</v>
+      </c>
+      <c r="I1235" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1236" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1236" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1236" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1236" s="56">
+        <v>46181</v>
+      </c>
+      <c r="E1236" s="32" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F1236" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1236" s="34">
+        <v>11</v>
+      </c>
+      <c r="H1236" s="34" t="s">
+        <v>2110</v>
+      </c>
+      <c r="I1236" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1237" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1237" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1237" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1237" s="56">
+        <v>46181</v>
+      </c>
+      <c r="E1237" s="32" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F1237" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1237" s="34">
+        <v>6</v>
+      </c>
+      <c r="H1237" s="34" t="s">
+        <v>2111</v>
+      </c>
+      <c r="I1237" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1238" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1238" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1238" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1238" s="56">
+        <v>46181</v>
+      </c>
+      <c r="E1238" s="32" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F1238" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1238" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1238" s="34" t="s">
+        <v>2112</v>
+      </c>
+      <c r="I1238" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1239" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1239" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1239" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1239" s="56">
+        <v>46181</v>
+      </c>
+      <c r="E1239" s="32" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F1239" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1239" s="34">
+        <v>2</v>
+      </c>
+      <c r="H1239" s="34" t="s">
+        <v>2113</v>
+      </c>
+      <c r="I1239" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1240" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1240" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1240" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1240" s="56">
+        <v>46181</v>
+      </c>
+      <c r="E1240" s="32" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F1240" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1240" s="34">
+        <v>1</v>
+      </c>
+      <c r="H1240" s="34" t="s">
+        <v>2114</v>
+      </c>
+      <c r="I1240" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1241" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1241" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1241" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1241" s="56">
+        <v>46181</v>
+      </c>
+      <c r="E1241" s="32" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F1241" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1241" s="34">
+        <v>2</v>
+      </c>
+      <c r="H1241" s="34" t="s">
+        <v>2115</v>
+      </c>
+      <c r="I1241" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1242" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1242" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1242" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1242" s="56">
+        <v>46181</v>
+      </c>
+      <c r="E1242" s="32" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F1242" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1242" s="34">
+        <v>1</v>
+      </c>
+      <c r="H1242" s="34" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I1242" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1243" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1243" s="33">
+        <v>46120</v>
+      </c>
+      <c r="C1243" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1243" s="56">
+        <v>46181</v>
+      </c>
+      <c r="E1243" s="32" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F1243" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1243" s="34">
+        <v>2</v>
+      </c>
+      <c r="H1243" s="34" t="s">
+        <v>2117</v>
+      </c>
+      <c r="I1243" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1244" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1244" s="33">
+        <v>46118</v>
+      </c>
+      <c r="C1244" s="33">
+        <v>46121</v>
+      </c>
+      <c r="D1244" s="56">
+        <v>46119</v>
+      </c>
+      <c r="E1244" s="32" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F1244" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1244" s="34">
+        <v>25</v>
+      </c>
+      <c r="H1244" s="34" t="s">
+        <v>1668</v>
+      </c>
+      <c r="I1244" s="26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1245" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1245" s="33">
+        <v>46121</v>
+      </c>
+      <c r="C1245" s="33">
+        <v>46122</v>
+      </c>
+      <c r="D1245" s="56">
+        <v>46181</v>
+      </c>
+      <c r="E1245" s="32" t="s">
+        <v>2103</v>
+      </c>
+      <c r="F1245" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1245" s="34">
+        <v>53</v>
+      </c>
+      <c r="H1245" s="34" t="s">
+        <v>2118</v>
+      </c>
+      <c r="I1245" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1246" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1246" s="33">
+        <v>46122</v>
+      </c>
+      <c r="C1246" s="33">
+        <v>46122</v>
+      </c>
+      <c r="D1246" s="56">
+        <v>46183</v>
+      </c>
+      <c r="E1246" s="32" t="s">
+        <v>2104</v>
+      </c>
+      <c r="F1246" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1246" s="34">
+        <v>21</v>
+      </c>
+      <c r="H1246" s="34" t="s">
+        <v>2119</v>
+      </c>
+      <c r="I1246" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1247" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1247" s="33">
+        <v>46122</v>
+      </c>
+      <c r="C1247" s="33">
+        <v>46122</v>
+      </c>
+      <c r="D1247" s="56">
+        <v>46295</v>
+      </c>
+      <c r="E1247" s="32" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F1247" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1247" s="34">
+        <v>198</v>
+      </c>
+      <c r="H1247" s="34" t="s">
+        <v>2120</v>
+      </c>
+      <c r="I1247" s="26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1248" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1248" s="33">
+        <v>46122</v>
+      </c>
+      <c r="C1248" s="33">
+        <v>46122</v>
+      </c>
+      <c r="D1248" s="56">
+        <v>46183</v>
+      </c>
+      <c r="E1248" s="32" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F1248" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1248" s="34">
+        <v>10</v>
+      </c>
+      <c r="H1248" s="34" t="s">
+        <v>1494</v>
+      </c>
+      <c r="I1248" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1249" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1249" s="33">
+        <v>46122</v>
+      </c>
+      <c r="C1249" s="33">
+        <v>46122</v>
+      </c>
+      <c r="D1249" s="56">
+        <v>46183</v>
+      </c>
+      <c r="E1249" s="32" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F1249" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1249" s="34">
+        <v>6</v>
+      </c>
+      <c r="H1249" s="34" t="s">
+        <v>1496</v>
+      </c>
+      <c r="I1249" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1250" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1250" s="33">
+        <v>46125</v>
+      </c>
+      <c r="C1250" s="33">
+        <v>46125</v>
+      </c>
+      <c r="D1250" s="56">
+        <v>46185</v>
+      </c>
+      <c r="E1250" s="32" t="s">
+        <v>2105</v>
+      </c>
+      <c r="F1250" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1250" s="34">
+        <v>13</v>
+      </c>
+      <c r="H1250" s="34" t="s">
+        <v>2121</v>
+      </c>
+      <c r="I1250" s="26" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -43955,7 +44601,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I1230</xm:sqref>
+          <xm:sqref>I3:I1250</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -43968,7 +44614,7 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.7109375" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -44064,13 +44710,13 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jchinn2\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F1B0EB3-86B8-43D0-8093-8B334953A44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FD3CB4C-BF87-44F7-9678-577955221B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6356" uniqueCount="2136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6546" uniqueCount="2199">
   <si>
     <t>County/Parish</t>
   </si>
@@ -6494,6 +6494,198 @@
     <t>Qualcomm Incorporated</t>
   </si>
   <si>
+    <t>The Gambrinus Company (Trumer Brewery and Taproom)</t>
+  </si>
+  <si>
+    <t>1404 Fourth Street  Berkeley CA 94710</t>
+  </si>
+  <si>
+    <t>Trumer Brewery, Comeback Brewing II dba Trumer Brewery</t>
+  </si>
+  <si>
+    <t>Redding Cement Plant</t>
+  </si>
+  <si>
+    <t>15390 Wonderland Blvd.  Redding CA 96003</t>
+  </si>
+  <si>
+    <t>Chen-Tech Industries LLC</t>
+  </si>
+  <si>
+    <t>9 Wrigley  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>12310 Avenue 368  Visalia CA 93291</t>
+  </si>
+  <si>
+    <t>Snap Inc.</t>
+  </si>
+  <si>
+    <t>2772 Donald Douglas Loop N  Santa Monica CA 90405</t>
+  </si>
+  <si>
+    <t>Block by Block</t>
+  </si>
+  <si>
+    <t>870 Market St.  San Francisco CA 94102</t>
+  </si>
+  <si>
+    <t>The Primary School</t>
+  </si>
+  <si>
+    <t>Noa Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>Disney Entertainment Operations LLC</t>
+  </si>
+  <si>
+    <t>FM Restaurants HQ, LLC</t>
+  </si>
+  <si>
+    <t>Best Formulations PC, LLC</t>
+  </si>
+  <si>
+    <t>Yanfeng International Automotive Technology</t>
+  </si>
+  <si>
+    <t>YMCA Arellanes Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA Arellanes Junior High</t>
+  </si>
+  <si>
+    <t>YMCA Bonita Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA Robert Bruce Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA El Camino Jr. High School</t>
+  </si>
+  <si>
+    <t>YMCA Fairlawn Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA Fesler Jr. High School</t>
+  </si>
+  <si>
+    <t>YMCA Roberto &amp; Dr. Francisco Jimenez Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA Tommie Kunst Jr. High School</t>
+  </si>
+  <si>
+    <t>YMCA Bill Libbon Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA Liberty Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA Juan Pacifico Ontiveros Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA Rice Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA Sanchez Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA Taylor Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA Tunnel Elementary School</t>
+  </si>
+  <si>
+    <t>YMCA Santa Maria Valley</t>
+  </si>
+  <si>
+    <t>YMCA Oakley Elementary School</t>
+  </si>
+  <si>
+    <t>Guayabito Farms, LLC</t>
+  </si>
+  <si>
+    <t>Premier Berry Farms, LLC</t>
+  </si>
+  <si>
+    <t>750 Fargo Ave  San Leandro CA 94579</t>
+  </si>
+  <si>
+    <t>395 Page Mill Road, 3rd Floor  Palo Alto CA 94306</t>
+  </si>
+  <si>
+    <t>1137 San Antonio Road  Mountain View CA 94043</t>
+  </si>
+  <si>
+    <t>500 South Buena Vista St.  Burbank CA 91521</t>
+  </si>
+  <si>
+    <t>11065 Knott Avenue, Suite A  Cypress CA 90630</t>
+  </si>
+  <si>
+    <t>5900 Skylab Rd  Huntington Beach CA 92647</t>
+  </si>
+  <si>
+    <t>1890 Sandalwood Dr.  Santa Maria CA 93455</t>
+  </si>
+  <si>
+    <t>2715 W. Main St.  Santa Maria CA 93458</t>
+  </si>
+  <si>
+    <t>604 W. Alvin Ave.  Santa Maria CA 93458</t>
+  </si>
+  <si>
+    <t>219 W El Camino St.  Santa Maria CA 93458</t>
+  </si>
+  <si>
+    <t>123 St Mary Drive  Santa Maria CA 93458</t>
+  </si>
+  <si>
+    <t>1100 E Fesler St.  Santa Maria CA 93454</t>
+  </si>
+  <si>
+    <t>1970 Biscayne St.  Santa Maria CA 93458</t>
+  </si>
+  <si>
+    <t>930 Hidden Pines Way  Santa Maria CA 93458</t>
+  </si>
+  <si>
+    <t>750 Meehan St.  Santa Maria CA 93454</t>
+  </si>
+  <si>
+    <t>1300 Sonya Ln.  Santa Maria CA 93458</t>
+  </si>
+  <si>
+    <t>930 Rancho Verde  Santa Maria CA 93458</t>
+  </si>
+  <si>
+    <t>700 Vickie Ave.  Santa Maria CA 93454</t>
+  </si>
+  <si>
+    <t>804 Liberty St.  Santa Maria CA 93458</t>
+  </si>
+  <si>
+    <t>1921 Carlotti Dr.  Santa Maria CA 93454</t>
+  </si>
+  <si>
+    <t>1248 Dena Way  Santa Maria CA 93454</t>
+  </si>
+  <si>
+    <t>3400 Skyway Drive  Santa Maria CA 93455</t>
+  </si>
+  <si>
+    <t>1120 W Harding Ave.  Santa Maria CA 93458</t>
+  </si>
+  <si>
+    <t>5060 Olivas Park Drive  Ventura CA 93003</t>
+  </si>
+  <si>
+    <t>2840 East Hueneme Road  Oxnard CA 93033</t>
+  </si>
+  <si>
+    <t>Paramount Skydance Corporation</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -6513,7 +6705,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 04/15/2026
+01/01/2023 - 04/22/2026
 </t>
     </r>
     <r>
@@ -6527,40 +6719,37 @@
     </r>
   </si>
   <si>
-    <t>The Gambrinus Company (Trumer Brewery and Taproom)</t>
-  </si>
-  <si>
-    <t>1404 Fourth Street  Berkeley CA 94710</t>
-  </si>
-  <si>
-    <t>Trumer Brewery, Comeback Brewing II dba Trumer Brewery</t>
-  </si>
-  <si>
-    <t>Redding Cement Plant</t>
-  </si>
-  <si>
-    <t>15390 Wonderland Blvd.  Redding CA 96003</t>
-  </si>
-  <si>
-    <t>Chen-Tech Industries LLC</t>
-  </si>
-  <si>
-    <t>9 Wrigley  Irvine CA 92618</t>
-  </si>
-  <si>
-    <t>12310 Avenue 368  Visalia CA 93291</t>
-  </si>
-  <si>
-    <t>Snap Inc.</t>
-  </si>
-  <si>
-    <t>2772 Donald Douglas Loop N  Santa Monica CA 90405</t>
-  </si>
-  <si>
-    <t>Block by Block</t>
-  </si>
-  <si>
-    <t>870 Market St.  San Francisco CA 94102</t>
+    <t>Ample Joy ABA Consulting Services, LLC</t>
+  </si>
+  <si>
+    <t>1411 Rimpau Avenue Suite 109  Corona CA 92879</t>
+  </si>
+  <si>
+    <t>ODS Technologies LP and Betfair Interactive US LLC</t>
+  </si>
+  <si>
+    <t>6701 Center Drive West, Suite 160  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Paramount Skydance Corporation - 1575 N. Gower</t>
+  </si>
+  <si>
+    <t>Next Stop Logistics Inc.</t>
+  </si>
+  <si>
+    <t>9350 Rayo Ave.  South Gate CA 90280</t>
+  </si>
+  <si>
+    <t>Joe's Crab Shack</t>
+  </si>
+  <si>
+    <t>12011 Harbor Blvd  Garden Grove CA 92840</t>
+  </si>
+  <si>
+    <t>Freudenberg Medical LLC</t>
+  </si>
+  <si>
+    <t>1110 Mark Avenue  Carpinteria CA 93013</t>
   </si>
   <si>
     <r>
@@ -6574,7 +6763,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/25 to 04/15/2026</t>
+      <t>07/01/25 to 04/22/2026</t>
     </r>
     <r>
       <rPr>
@@ -6594,7 +6783,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1259.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1297.</t>
     </r>
   </si>
 </sst>
@@ -7899,7 +8088,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1259" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1297" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
     <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="28"/>
@@ -8317,7 +8506,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>64466</v>
+        <v>65709</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -8351,7 +8540,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -8382,7 +8571,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I1259"/>
+  <dimension ref="A1:I1297"/>
   <sheetFormatPr defaultColWidth="161.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.90625" style="3" bestFit="1" customWidth="1"/>
@@ -8398,7 +8587,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="100" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>2135</v>
+        <v>2198</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -44637,16 +44826,16 @@
         <v>46171</v>
       </c>
       <c r="E1251" s="37" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F1251" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1251" s="43">
+        <v>6</v>
+      </c>
+      <c r="H1251" s="34" t="s">
         <v>2123</v>
-      </c>
-      <c r="F1251" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1251" s="43">
-        <v>6</v>
-      </c>
-      <c r="H1251" s="34" t="s">
-        <v>2124</v>
       </c>
       <c r="I1251" s="26" t="s">
         <v>35</v>
@@ -44666,7 +44855,7 @@
         <v>46171</v>
       </c>
       <c r="E1252" s="37" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="F1252" s="37" t="s">
         <v>54</v>
@@ -44675,7 +44864,7 @@
         <v>27</v>
       </c>
       <c r="H1252" s="34" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="I1252" s="26" t="s">
         <v>35</v>
@@ -44724,7 +44913,7 @@
         <v>46188</v>
       </c>
       <c r="E1254" s="37" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="F1254" s="37" t="s">
         <v>280</v>
@@ -44733,7 +44922,7 @@
         <v>53</v>
       </c>
       <c r="H1254" s="34" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="I1254" s="26" t="s">
         <v>34</v>
@@ -44753,7 +44942,7 @@
         <v>46114</v>
       </c>
       <c r="E1255" s="37" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="F1255" s="37" t="s">
         <v>6</v>
@@ -44762,7 +44951,7 @@
         <v>98</v>
       </c>
       <c r="H1255" s="34" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="I1255" s="26" t="s">
         <v>34</v>
@@ -44820,7 +45009,7 @@
         <v>69</v>
       </c>
       <c r="H1257" s="34" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="I1257" s="26" t="s">
         <v>34</v>
@@ -44840,7 +45029,7 @@
         <v>46128</v>
       </c>
       <c r="E1258" s="37" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="F1258" s="37" t="s">
         <v>6</v>
@@ -44849,7 +45038,7 @@
         <v>247</v>
       </c>
       <c r="H1258" s="34" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="I1258" s="26" t="s">
         <v>41</v>
@@ -44869,7 +45058,7 @@
         <v>46186</v>
       </c>
       <c r="E1259" s="41" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="F1259" s="41" t="s">
         <v>6</v>
@@ -44878,10 +45067,1112 @@
         <v>47</v>
       </c>
       <c r="H1259" s="34" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="I1259" s="26" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1260" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1260" s="33">
+        <v>46127</v>
+      </c>
+      <c r="C1260" s="33">
+        <v>46128</v>
+      </c>
+      <c r="D1260" s="56">
+        <v>46185</v>
+      </c>
+      <c r="E1260" s="32" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F1260" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1260" s="34">
+        <v>147</v>
+      </c>
+      <c r="H1260" s="34" t="s">
+        <v>2160</v>
+      </c>
+      <c r="I1260" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1261" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1261" s="33">
+        <v>46128</v>
+      </c>
+      <c r="C1261" s="33">
+        <v>46128</v>
+      </c>
+      <c r="D1261" s="56">
+        <v>46024</v>
+      </c>
+      <c r="E1261" s="26" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1261" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1261" s="34">
+        <v>2</v>
+      </c>
+      <c r="H1261" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="I1261" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1262" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1262" s="33">
+        <v>46128</v>
+      </c>
+      <c r="C1262" s="33">
+        <v>46128</v>
+      </c>
+      <c r="D1262" s="56">
+        <v>46024</v>
+      </c>
+      <c r="E1262" s="26" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1262" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1262" s="34">
+        <v>5</v>
+      </c>
+      <c r="H1262" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1262" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1263" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1263" s="33">
+        <v>46127</v>
+      </c>
+      <c r="C1263" s="33">
+        <v>46128</v>
+      </c>
+      <c r="D1263" s="56">
+        <v>46128</v>
+      </c>
+      <c r="E1263" s="32" t="s">
+        <v>2130</v>
+      </c>
+      <c r="F1263" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1263" s="34">
+        <v>73</v>
+      </c>
+      <c r="H1263" s="34" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I1263" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1264" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1264" s="33">
+        <v>46119</v>
+      </c>
+      <c r="C1264" s="33">
+        <v>46128</v>
+      </c>
+      <c r="D1264" s="56">
+        <v>46174</v>
+      </c>
+      <c r="E1264" s="32" t="s">
+        <v>2135</v>
+      </c>
+      <c r="F1264" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1264" s="34">
+        <v>69</v>
+      </c>
+      <c r="H1264" s="34" t="s">
+        <v>2162</v>
+      </c>
+      <c r="I1264" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1265" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1265" s="33">
+        <v>46128</v>
+      </c>
+      <c r="C1265" s="33">
+        <v>46128</v>
+      </c>
+      <c r="D1265" s="56">
+        <v>46193</v>
+      </c>
+      <c r="E1265" s="32" t="s">
+        <v>2136</v>
+      </c>
+      <c r="F1265" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1265" s="34">
+        <v>53</v>
+      </c>
+      <c r="H1265" s="34" t="s">
+        <v>2163</v>
+      </c>
+      <c r="I1265" s="26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1266" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1266" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1266" s="33">
+        <v>46129</v>
+      </c>
+      <c r="D1266" s="56">
+        <v>46131</v>
+      </c>
+      <c r="E1266" s="32" t="s">
+        <v>2137</v>
+      </c>
+      <c r="F1266" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1266" s="34">
+        <v>49</v>
+      </c>
+      <c r="H1266" s="34" t="s">
+        <v>2164</v>
+      </c>
+      <c r="I1266" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1267" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1267" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1267" s="33">
+        <v>46129</v>
+      </c>
+      <c r="D1267" s="56">
+        <v>46188</v>
+      </c>
+      <c r="E1267" s="32" t="s">
+        <v>2138</v>
+      </c>
+      <c r="F1267" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1267" s="34">
+        <v>32</v>
+      </c>
+      <c r="H1267" s="34" t="s">
+        <v>2165</v>
+      </c>
+      <c r="I1267" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1268" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1268" s="33">
+        <v>46132</v>
+      </c>
+      <c r="C1268" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1268" s="56">
+        <v>46195</v>
+      </c>
+      <c r="E1268" s="32" t="s">
+        <v>2139</v>
+      </c>
+      <c r="F1268" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1268" s="34">
+        <v>17</v>
+      </c>
+      <c r="H1268" s="34" t="s">
+        <v>1682</v>
+      </c>
+      <c r="I1268" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1269" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1269" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1269" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1269" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1269" s="32" t="s">
+        <v>2140</v>
+      </c>
+      <c r="F1269" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1269" s="34">
+        <v>6</v>
+      </c>
+      <c r="H1269" s="34" t="s">
+        <v>2166</v>
+      </c>
+      <c r="I1269" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1270" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1270" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1270" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1270" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1270" s="32" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1270" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1270" s="34">
+        <v>4</v>
+      </c>
+      <c r="H1270" s="34" t="s">
+        <v>2166</v>
+      </c>
+      <c r="I1270" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1271" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1271" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1271" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1271" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1271" s="32" t="s">
+        <v>2142</v>
+      </c>
+      <c r="F1271" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1271" s="34">
+        <v>6</v>
+      </c>
+      <c r="H1271" s="34" t="s">
+        <v>2167</v>
+      </c>
+      <c r="I1271" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1272" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1272" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1272" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1272" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1272" s="32" t="s">
+        <v>2143</v>
+      </c>
+      <c r="F1272" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1272" s="34">
+        <v>8</v>
+      </c>
+      <c r="H1272" s="34" t="s">
+        <v>2168</v>
+      </c>
+      <c r="I1272" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1273" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1273" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1273" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1273" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1273" s="32" t="s">
+        <v>2144</v>
+      </c>
+      <c r="F1273" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1273" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1273" s="34" t="s">
+        <v>2169</v>
+      </c>
+      <c r="I1273" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1274" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1274" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1274" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1274" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1274" s="32" t="s">
+        <v>2145</v>
+      </c>
+      <c r="F1274" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1274" s="34">
+        <v>6</v>
+      </c>
+      <c r="H1274" s="34" t="s">
+        <v>2170</v>
+      </c>
+      <c r="I1274" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1275" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1275" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1275" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1275" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1275" s="32" t="s">
+        <v>2146</v>
+      </c>
+      <c r="F1275" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1275" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1275" s="34" t="s">
+        <v>2171</v>
+      </c>
+      <c r="I1275" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1276" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1276" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1276" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1276" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1276" s="32" t="s">
+        <v>2147</v>
+      </c>
+      <c r="F1276" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1276" s="34">
+        <v>12</v>
+      </c>
+      <c r="H1276" s="34" t="s">
+        <v>2172</v>
+      </c>
+      <c r="I1276" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1277" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1277" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1277" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1277" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1277" s="32" t="s">
+        <v>2148</v>
+      </c>
+      <c r="F1277" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1277" s="34">
+        <v>3</v>
+      </c>
+      <c r="H1277" s="34" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I1277" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1278" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1278" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1278" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1278" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1278" s="32" t="s">
+        <v>2149</v>
+      </c>
+      <c r="F1278" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1278" s="34">
+        <v>11</v>
+      </c>
+      <c r="H1278" s="34" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I1278" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1279" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1279" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1279" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1279" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1279" s="32" t="s">
+        <v>2150</v>
+      </c>
+      <c r="F1279" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1279" s="34">
+        <v>9</v>
+      </c>
+      <c r="H1279" s="34" t="s">
+        <v>2175</v>
+      </c>
+      <c r="I1279" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1280" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1280" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1280" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1280" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1280" s="32" t="s">
+        <v>2151</v>
+      </c>
+      <c r="F1280" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1280" s="34">
+        <v>10</v>
+      </c>
+      <c r="H1280" s="34" t="s">
+        <v>2176</v>
+      </c>
+      <c r="I1280" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1281" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1281" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1281" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1281" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1281" s="32" t="s">
+        <v>2152</v>
+      </c>
+      <c r="F1281" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1281" s="34">
+        <v>11</v>
+      </c>
+      <c r="H1281" s="34" t="s">
+        <v>2177</v>
+      </c>
+      <c r="I1281" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1282" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1282" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1282" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1282" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1282" s="32" t="s">
+        <v>2153</v>
+      </c>
+      <c r="F1282" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1282" s="34">
+        <v>8</v>
+      </c>
+      <c r="H1282" s="34" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I1282" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1283" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1283" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1283" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1283" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1283" s="32" t="s">
+        <v>2154</v>
+      </c>
+      <c r="F1283" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1283" s="34">
+        <v>10</v>
+      </c>
+      <c r="H1283" s="34" t="s">
+        <v>2179</v>
+      </c>
+      <c r="I1283" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1284" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1284" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1284" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1284" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1284" s="32" t="s">
+        <v>2155</v>
+      </c>
+      <c r="F1284" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1284" s="34">
+        <v>10</v>
+      </c>
+      <c r="H1284" s="34" t="s">
+        <v>2180</v>
+      </c>
+      <c r="I1284" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1285" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1285" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1285" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1285" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1285" s="32" t="s">
+        <v>2156</v>
+      </c>
+      <c r="F1285" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1285" s="34">
+        <v>7</v>
+      </c>
+      <c r="H1285" s="34" t="s">
+        <v>2181</v>
+      </c>
+      <c r="I1285" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1286" s="32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1286" s="33">
+        <v>46129</v>
+      </c>
+      <c r="C1286" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1286" s="56">
+        <v>46182</v>
+      </c>
+      <c r="E1286" s="32" t="s">
+        <v>2157</v>
+      </c>
+      <c r="F1286" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1286" s="34">
+        <v>9</v>
+      </c>
+      <c r="H1286" s="34" t="s">
+        <v>2182</v>
+      </c>
+      <c r="I1286" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1287" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="B1287" s="33">
+        <v>46119</v>
+      </c>
+      <c r="C1287" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1287" s="56">
+        <v>46179</v>
+      </c>
+      <c r="E1287" s="32" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F1287" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1287" s="34">
+        <v>98</v>
+      </c>
+      <c r="H1287" s="34" t="s">
+        <v>2183</v>
+      </c>
+      <c r="I1287" s="26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1288" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="B1288" s="33">
+        <v>46119</v>
+      </c>
+      <c r="C1288" s="33">
+        <v>46132</v>
+      </c>
+      <c r="D1288" s="56">
+        <v>46179</v>
+      </c>
+      <c r="E1288" s="32" t="s">
+        <v>2159</v>
+      </c>
+      <c r="F1288" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1288" s="34">
+        <v>74</v>
+      </c>
+      <c r="H1288" s="34" t="s">
+        <v>2184</v>
+      </c>
+      <c r="I1288" s="26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1289" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1289" s="36">
+        <v>46133</v>
+      </c>
+      <c r="C1289" s="36">
+        <v>46133</v>
+      </c>
+      <c r="D1289" s="36">
+        <v>46206</v>
+      </c>
+      <c r="E1289" s="37" t="s">
+        <v>459</v>
+      </c>
+      <c r="F1289" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1289" s="43">
+        <v>2</v>
+      </c>
+      <c r="H1289" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="I1289" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1290" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1290" s="36">
+        <v>46133</v>
+      </c>
+      <c r="C1290" s="36">
+        <v>46133</v>
+      </c>
+      <c r="D1290" s="36">
+        <v>46195</v>
+      </c>
+      <c r="E1290" s="37" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F1290" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1290" s="43">
+        <v>1</v>
+      </c>
+      <c r="H1290" s="34" t="s">
+        <v>1939</v>
+      </c>
+      <c r="I1290" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1291" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1291" s="36">
+        <v>45992</v>
+      </c>
+      <c r="C1291" s="36">
+        <v>46133</v>
+      </c>
+      <c r="D1291" s="36">
+        <v>46055</v>
+      </c>
+      <c r="E1291" s="37" t="s">
+        <v>2187</v>
+      </c>
+      <c r="F1291" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1291" s="43">
+        <v>100</v>
+      </c>
+      <c r="H1291" s="34" t="s">
+        <v>2188</v>
+      </c>
+      <c r="I1291" s="26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1292" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1292" s="36">
+        <v>46118</v>
+      </c>
+      <c r="C1292" s="36">
+        <v>46134</v>
+      </c>
+      <c r="D1292" s="36">
+        <v>46203</v>
+      </c>
+      <c r="E1292" s="37" t="s">
+        <v>2189</v>
+      </c>
+      <c r="F1292" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1292" s="43">
+        <v>174</v>
+      </c>
+      <c r="H1292" s="34" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1292" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1293" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1293" s="36">
+        <v>46128</v>
+      </c>
+      <c r="C1293" s="36">
+        <v>46134</v>
+      </c>
+      <c r="D1293" s="36">
+        <v>46024</v>
+      </c>
+      <c r="E1293" s="37" t="s">
+        <v>2191</v>
+      </c>
+      <c r="F1293" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1293" s="43">
+        <v>5</v>
+      </c>
+      <c r="H1293" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1293" s="26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1294" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1294" s="36">
+        <v>46128</v>
+      </c>
+      <c r="C1294" s="36">
+        <v>46134</v>
+      </c>
+      <c r="D1294" s="36">
+        <v>46024</v>
+      </c>
+      <c r="E1294" s="37" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1294" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1294" s="43">
+        <v>2</v>
+      </c>
+      <c r="H1294" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1294" s="26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1295" s="35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1295" s="36">
+        <v>46134</v>
+      </c>
+      <c r="C1295" s="36">
+        <v>46134</v>
+      </c>
+      <c r="D1295" s="36">
+        <v>46128</v>
+      </c>
+      <c r="E1295" s="37" t="s">
+        <v>2192</v>
+      </c>
+      <c r="F1295" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1295" s="43">
+        <v>80</v>
+      </c>
+      <c r="H1295" s="34" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I1295" s="26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1296" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1296" s="36">
+        <v>46134</v>
+      </c>
+      <c r="C1296" s="36">
+        <v>46134</v>
+      </c>
+      <c r="D1296" s="36">
+        <v>46194</v>
+      </c>
+      <c r="E1296" s="37" t="s">
+        <v>2194</v>
+      </c>
+      <c r="F1296" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1296" s="43">
+        <v>44</v>
+      </c>
+      <c r="H1296" s="34" t="s">
+        <v>2195</v>
+      </c>
+      <c r="I1296" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1297" s="39" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1297" s="40">
+        <v>46134</v>
+      </c>
+      <c r="C1297" s="40">
+        <v>46134</v>
+      </c>
+      <c r="D1297" s="40">
+        <v>46197</v>
+      </c>
+      <c r="E1297" s="41" t="s">
+        <v>2196</v>
+      </c>
+      <c r="F1297" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1297" s="44">
+        <v>80</v>
+      </c>
+      <c r="H1297" s="34" t="s">
+        <v>2197</v>
+      </c>
+      <c r="I1297" s="26" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -44898,7 +46189,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I1259</xm:sqref>
+          <xm:sqref>I3:I1297</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -45019,7 +46310,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="98.5" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
-        <v>2122</v>
+        <v>2186</v>
       </c>
       <c r="E1"/>
     </row>
@@ -45434,13 +46725,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC527349-10F9-4003-A144-4F96EF960A74}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95E01B57-D614-41BC-AE62-43D662FDD3AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8C7D1B5-9CBD-4D1A-A65C-B4545EBF8D5B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{517D6B8D-76BB-4ABE-A172-2873058A1C99}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B445B74-3ADA-4904-AE59-5EFF2F39AABB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AF106E1-114F-455F-BA9F-DE4AE8673A1D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Program Support\WARN\CalJOBS WARN Reports\WARN CALJOBS REPORTS - DAILY\SFY26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{192DC7D3-6F64-4C2E-9447-F5F0BDCA9B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE8E07C-F74A-48D0-986A-5F8DE775272D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" firstSheet="2" activeTab="2" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7656" uniqueCount="2584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7671" uniqueCount="2590">
   <si>
     <t>This worksheet contains 5 sheets. The introductory page, WARN Report Summary, Detailed WARN Report, Call Center Relocations Summary, and Call Center Relocations Report. The second sheet provides an overview of the report according to layoff/closure/relocation types and related quantitative data. The third sheet displays a detailed summary report of affected companies by county. The fourth sheet provides an overview of the report specificially for call center relocations. The fifth sheet displays a detailed summary report of affected companies by county. This Daily WARN Report is updated every Tuesday and Thursday. Hyperlinks to the other 4 sheets can be found below in cell A3-A6.</t>
   </si>
@@ -123,7 +123,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/25 to 06/10/2026</t>
+      <t>07/01/25 to 06/15/2026</t>
     </r>
     <r>
       <rPr>
@@ -143,7 +143,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1519.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1522.</t>
     </r>
   </si>
   <si>
@@ -7871,6 +7871,24 @@
   </si>
   <si>
     <t>300 Mission Street, 20th Floor  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>Hy-Tek Intralogistics</t>
+  </si>
+  <si>
+    <t>11500 Phelan Road  Hesperia CA 92344</t>
+  </si>
+  <si>
+    <t>Leggett &amp; Platt</t>
+  </si>
+  <si>
+    <t>1671 S. Champagne Avenue  Ontario CA 91761</t>
+  </si>
+  <si>
+    <t>Uber Technologies, Inc.</t>
+  </si>
+  <si>
+    <t>1655 3rd Street  San Francisco CA 94158</t>
   </si>
   <si>
     <r>
@@ -7916,7 +7934,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 06/10/2026
+01/01/2023 - 06/15/2026
 </t>
     </r>
     <r>
@@ -8279,7 +8297,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8421,6 +8439,18 @@
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -9214,7 +9244,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1519" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1522" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="25"/>
     <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="24"/>
@@ -9558,12 +9588,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D341DFFF-02D2-4572-95F5-BB3221952133}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="73.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="74" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="130.5">
+    <row r="1" spans="1:1" ht="135">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -9607,13 +9637,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832896D-8AFB-4FFC-957E-910308F3BC0C}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" style="3" customWidth="1"/>
     <col min="2" max="2" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="76.5">
+    <row r="1" spans="1:2" ht="78.75">
       <c r="A1" s="10" t="s">
         <v>6</v>
       </c>
@@ -9632,7 +9662,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>78238</v>
+        <v>78566</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9641,7 +9671,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9668,7 +9698,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9700,18 +9730,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I1519"/>
-  <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="14.45"/>
+  <dimension ref="A1:I1522"/>
+  <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="66.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" style="3" customWidth="1"/>
     <col min="7" max="7" width="9.85546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="54.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="47.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="55.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.5703125" customWidth="1"/>
     <col min="11" max="11" width="13.140625" customWidth="1"/>
     <col min="12" max="12" width="12.7109375" customWidth="1"/>
@@ -9719,13 +9749,13 @@
     <col min="14" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="99.95">
+    <row r="1" spans="1:9" ht="102">
       <c r="A1" s="16" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" ht="24">
+    <row r="2" spans="1:9" ht="24.75">
       <c r="A2" s="26" t="s">
         <v>17</v>
       </c>
@@ -13640,7 +13670,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" ht="22.5">
       <c r="A137" s="28" t="s">
         <v>31</v>
       </c>
@@ -30402,7 +30432,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="715" spans="1:9" ht="20.100000000000001">
+    <row r="715" spans="1:9" ht="22.5">
       <c r="A715" s="28" t="s">
         <v>31</v>
       </c>
@@ -47483,7 +47513,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="1304" spans="1:9" ht="20.100000000000001">
+    <row r="1304" spans="1:9" ht="22.5">
       <c r="A1304" s="28" t="s">
         <v>52</v>
       </c>
@@ -47512,7 +47542,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="1305" spans="1:9" ht="20.100000000000001">
+    <row r="1305" spans="1:9" ht="22.5">
       <c r="A1305" s="28" t="s">
         <v>52</v>
       </c>
@@ -47541,7 +47571,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="1306" spans="1:9" ht="20.100000000000001">
+    <row r="1306" spans="1:9" ht="22.5">
       <c r="A1306" s="28" t="s">
         <v>52</v>
       </c>
@@ -53745,6 +53775,93 @@
       </c>
       <c r="I1519" s="31" t="s">
         <v>347</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:9">
+      <c r="A1520" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1520" s="51">
+        <v>46184</v>
+      </c>
+      <c r="C1520" s="51">
+        <v>46184</v>
+      </c>
+      <c r="D1520" s="51">
+        <v>46244</v>
+      </c>
+      <c r="E1520" s="50" t="s">
+        <v>2578</v>
+      </c>
+      <c r="F1520" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1520" s="52">
+        <v>200</v>
+      </c>
+      <c r="H1520" s="52" t="s">
+        <v>2579</v>
+      </c>
+      <c r="I1520" s="53" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:9">
+      <c r="A1521" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1521" s="51">
+        <v>46188</v>
+      </c>
+      <c r="C1521" s="51">
+        <v>46188</v>
+      </c>
+      <c r="D1521" s="51">
+        <v>46248</v>
+      </c>
+      <c r="E1521" s="50" t="s">
+        <v>2580</v>
+      </c>
+      <c r="F1521" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1521" s="52">
+        <v>125</v>
+      </c>
+      <c r="H1521" s="52" t="s">
+        <v>2581</v>
+      </c>
+      <c r="I1521" s="53" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:9">
+      <c r="A1522" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1522" s="51">
+        <v>46185</v>
+      </c>
+      <c r="C1522" s="51">
+        <v>46188</v>
+      </c>
+      <c r="D1522" s="51">
+        <v>46245</v>
+      </c>
+      <c r="E1522" s="50" t="s">
+        <v>2582</v>
+      </c>
+      <c r="F1522" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1522" s="52">
+        <v>3</v>
+      </c>
+      <c r="H1522" s="52" t="s">
+        <v>2583</v>
+      </c>
+      <c r="I1522" s="53" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -53761,7 +53878,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I1519</xm:sqref>
+          <xm:sqref>I3:I1522</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -53772,15 +53889,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC03875-3DF4-4258-8762-7FFE2A7D620D}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" style="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="95.1">
+    <row r="1" spans="1:2" ht="97.5">
       <c r="A1" s="1" t="s">
-        <v>2578</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -53868,25 +53985,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE76718-798E-45ED-8CA1-01AA760CE5F1}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="98.45">
+    <row r="1" spans="1:8" ht="99.75">
       <c r="A1" s="25" t="s">
-        <v>2579</v>
+        <v>2585</v>
       </c>
       <c r="E1"/>
     </row>
-    <row r="2" spans="1:8" ht="24">
+    <row r="2" spans="1:8" ht="24.75">
       <c r="A2" s="19" t="s">
         <v>17</v>
       </c>
@@ -53926,7 +54043,7 @@
         <v>45047</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>2580</v>
+        <v>2586</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>54</v>
@@ -53949,7 +54066,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E81B0C9-EE0D-4672-99B4-ACA7D2D31E92}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="67.28515625" bestFit="1" customWidth="1"/>
   </cols>
@@ -53966,7 +54083,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>2581</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -54056,12 +54173,12 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>2582</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>2583</v>
+        <v>2589</v>
       </c>
     </row>
   </sheetData>
@@ -54070,17 +54187,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82b749e3-8208-459a-bfc0-9b428d09cbab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -54089,7 +54195,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E614ED5C53901F4C88FF6AEBBF3D8E0D" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="529ed3825ab478a5ffdc44eb265dc6f5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="82b749e3-8208-459a-bfc0-9b428d09cbab" xmlns:ns3="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7c2030912f9588e16c624efbe24e62a" ns2:_="" ns3:_="">
     <xsd:import namespace="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
@@ -54296,16 +54402,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="82b749e3-8208-459a-bfc0-9b428d09cbab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{003C8481-1A20-4EFB-B5FE-803A2EDAB8F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E685C52-A6E2-47A3-B296-630123D79679}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5EB3E32-C54D-49D1-86F5-AD55C5FB43B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92D1B9B6-2C55-4A38-8AC5-6016FD477CCF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9EC50D9-E8AD-45D0-AAAA-B1B0DE75EBF3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58D11D8A-B943-4ACE-951B-4E94023D0688}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Program Support\WARN\CalJOBS WARN Reports\WARN CALJOBS REPORTS - DAILY\SFY26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BVang\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE8E07C-F74A-48D0-986A-5F8DE775272D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5382F7B-CBBE-43C4-A2F8-28AB376F12B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" firstSheet="2" activeTab="2" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" firstSheet="2" activeTab="2" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7671" uniqueCount="2590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7681" uniqueCount="2593">
   <si>
     <t>This worksheet contains 5 sheets. The introductory page, WARN Report Summary, Detailed WARN Report, Call Center Relocations Summary, and Call Center Relocations Report. The second sheet provides an overview of the report according to layoff/closure/relocation types and related quantitative data. The third sheet displays a detailed summary report of affected companies by county. The fourth sheet provides an overview of the report specificially for call center relocations. The fifth sheet displays a detailed summary report of affected companies by county. This Daily WARN Report is updated every Tuesday and Thursday. Hyperlinks to the other 4 sheets can be found below in cell A3-A6.</t>
   </si>
@@ -123,7 +123,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/25 to 06/15/2026</t>
+      <t>07/01/25 to 06/17/2026</t>
     </r>
     <r>
       <rPr>
@@ -143,7 +143,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1522.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I1524.</t>
     </r>
   </si>
   <si>
@@ -7889,6 +7889,15 @@
   </si>
   <si>
     <t>1655 3rd Street  San Francisco CA 94158</t>
+  </si>
+  <si>
+    <t>United Natural Foods West</t>
+  </si>
+  <si>
+    <t>5300 Sheila St.  Los Angeles CA 90040</t>
+  </si>
+  <si>
+    <t>370 W. Trimble Rd  San Jose CA 95131</t>
   </si>
   <si>
     <r>
@@ -7934,7 +7943,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 06/15/2026
+01/01/2023 - 06/17/2026
 </t>
     </r>
     <r>
@@ -8297,7 +8306,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8439,18 +8448,6 @@
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -9244,7 +9241,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1522" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I1524" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="25"/>
     <tableColumn id="2" xr3:uid="{058DED91-D77E-48B6-A71D-06D4A25AA391}" name="Notice_x000a_Date" dataDxfId="24"/>
@@ -9662,7 +9659,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>78566</v>
+        <v>78588</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9698,7 +9695,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9730,7 +9727,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I1522"/>
+  <dimension ref="A1:I1524"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -53778,90 +53775,148 @@
       </c>
     </row>
     <row r="1520" spans="1:9">
-      <c r="A1520" s="50" t="s">
+      <c r="A1520" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B1520" s="51">
+      <c r="B1520" s="29">
         <v>46184</v>
       </c>
-      <c r="C1520" s="51">
+      <c r="C1520" s="29">
         <v>46184</v>
       </c>
-      <c r="D1520" s="51">
+      <c r="D1520" s="29">
         <v>46244</v>
       </c>
-      <c r="E1520" s="50" t="s">
+      <c r="E1520" s="28" t="s">
         <v>2578</v>
       </c>
-      <c r="F1520" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1520" s="52">
+      <c r="F1520" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1520" s="30">
         <v>200</v>
       </c>
-      <c r="H1520" s="52" t="s">
+      <c r="H1520" s="30" t="s">
         <v>2579</v>
       </c>
-      <c r="I1520" s="53" t="s">
+      <c r="I1520" s="31" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="1521" spans="1:9">
-      <c r="A1521" s="50" t="s">
+      <c r="A1521" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="B1521" s="51">
+      <c r="B1521" s="29">
         <v>46188</v>
       </c>
-      <c r="C1521" s="51">
+      <c r="C1521" s="29">
         <v>46188</v>
       </c>
-      <c r="D1521" s="51">
+      <c r="D1521" s="29">
         <v>46248</v>
       </c>
-      <c r="E1521" s="50" t="s">
+      <c r="E1521" s="28" t="s">
         <v>2580</v>
       </c>
-      <c r="F1521" s="50" t="s">
+      <c r="F1521" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="G1521" s="52">
+      <c r="G1521" s="30">
         <v>125</v>
       </c>
-      <c r="H1521" s="52" t="s">
+      <c r="H1521" s="30" t="s">
         <v>2581</v>
       </c>
-      <c r="I1521" s="53" t="s">
+      <c r="I1521" s="31" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="1522" spans="1:9">
-      <c r="A1522" s="50" t="s">
+      <c r="A1522" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="B1522" s="51">
+      <c r="B1522" s="29">
         <v>46185</v>
       </c>
-      <c r="C1522" s="51">
+      <c r="C1522" s="29">
         <v>46188</v>
       </c>
-      <c r="D1522" s="51">
+      <c r="D1522" s="29">
         <v>46245</v>
       </c>
-      <c r="E1522" s="50" t="s">
+      <c r="E1522" s="28" t="s">
         <v>2582</v>
       </c>
-      <c r="F1522" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1522" s="52">
+      <c r="F1522" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1522" s="30">
         <v>3</v>
       </c>
-      <c r="H1522" s="52" t="s">
+      <c r="H1522" s="30" t="s">
         <v>2583</v>
       </c>
-      <c r="I1522" s="53" t="s">
+      <c r="I1522" s="31" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:9">
+      <c r="A1523" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1523" s="29">
+        <v>46188</v>
+      </c>
+      <c r="C1523" s="29">
+        <v>46189</v>
+      </c>
+      <c r="D1523" s="29">
+        <v>46251</v>
+      </c>
+      <c r="E1523" s="28" t="s">
+        <v>2584</v>
+      </c>
+      <c r="F1523" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1523" s="30">
+        <v>11</v>
+      </c>
+      <c r="H1523" s="30" t="s">
+        <v>2585</v>
+      </c>
+      <c r="I1523" s="31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:9">
+      <c r="A1524" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1524" s="29">
+        <v>46190</v>
+      </c>
+      <c r="C1524" s="29">
+        <v>46190</v>
+      </c>
+      <c r="D1524" s="29">
+        <v>46265</v>
+      </c>
+      <c r="E1524" s="28" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F1524" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1524" s="30">
+        <v>11</v>
+      </c>
+      <c r="H1524" s="30" t="s">
+        <v>2586</v>
+      </c>
+      <c r="I1524" s="31" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -53878,7 +53933,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I1522</xm:sqref>
+          <xm:sqref>I3:I1524</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -53897,7 +53952,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="97.5">
       <c r="A1" s="1" t="s">
-        <v>2584</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -53999,7 +54054,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75">
       <c r="A1" s="25" t="s">
-        <v>2585</v>
+        <v>2588</v>
       </c>
       <c r="E1"/>
     </row>
@@ -54043,7 +54098,7 @@
         <v>45047</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>2586</v>
+        <v>2589</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>54</v>
@@ -54083,7 +54138,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>2587</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -54173,12 +54228,12 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>2588</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>2589</v>
+        <v>2592</v>
       </c>
     </row>
   </sheetData>
@@ -54187,15 +54242,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E614ED5C53901F4C88FF6AEBBF3D8E0D" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="529ed3825ab478a5ffdc44eb265dc6f5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="82b749e3-8208-459a-bfc0-9b428d09cbab" xmlns:ns3="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7c2030912f9588e16c624efbe24e62a" ns2:_="" ns3:_="">
     <xsd:import namespace="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
@@ -54402,7 +54448,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2" xsi:nil="true"/>
@@ -54413,16 +54459,25 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E685C52-A6E2-47A3-B296-630123D79679}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57606180-B290-4ABA-95DB-19B081E26D01}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92D1B9B6-2C55-4A38-8AC5-6016FD477CCF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99C1337E-595A-474A-AE35-DA5661CA1AC0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58D11D8A-B943-4ACE-951B-4E94023D0688}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59366606-B8DE-4F23-8874-6EA9BB5ACFD1}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6862B30-D57A-48DD-BDE1-508F78C76CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32F71B92-82E3-486B-B364-698CC8FFC060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="115">
   <si>
     <t>County/Parish</t>
   </si>
@@ -341,6 +341,66 @@
     <t>17110 South Main Street  Carson CA 90248</t>
   </si>
   <si>
+    <t>701A Sally Pl  Fullerton CA 92831</t>
+  </si>
+  <si>
+    <t>Obsidian</t>
+  </si>
+  <si>
+    <t>100 Spectrum Center Dr.  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>LeeMAH Electronics</t>
+  </si>
+  <si>
+    <t>155 South Hill Drive  Brisbane CA 94005</t>
+  </si>
+  <si>
+    <t>Alameda County</t>
+  </si>
+  <si>
+    <t>Xpress Delivery LLC (DSJ9)</t>
+  </si>
+  <si>
+    <t>5800 Coliseum Way  Oakland CA 94621</t>
+  </si>
+  <si>
+    <t>San Francisco County</t>
+  </si>
+  <si>
+    <t>OnPoint Logistics LLC</t>
+  </si>
+  <si>
+    <t>749 Toland Street  San Francisco CA 94124</t>
+  </si>
+  <si>
+    <t>Butte County</t>
+  </si>
+  <si>
+    <t>6th Street Center for Youth (Youth for Change)</t>
+  </si>
+  <si>
+    <t>130 W. 6th Street  Chico CA 95928</t>
+  </si>
+  <si>
+    <t>Sentinel Restaurant &amp; Hospitality Group LLC</t>
+  </si>
+  <si>
+    <t>627 Sleepy Hollow Ln  Laguna Beach CA 92651</t>
+  </si>
+  <si>
+    <t>The Vons Companies Inc.</t>
+  </si>
+  <si>
+    <t>845 E. California St.  Pasadena CA 91106</t>
+  </si>
+  <si>
+    <t>GEODIS</t>
+  </si>
+  <si>
+    <t>1950 Palmetto Ave.  Redlands CA 92374</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -360,7 +420,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 07/08/2026
+01/01/2023 - 07/15/2026
 </t>
     </r>
     <r>
@@ -374,19 +434,70 @@
     </r>
   </si>
   <si>
-    <t>701A Sally Pl  Fullerton CA 92831</t>
-  </si>
-  <si>
-    <t>Obsidian</t>
-  </si>
-  <si>
-    <t>100 Spectrum Center Dr.  Irvine CA 92618</t>
-  </si>
-  <si>
-    <t>LeeMAH Electronics</t>
-  </si>
-  <si>
-    <t>155 South Hill Drive  Brisbane CA 94005</t>
+    <t>Conduent</t>
+  </si>
+  <si>
+    <t>11165 Knott Avenue, Suite D  Cypress CA 90630</t>
+  </si>
+  <si>
+    <t>GMRI, Inc. dba Yard House</t>
+  </si>
+  <si>
+    <t>1875 Newport Blvd., A219  Costa Mesa CA 92627</t>
+  </si>
+  <si>
+    <t>GXO Logistics Worldwide, LLC</t>
+  </si>
+  <si>
+    <t>7010 Cajon Blvd.  San Bernardino CA 92407</t>
+  </si>
+  <si>
+    <t>Udemy, Inc.</t>
+  </si>
+  <si>
+    <t>600 Harrison Street, 3rd Floor  San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>Yolo County</t>
+  </si>
+  <si>
+    <t>AWCS, LLC (Cottonwood Post-Acute Rehab</t>
+  </si>
+  <si>
+    <t>Closure Temporary</t>
+  </si>
+  <si>
+    <t>625 Cottonwood St.  Woodland CA 95695</t>
+  </si>
+  <si>
+    <t>Santa Clara County</t>
+  </si>
+  <si>
+    <t>Coursera, Inc.</t>
+  </si>
+  <si>
+    <t>2440West El Camino Real, Suite 500  Mountain View CA 94040</t>
+  </si>
+  <si>
+    <t>ELC Beauty LLC (Too Faced Cosmetics, LLC)</t>
+  </si>
+  <si>
+    <t>18231 W. McDurmott #100  Irvine CA 92614</t>
+  </si>
+  <si>
+    <t>Eargo, Inc.</t>
+  </si>
+  <si>
+    <t>2665 North First Street, Suite 3000  San Jose CA 95134</t>
+  </si>
+  <si>
+    <t>Santa Barbara County</t>
+  </si>
+  <si>
+    <t>Red Lobster Restaurants LLC</t>
+  </si>
+  <si>
+    <t>1525 S. Bradley Road  Santa Maria CA 93454</t>
   </si>
   <si>
     <r>
@@ -400,7 +511,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 07/08/2026</t>
+      <t>07/01/26 to 07/15/2026</t>
     </r>
     <r>
       <rPr>
@@ -420,7 +531,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I11.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I26.</t>
     </r>
   </si>
 </sst>
@@ -652,7 +763,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -741,6 +852,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1533,10 +1647,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I11" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I11" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I11">
-    <sortCondition ref="C2:C11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I26" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I26" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I26">
+    <sortCondition ref="C2:C26"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
@@ -1933,7 +2047,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
@@ -1955,7 +2069,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>655</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1964,7 +2078,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1991,7 +2105,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2000,7 +2114,7 @@
       </c>
       <c r="B8" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2023,17 +2137,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.5703125" customWidth="1"/>
     <col min="11" max="11" width="13.140625" customWidth="1"/>
@@ -2044,7 +2158,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -2245,7 +2359,7 @@
         <v>33</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I8" s="31" t="s">
         <v>37</v>
@@ -2265,7 +2379,7 @@
         <v>46269</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" s="28" t="s">
         <v>6</v>
@@ -2274,7 +2388,7 @@
         <v>52</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I9" s="31" t="s">
         <v>46</v>
@@ -2306,7 +2420,7 @@
         <v>61</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -2323,7 +2437,7 @@
         <v>46273</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F11" s="28" t="s">
         <v>52</v>
@@ -2332,10 +2446,445 @@
         <v>212</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="29">
+        <v>46212</v>
+      </c>
+      <c r="C12" s="29">
+        <v>46212</v>
+      </c>
+      <c r="D12" s="29">
+        <v>46274</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="30">
+        <v>80</v>
+      </c>
+      <c r="H12" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="29">
+        <v>46212</v>
+      </c>
+      <c r="C13" s="29">
+        <v>46212</v>
+      </c>
+      <c r="D13" s="29">
+        <v>46272</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="30">
+        <v>96</v>
+      </c>
+      <c r="H13" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="29">
+        <v>46213</v>
+      </c>
+      <c r="C14" s="29">
+        <v>46213</v>
+      </c>
+      <c r="D14" s="29">
+        <v>46265</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="30">
+        <v>6</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="29">
+        <v>46211</v>
+      </c>
+      <c r="C15" s="29">
+        <v>46213</v>
+      </c>
+      <c r="D15" s="29">
+        <v>46273</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="30">
+        <v>113</v>
+      </c>
+      <c r="H15" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="29">
+        <v>46210</v>
+      </c>
+      <c r="C16" s="29">
+        <v>46216</v>
+      </c>
+      <c r="D16" s="29">
+        <v>46270</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="30">
+        <v>55</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="29">
+        <v>46209</v>
+      </c>
+      <c r="C17" s="29">
+        <v>46216</v>
+      </c>
+      <c r="D17" s="29">
+        <v>46268</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="30">
+        <v>81</v>
+      </c>
+      <c r="H17" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="29">
+        <v>46199</v>
+      </c>
+      <c r="C18" s="29">
+        <v>46217</v>
+      </c>
+      <c r="D18" s="29">
+        <v>46262</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="30">
+        <v>51</v>
+      </c>
+      <c r="H18" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="29">
+        <v>46217</v>
+      </c>
+      <c r="C19" s="29">
+        <v>46217</v>
+      </c>
+      <c r="D19" s="29">
+        <v>46279</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="30">
+        <v>78</v>
+      </c>
+      <c r="H19" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="29">
+        <v>46213</v>
+      </c>
+      <c r="C20" s="29">
+        <v>46217</v>
+      </c>
+      <c r="D20" s="29">
+        <v>46283</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="30">
+        <v>46</v>
+      </c>
+      <c r="H20" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="29">
+        <v>46217</v>
+      </c>
+      <c r="C21" s="29">
+        <v>46217</v>
+      </c>
+      <c r="D21" s="29">
+        <v>46276</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="30">
+        <v>28</v>
+      </c>
+      <c r="H21" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" s="29">
+        <v>46216</v>
+      </c>
+      <c r="C22" s="29">
+        <v>46217</v>
+      </c>
+      <c r="D22" s="29">
+        <v>46276</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" s="30">
+        <v>158</v>
+      </c>
+      <c r="H22" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="29">
+        <v>46217</v>
+      </c>
+      <c r="C23" s="29">
+        <v>46218</v>
+      </c>
+      <c r="D23" s="29">
+        <v>46276</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="30">
+        <v>31</v>
+      </c>
+      <c r="H23" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="29">
+        <v>46217</v>
+      </c>
+      <c r="C24" s="29">
+        <v>46218</v>
+      </c>
+      <c r="D24" s="29">
+        <v>46295</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="30">
+        <v>67</v>
+      </c>
+      <c r="H24" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" s="29">
+        <v>46218</v>
+      </c>
+      <c r="C25" s="29">
+        <v>46218</v>
+      </c>
+      <c r="D25" s="29">
+        <v>46279</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="30">
+        <v>57</v>
+      </c>
+      <c r="H25" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="29">
+        <v>46217</v>
+      </c>
+      <c r="C26" s="29">
+        <v>46218</v>
+      </c>
+      <c r="D26" s="29">
+        <v>46265</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="30">
+        <v>37</v>
+      </c>
+      <c r="H26" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2352,7 +2901,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I11</xm:sqref>
+          <xm:sqref>I3:I26</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2473,7 +3022,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E1"/>
     </row>
@@ -2888,7 +3437,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE592D66-A02C-451B-92F2-AFC8E561A735}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B74C2D5-B8D0-4DDC-8CA0-BA34BD3D1EA6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -2907,7 +3456,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{239E1C96-ADA7-4401-B3C8-A8B3B6BD6E19}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4447E3A-2998-4D26-907D-DE9FB5C743F8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -2915,18 +3464,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3D8ADE4-7F9C-4242-939C-3936AF4A45C3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D1B8318-8F13-4FC9-BB78-6A486FF75F89}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32F71B92-82E3-486B-B364-698CC8FFC060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89117950-55BE-4A5D-A858-5D006DBD2A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="143">
   <si>
     <t>County/Parish</t>
   </si>
@@ -401,6 +401,72 @@
     <t>1950 Palmetto Ave.  Redlands CA 92374</t>
   </si>
   <si>
+    <t>Conduent</t>
+  </si>
+  <si>
+    <t>11165 Knott Avenue, Suite D  Cypress CA 90630</t>
+  </si>
+  <si>
+    <t>GMRI, Inc. dba Yard House</t>
+  </si>
+  <si>
+    <t>1875 Newport Blvd., A219  Costa Mesa CA 92627</t>
+  </si>
+  <si>
+    <t>GXO Logistics Worldwide, LLC</t>
+  </si>
+  <si>
+    <t>7010 Cajon Blvd.  San Bernardino CA 92407</t>
+  </si>
+  <si>
+    <t>Udemy, Inc.</t>
+  </si>
+  <si>
+    <t>600 Harrison Street, 3rd Floor  San Francisco CA 94107</t>
+  </si>
+  <si>
+    <t>Yolo County</t>
+  </si>
+  <si>
+    <t>AWCS, LLC (Cottonwood Post-Acute Rehab</t>
+  </si>
+  <si>
+    <t>Closure Temporary</t>
+  </si>
+  <si>
+    <t>625 Cottonwood St.  Woodland CA 95695</t>
+  </si>
+  <si>
+    <t>Santa Clara County</t>
+  </si>
+  <si>
+    <t>Coursera, Inc.</t>
+  </si>
+  <si>
+    <t>2440West El Camino Real, Suite 500  Mountain View CA 94040</t>
+  </si>
+  <si>
+    <t>ELC Beauty LLC (Too Faced Cosmetics, LLC)</t>
+  </si>
+  <si>
+    <t>18231 W. McDurmott #100  Irvine CA 92614</t>
+  </si>
+  <si>
+    <t>Eargo, Inc.</t>
+  </si>
+  <si>
+    <t>2665 North First Street, Suite 3000  San Jose CA 95134</t>
+  </si>
+  <si>
+    <t>Santa Barbara County</t>
+  </si>
+  <si>
+    <t>Red Lobster Restaurants LLC</t>
+  </si>
+  <si>
+    <t>1525 S. Bradley Road  Santa Maria CA 93454</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -420,7 +486,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 07/15/2026
+01/01/2023 - 07/20/2026
 </t>
     </r>
     <r>
@@ -434,70 +500,88 @@
     </r>
   </si>
   <si>
-    <t>Conduent</t>
-  </si>
-  <si>
-    <t>11165 Knott Avenue, Suite D  Cypress CA 90630</t>
-  </si>
-  <si>
-    <t>GMRI, Inc. dba Yard House</t>
-  </si>
-  <si>
-    <t>1875 Newport Blvd., A219  Costa Mesa CA 92627</t>
-  </si>
-  <si>
-    <t>GXO Logistics Worldwide, LLC</t>
-  </si>
-  <si>
-    <t>7010 Cajon Blvd.  San Bernardino CA 92407</t>
-  </si>
-  <si>
-    <t>Udemy, Inc.</t>
-  </si>
-  <si>
-    <t>600 Harrison Street, 3rd Floor  San Francisco CA 94107</t>
-  </si>
-  <si>
-    <t>Yolo County</t>
-  </si>
-  <si>
-    <t>AWCS, LLC (Cottonwood Post-Acute Rehab</t>
-  </si>
-  <si>
-    <t>Closure Temporary</t>
-  </si>
-  <si>
-    <t>625 Cottonwood St.  Woodland CA 95695</t>
-  </si>
-  <si>
-    <t>Santa Clara County</t>
-  </si>
-  <si>
-    <t>Coursera, Inc.</t>
-  </si>
-  <si>
-    <t>2440West El Camino Real, Suite 500  Mountain View CA 94040</t>
-  </si>
-  <si>
-    <t>ELC Beauty LLC (Too Faced Cosmetics, LLC)</t>
-  </si>
-  <si>
-    <t>18231 W. McDurmott #100  Irvine CA 92614</t>
-  </si>
-  <si>
-    <t>Eargo, Inc.</t>
-  </si>
-  <si>
-    <t>2665 North First Street, Suite 3000  San Jose CA 95134</t>
-  </si>
-  <si>
-    <t>Santa Barbara County</t>
-  </si>
-  <si>
-    <t>Red Lobster Restaurants LLC</t>
-  </si>
-  <si>
-    <t>1525 S. Bradley Road  Santa Maria CA 93454</t>
+    <t>Phillips 66</t>
+  </si>
+  <si>
+    <t>1660 W. Anaheim Street  Wilmington CA 90744</t>
+  </si>
+  <si>
+    <t>NBCUniversal Media, LLC - 1320</t>
+  </si>
+  <si>
+    <t>100 Universal City Plaza, Bldg. 1320  Universal City CA 91608</t>
+  </si>
+  <si>
+    <t>NBCUniversal Media, LLC - 1360</t>
+  </si>
+  <si>
+    <t>100 Universal City Plaza, Bldg. 1360  Universal City CA 91608</t>
+  </si>
+  <si>
+    <t>NBCUniversal Media, LLC -1440</t>
+  </si>
+  <si>
+    <t>100 Universal City Plaza, Bldg. 1440  Universal City CA 91608</t>
+  </si>
+  <si>
+    <t>NBCUniversal Media, LLC - 1460</t>
+  </si>
+  <si>
+    <t>100 Universal City Plaza, Bldg. 1460  Universal City CA 91608</t>
+  </si>
+  <si>
+    <t>Aramark Campus, LLC</t>
+  </si>
+  <si>
+    <t>1259 E Colton Avenue  Redlands CA 92374</t>
+  </si>
+  <si>
+    <t>Monterey Mushrooms, LLC</t>
+  </si>
+  <si>
+    <t>642 Hale Ave.  Morgan Hill CA 95037</t>
+  </si>
+  <si>
+    <t>Tulare County</t>
+  </si>
+  <si>
+    <t>Ventura Coastal</t>
+  </si>
+  <si>
+    <t>Layoff Temporary</t>
+  </si>
+  <si>
+    <t>531 W. Poplar Avenue  Tipton CA 93272</t>
+  </si>
+  <si>
+    <t>Magic Leap, Inc.</t>
+  </si>
+  <si>
+    <t>1376 Bordeaux Dr.  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>Wind &amp; Sea Restaurant</t>
+  </si>
+  <si>
+    <t>34699 Golden Lantern  Dana Point CA 92629</t>
+  </si>
+  <si>
+    <t>Solano County</t>
+  </si>
+  <si>
+    <t>DesigneRX Pharmaceuticals, Inc.</t>
+  </si>
+  <si>
+    <t>4941 Allison Parkway, Suite B  Vacaville CA 95688</t>
+  </si>
+  <si>
+    <t>Sonoma County</t>
+  </si>
+  <si>
+    <t>Queen City Staffing</t>
+  </si>
+  <si>
+    <t>2717 Giffen Avenue  Santa Rosa CA 95407</t>
   </si>
   <si>
     <r>
@@ -511,7 +595,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 07/15/2026</t>
+      <t>07/01/26 to 07/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -531,7 +615,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I26.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I38.</t>
     </r>
   </si>
 </sst>
@@ -1647,8 +1731,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I26" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I26" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I38" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I38" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I26">
     <sortCondition ref="C2:C26"/>
   </sortState>
@@ -2069,7 +2153,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>1639</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2078,7 +2162,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2087,7 +2171,7 @@
       </c>
       <c r="B5" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2105,7 +2189,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2137,7 +2221,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -2158,7 +2242,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -2640,7 +2724,7 @@
         <v>46262</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F18" s="28" t="s">
         <v>6</v>
@@ -2649,7 +2733,7 @@
         <v>51</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I18" s="32" t="s">
         <v>41</v>
@@ -2669,7 +2753,7 @@
         <v>46279</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F19" s="28" t="s">
         <v>52</v>
@@ -2678,7 +2762,7 @@
         <v>78</v>
       </c>
       <c r="H19" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I19" s="32" t="s">
         <v>47</v>
@@ -2698,7 +2782,7 @@
         <v>46283</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F20" s="28" t="s">
         <v>52</v>
@@ -2707,7 +2791,7 @@
         <v>46</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I20" s="32" t="s">
         <v>37</v>
@@ -2727,7 +2811,7 @@
         <v>46276</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F21" s="28" t="s">
         <v>6</v>
@@ -2736,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="H21" s="30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I21" s="32" t="s">
         <v>44</v>
@@ -2744,7 +2828,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B22" s="29">
         <v>46216</v>
@@ -2756,16 +2840,16 @@
         <v>46276</v>
       </c>
       <c r="E22" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="28" t="s">
         <v>101</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>102</v>
       </c>
       <c r="G22" s="30">
         <v>158</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I22" s="32" t="s">
         <v>45</v>
@@ -2773,7 +2857,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B23" s="29">
         <v>46217</v>
@@ -2785,7 +2869,7 @@
         <v>46276</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F23" s="28" t="s">
         <v>6</v>
@@ -2794,7 +2878,7 @@
         <v>31</v>
       </c>
       <c r="H23" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I23" s="32" t="s">
         <v>41</v>
@@ -2814,7 +2898,7 @@
         <v>46295</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F24" s="28" t="s">
         <v>52</v>
@@ -2823,7 +2907,7 @@
         <v>67</v>
       </c>
       <c r="H24" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I24" s="32" t="s">
         <v>36</v>
@@ -2831,7 +2915,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" s="29">
         <v>46218</v>
@@ -2843,7 +2927,7 @@
         <v>46279</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F25" s="28" t="s">
         <v>52</v>
@@ -2852,7 +2936,7 @@
         <v>57</v>
       </c>
       <c r="H25" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I25" s="32" t="s">
         <v>34</v>
@@ -2860,7 +2944,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B26" s="29">
         <v>46217</v>
@@ -2872,7 +2956,7 @@
         <v>46265</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F26" s="28" t="s">
         <v>52</v>
@@ -2881,10 +2965,358 @@
         <v>37</v>
       </c>
       <c r="H26" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I26" s="32" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="29">
+        <v>46219</v>
+      </c>
+      <c r="C27" s="29">
+        <v>46219</v>
+      </c>
+      <c r="D27" s="29">
+        <v>46281</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="30">
+        <v>5</v>
+      </c>
+      <c r="H27" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="29">
+        <v>46220</v>
+      </c>
+      <c r="C28" s="29">
+        <v>46220</v>
+      </c>
+      <c r="D28" s="29">
+        <v>46262</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G28" s="30">
+        <v>3</v>
+      </c>
+      <c r="H28" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="I28" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="29">
+        <v>46220</v>
+      </c>
+      <c r="C29" s="29">
+        <v>46220</v>
+      </c>
+      <c r="D29" s="29">
+        <v>46262</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="30">
+        <v>5</v>
+      </c>
+      <c r="H29" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="29">
+        <v>46220</v>
+      </c>
+      <c r="C30" s="29">
+        <v>46220</v>
+      </c>
+      <c r="D30" s="29">
+        <v>46262</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30" s="30">
+        <v>87</v>
+      </c>
+      <c r="H30" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="I30" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="29">
+        <v>46220</v>
+      </c>
+      <c r="C31" s="29">
+        <v>46220</v>
+      </c>
+      <c r="D31" s="29">
+        <v>46262</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="30">
+        <v>55</v>
+      </c>
+      <c r="H31" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="I31" s="32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="29">
+        <v>46219</v>
+      </c>
+      <c r="C32" s="29">
+        <v>46220</v>
+      </c>
+      <c r="D32" s="29">
+        <v>46234</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="30">
+        <v>94</v>
+      </c>
+      <c r="H32" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="I32" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="29">
+        <v>46220</v>
+      </c>
+      <c r="C33" s="29">
+        <v>46220</v>
+      </c>
+      <c r="D33" s="29">
+        <v>46285</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G33" s="30">
+        <v>253</v>
+      </c>
+      <c r="H33" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="I33" s="32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" s="29">
+        <v>46218</v>
+      </c>
+      <c r="C34" s="29">
+        <v>46220</v>
+      </c>
+      <c r="D34" s="29">
+        <v>46283</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="G34" s="30">
+        <v>71</v>
+      </c>
+      <c r="H34" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="I34" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="29">
+        <v>46220</v>
+      </c>
+      <c r="C35" s="29">
+        <v>46223</v>
+      </c>
+      <c r="D35" s="29">
+        <v>46296</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G35" s="30">
+        <v>76</v>
+      </c>
+      <c r="H35" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="29">
+        <v>46217</v>
+      </c>
+      <c r="C36" s="29">
+        <v>46223</v>
+      </c>
+      <c r="D36" s="29">
+        <v>46280</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="30">
+        <v>198</v>
+      </c>
+      <c r="H36" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="I36" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="B37" s="29">
+        <v>46223</v>
+      </c>
+      <c r="C37" s="29">
+        <v>46223</v>
+      </c>
+      <c r="D37" s="29">
+        <v>46286</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G37" s="30">
+        <v>25</v>
+      </c>
+      <c r="H37" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="I37" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="B38" s="29">
+        <v>46217</v>
+      </c>
+      <c r="C38" s="29">
+        <v>46223</v>
+      </c>
+      <c r="D38" s="29">
+        <v>46278</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="F38" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="30">
+        <v>49</v>
+      </c>
+      <c r="H38" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="I38" s="32" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2901,7 +3333,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I26</xm:sqref>
+          <xm:sqref>I3:I38</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3022,7 +3454,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="E1"/>
     </row>
@@ -3437,7 +3869,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B74C2D5-B8D0-4DDC-8CA0-BA34BD3D1EA6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6272687-601F-424B-A8D8-C079CFA9EA3C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -3456,7 +3888,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4447E3A-2998-4D26-907D-DE9FB5C743F8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{114C4746-C3AE-4E3C-852F-947D928A7F58}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -3464,17 +3896,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D1B8318-8F13-4FC9-BB78-6A486FF75F89}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B66F8A0-9A49-4A75-B4A3-15CE84DBE70A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Program Support\WARN\CalJOBS WARN Reports\WARN CALJOBS REPORTS - DAILY\SFY27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89117950-55BE-4A5D-A858-5D006DBD2A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE40062-A11B-4C19-8D07-8A155D7AC06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" activeTab="2" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="151">
   <si>
     <t>County/Parish</t>
   </si>
@@ -467,39 +467,6 @@
     <t>1525 S. Bradley Road  Santa Maria CA 93454</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>WARN REPORT -</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-01/01/2023 - 07/20/2026
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through H3.</t>
-    </r>
-  </si>
-  <si>
     <t>Phillips 66</t>
   </si>
   <si>
@@ -582,6 +549,30 @@
   </si>
   <si>
     <t>2717 Giffen Avenue  Santa Rosa CA 95407</t>
+  </si>
+  <si>
+    <t>New Leaf Community Markets, Inc.</t>
+  </si>
+  <si>
+    <t>5667 Silver Creek Valley Road  San Jose CA 95138</t>
+  </si>
+  <si>
+    <t>Pixar</t>
+  </si>
+  <si>
+    <t>1200 Park Avenue  Emeryville CA 94608</t>
+  </si>
+  <si>
+    <t>CraftForce Services, Inc. (2330 Circadian Way)</t>
+  </si>
+  <si>
+    <t>2330 Circadian Way  Santa Rosa CA 95407</t>
+  </si>
+  <si>
+    <t>CraftForce Services, Inc. (2753 Giffen Avenue)</t>
+  </si>
+  <si>
+    <t>2753 Giffen Avenue  Santa Rosa CA 95407</t>
   </si>
   <si>
     <r>
@@ -595,7 +586,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 07/20/2026</t>
+      <t>07/01/26 to 07/22/2026</t>
     </r>
     <r>
       <rPr>
@@ -616,6 +607,39 @@
         <scheme val="minor"/>
       </rPr>
       <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I38.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WARN REPORT -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+01/01/2023 - 07/22/2026
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through H3.</t>
     </r>
   </si>
 </sst>
@@ -847,7 +871,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -937,6 +961,18 @@
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1731,10 +1767,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I38" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I38" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I26">
-    <sortCondition ref="C2:C26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I42" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I42" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
+    <sortCondition ref="C2:C42"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3E60720E-46D7-48F7-AF17-837D42D08A11}" name="County/Parish" dataDxfId="29"/>
@@ -2130,8 +2166,8 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
@@ -2153,7 +2189,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>2560</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2162,7 +2198,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2189,7 +2225,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2221,17 +2257,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="45.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="55.140625" style="3" customWidth="1"/>
     <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.5703125" customWidth="1"/>
     <col min="11" max="11" width="13.140625" customWidth="1"/>
@@ -2242,7 +2278,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -2985,7 +3021,7 @@
         <v>46281</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F27" s="28" t="s">
         <v>52</v>
@@ -2994,7 +3030,7 @@
         <v>5</v>
       </c>
       <c r="H27" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I27" s="32" t="s">
         <v>34</v>
@@ -3014,7 +3050,7 @@
         <v>46262</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F28" s="28" t="s">
         <v>6</v>
@@ -3023,7 +3059,7 @@
         <v>3</v>
       </c>
       <c r="H28" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I28" s="32" t="s">
         <v>46</v>
@@ -3043,7 +3079,7 @@
         <v>46262</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F29" s="28" t="s">
         <v>6</v>
@@ -3052,7 +3088,7 @@
         <v>5</v>
       </c>
       <c r="H29" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I29" s="32" t="s">
         <v>46</v>
@@ -3072,7 +3108,7 @@
         <v>46262</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F30" s="28" t="s">
         <v>6</v>
@@ -3081,7 +3117,7 @@
         <v>87</v>
       </c>
       <c r="H30" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I30" s="32" t="s">
         <v>46</v>
@@ -3101,7 +3137,7 @@
         <v>46262</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F31" s="28" t="s">
         <v>6</v>
@@ -3110,7 +3146,7 @@
         <v>55</v>
       </c>
       <c r="H31" s="30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I31" s="32" t="s">
         <v>46</v>
@@ -3130,7 +3166,7 @@
         <v>46234</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F32" s="28" t="s">
         <v>6</v>
@@ -3139,7 +3175,7 @@
         <v>94</v>
       </c>
       <c r="H32" s="30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I32" s="32" t="s">
         <v>47</v>
@@ -3159,7 +3195,7 @@
         <v>46285</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F33" s="28" t="s">
         <v>6</v>
@@ -3168,7 +3204,7 @@
         <v>253</v>
       </c>
       <c r="H33" s="30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I33" s="32" t="s">
         <v>30</v>
@@ -3176,7 +3212,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34" s="29">
         <v>46218</v>
@@ -3188,16 +3224,16 @@
         <v>46283</v>
       </c>
       <c r="E34" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="F34" s="28" t="s">
         <v>129</v>
-      </c>
-      <c r="F34" s="28" t="s">
-        <v>130</v>
       </c>
       <c r="G34" s="30">
         <v>71</v>
       </c>
       <c r="H34" s="30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I34" s="32" t="s">
         <v>34</v>
@@ -3217,7 +3253,7 @@
         <v>46296</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F35" s="28" t="s">
         <v>6</v>
@@ -3226,7 +3262,7 @@
         <v>76</v>
       </c>
       <c r="H35" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I35" s="32" t="s">
         <v>41</v>
@@ -3246,7 +3282,7 @@
         <v>46280</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F36" s="28" t="s">
         <v>52</v>
@@ -3255,7 +3291,7 @@
         <v>198</v>
       </c>
       <c r="H36" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I36" s="32" t="s">
         <v>47</v>
@@ -3263,7 +3299,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B37" s="29">
         <v>46223</v>
@@ -3275,7 +3311,7 @@
         <v>46286</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="28" t="s">
         <v>6</v>
@@ -3284,7 +3320,7 @@
         <v>25</v>
       </c>
       <c r="H37" s="30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I37" s="32" t="s">
         <v>41</v>
@@ -3292,7 +3328,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="29">
         <v>46217</v>
@@ -3304,7 +3340,7 @@
         <v>46278</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F38" s="28" t="s">
         <v>52</v>
@@ -3313,9 +3349,125 @@
         <v>49</v>
       </c>
       <c r="H38" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="I38" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="34">
+        <v>46224</v>
+      </c>
+      <c r="C39" s="34">
+        <v>46224</v>
+      </c>
+      <c r="D39" s="34">
+        <v>46285</v>
+      </c>
+      <c r="E39" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="I38" s="32" t="s">
+      <c r="F39" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" s="35">
+        <v>61</v>
+      </c>
+      <c r="H39" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="I39" s="36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" s="34">
+        <v>46224</v>
+      </c>
+      <c r="C40" s="34">
+        <v>46225</v>
+      </c>
+      <c r="D40" s="34">
+        <v>46291</v>
+      </c>
+      <c r="E40" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="G40" s="35">
+        <v>108</v>
+      </c>
+      <c r="H40" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="I40" s="36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" s="34">
+        <v>46225</v>
+      </c>
+      <c r="C41" s="34">
+        <v>46225</v>
+      </c>
+      <c r="D41" s="34">
+        <v>46285</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="35">
+        <v>51</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="I41" s="36" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B42" s="34">
+        <v>46225</v>
+      </c>
+      <c r="C42" s="34">
+        <v>46225</v>
+      </c>
+      <c r="D42" s="34">
+        <v>46285</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="35">
+        <v>7</v>
+      </c>
+      <c r="H42" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="I42" s="36" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3333,7 +3485,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I38</xm:sqref>
+          <xm:sqref>I3:I42</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3454,7 +3606,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="E1"/>
     </row>
@@ -3869,47 +4021,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6272687-601F-424B-A8D8-C079CFA9EA3C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{635270C0-88C0-4230-934C-061448031A4A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{114C4746-C3AE-4E3C-852F-947D928A7F58}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{430DD834-7124-4E64-9722-C8486ADAC12C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B66F8A0-9A49-4A75-B4A3-15CE84DBE70A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20985313-04A7-4ED1-A6BE-346FA5C191E8}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\WSB-CO\Program Support\WARN\CalJOBS WARN Reports\WARN CALJOBS REPORTS - DAILY\SFY27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE40062-A11B-4C19-8D07-8A155D7AC06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44EDF889-ABD7-4825-A4AB-44908F0B6CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" activeTab="2" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="178">
   <si>
     <t>County/Parish</t>
   </si>
@@ -575,6 +575,87 @@
     <t>2753 Giffen Avenue  Santa Rosa CA 95407</t>
   </si>
   <si>
+    <t>Imperial County</t>
+  </si>
+  <si>
+    <t>Fortrex</t>
+  </si>
+  <si>
+    <t>57 Shank Road  Brawley CA 92227</t>
+  </si>
+  <si>
+    <t>Uber Technologies, Inc. (1655 3rd Street)</t>
+  </si>
+  <si>
+    <t>1655 3rd Street  San Francisco CA 94158</t>
+  </si>
+  <si>
+    <t>Uber Technologies, Inc. (1725 3rd St.)</t>
+  </si>
+  <si>
+    <t>1725 3rd St.  San Francisco CA 94158</t>
+  </si>
+  <si>
+    <t>Uber Technologies, Inc. (Remote)</t>
+  </si>
+  <si>
+    <t>1655 3rd Street (Remote)  San Francisco CA 94158</t>
+  </si>
+  <si>
+    <t>Chick-fil-A &amp; Fig</t>
+  </si>
+  <si>
+    <t>660 S Figueroa St., Ste. 100  Los Angeles CA 90017</t>
+  </si>
+  <si>
+    <t>Monterey County</t>
+  </si>
+  <si>
+    <t>PD Systems</t>
+  </si>
+  <si>
+    <t>Fort Hunter Liggett, Building 3360 Hunter Liggett Road Jolon CA 93928</t>
+  </si>
+  <si>
+    <t>Intel Corporation - Robert Noyce Building</t>
+  </si>
+  <si>
+    <t>2200 Mission College Blvd  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Intel Corporation - SC-9</t>
+  </si>
+  <si>
+    <t>3601 Juliette Lane  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Intel Corporation - SC11</t>
+  </si>
+  <si>
+    <t>2191 Laurelwood Rd.  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Intel Corporation - SC-12</t>
+  </si>
+  <si>
+    <t>3600 Juliette Lane  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>Stanislaus County</t>
+  </si>
+  <si>
+    <t>O'Brien's Market Inc.</t>
+  </si>
+  <si>
+    <t>839 W. Roseburg Avenue  Modesto CA 95350</t>
+  </si>
+  <si>
+    <t>O'Briens Market Inc.</t>
+  </si>
+  <si>
+    <t>4120 Dale Road  Modesto CA 95356</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
@@ -586,7 +667,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 07/22/2026</t>
+      <t>07/01/26 to 07/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -606,7 +687,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I38.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I54.</t>
     </r>
   </si>
   <si>
@@ -629,7 +710,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 07/22/2026
+01/01/2023 - 07/28/2026
 </t>
     </r>
     <r>
@@ -756,7 +837,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -775,8 +856,14 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -864,6 +951,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA9A9A9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA9A9A9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA9A9A9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFA9A9A9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA9A9A9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -871,7 +984,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -963,16 +1076,31 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1767,8 +1895,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I42" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I42" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I54" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I54" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2166,8 +2294,8 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
@@ -2189,7 +2317,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>2787</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2198,7 +2326,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2207,7 +2335,7 @@
       </c>
       <c r="B5" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2225,7 +2353,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2257,17 +2385,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="72.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="55.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.5703125" customWidth="1"/>
     <col min="11" max="11" width="13.140625" customWidth="1"/>
@@ -2278,7 +2406,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -3356,119 +3484,467 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="33" t="s">
+      <c r="A39" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="34">
+      <c r="B39" s="29">
         <v>46224</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="29">
         <v>46224</v>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="29">
         <v>46285</v>
       </c>
-      <c r="E39" s="33" t="s">
+      <c r="E39" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="F39" s="33" t="s">
+      <c r="F39" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="35">
+      <c r="G39" s="30">
         <v>61</v>
       </c>
-      <c r="H39" s="35" t="s">
+      <c r="H39" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="I39" s="36" t="s">
+      <c r="I39" s="32" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="33" t="s">
+      <c r="A40" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="34">
+      <c r="B40" s="29">
         <v>46224</v>
       </c>
-      <c r="C40" s="34">
+      <c r="C40" s="29">
         <v>46225</v>
       </c>
-      <c r="D40" s="34">
+      <c r="D40" s="29">
         <v>46291</v>
       </c>
-      <c r="E40" s="33" t="s">
+      <c r="E40" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="F40" s="33" t="s">
+      <c r="F40" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="35">
+      <c r="G40" s="30">
         <v>108</v>
       </c>
-      <c r="H40" s="35" t="s">
+      <c r="H40" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="I40" s="36" t="s">
+      <c r="I40" s="32" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="33" t="s">
+      <c r="A41" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B41" s="34">
+      <c r="B41" s="29">
         <v>46225</v>
       </c>
-      <c r="C41" s="34">
+      <c r="C41" s="29">
         <v>46225</v>
       </c>
-      <c r="D41" s="34">
+      <c r="D41" s="29">
         <v>46285</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="35">
+      <c r="G41" s="30">
         <v>51</v>
       </c>
-      <c r="H41" s="35" t="s">
+      <c r="H41" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="I41" s="36" t="s">
+      <c r="I41" s="32" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="33" t="s">
+      <c r="A42" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B42" s="34">
+      <c r="B42" s="29">
         <v>46225</v>
       </c>
-      <c r="C42" s="34">
+      <c r="C42" s="29">
         <v>46225</v>
       </c>
-      <c r="D42" s="34">
+      <c r="D42" s="29">
         <v>46285</v>
       </c>
-      <c r="E42" s="33" t="s">
+      <c r="E42" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="F42" s="33" t="s">
+      <c r="F42" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="35">
+      <c r="G42" s="30">
         <v>7</v>
       </c>
-      <c r="H42" s="35" t="s">
+      <c r="H42" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="I42" s="36" t="s">
+      <c r="I42" s="32" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="B43" s="34">
+        <v>46226</v>
+      </c>
+      <c r="C43" s="35">
+        <v>46226</v>
+      </c>
+      <c r="D43" s="34">
+        <v>46255</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" s="37">
+        <v>91</v>
+      </c>
+      <c r="H43" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="I43" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="38">
+        <v>46225</v>
+      </c>
+      <c r="C44" s="39">
+        <v>46226</v>
+      </c>
+      <c r="D44" s="38">
+        <v>46286</v>
+      </c>
+      <c r="E44" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="F44" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="G44" s="41">
+        <v>26</v>
+      </c>
+      <c r="H44" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="I44" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="34">
+        <v>46225</v>
+      </c>
+      <c r="C45" s="35">
+        <v>46226</v>
+      </c>
+      <c r="D45" s="34">
+        <v>46286</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G45" s="37">
+        <v>1</v>
+      </c>
+      <c r="H45" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="I45" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="38">
+        <v>46225</v>
+      </c>
+      <c r="C46" s="39">
+        <v>46226</v>
+      </c>
+      <c r="D46" s="38">
+        <v>46286</v>
+      </c>
+      <c r="E46" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="F46" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="41">
+        <v>14</v>
+      </c>
+      <c r="H46" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="I46" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="34">
+        <v>46227</v>
+      </c>
+      <c r="C47" s="35">
+        <v>46227</v>
+      </c>
+      <c r="D47" s="34">
+        <v>46292</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="F47" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="G47" s="37">
+        <v>77</v>
+      </c>
+      <c r="H47" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="I47" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="B48" s="34">
+        <v>46230</v>
+      </c>
+      <c r="C48" s="34">
+        <v>46230</v>
+      </c>
+      <c r="D48" s="34">
+        <v>46262</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="F48" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="37">
+        <v>81</v>
+      </c>
+      <c r="H48" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="I48" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" s="34">
+        <v>46227</v>
+      </c>
+      <c r="C49" s="35">
+        <v>46230</v>
+      </c>
+      <c r="D49" s="34">
+        <v>46249</v>
+      </c>
+      <c r="E49" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="F49" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G49" s="37">
+        <v>24</v>
+      </c>
+      <c r="H49" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="I49" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="38">
+        <v>46227</v>
+      </c>
+      <c r="C50" s="35">
+        <v>46230</v>
+      </c>
+      <c r="D50" s="34">
+        <v>46249</v>
+      </c>
+      <c r="E50" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="F50" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="41">
+        <v>10</v>
+      </c>
+      <c r="H50" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="I50" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51" s="34">
+        <v>46227</v>
+      </c>
+      <c r="C51" s="35">
+        <v>46230</v>
+      </c>
+      <c r="D51" s="34">
+        <v>46249</v>
+      </c>
+      <c r="E51" s="36" t="s">
+        <v>167</v>
+      </c>
+      <c r="F51" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="37">
+        <v>2</v>
+      </c>
+      <c r="H51" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="I51" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="38">
+        <v>46227</v>
+      </c>
+      <c r="C52" s="39">
+        <v>46230</v>
+      </c>
+      <c r="D52" s="38">
+        <v>46249</v>
+      </c>
+      <c r="E52" s="40" t="s">
+        <v>169</v>
+      </c>
+      <c r="F52" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="41">
+        <v>67</v>
+      </c>
+      <c r="H52" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="I52" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B53" s="38">
+        <v>46230</v>
+      </c>
+      <c r="C53" s="38">
+        <v>46230</v>
+      </c>
+      <c r="D53" s="38">
+        <v>46291</v>
+      </c>
+      <c r="E53" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F53" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="G53" s="41">
+        <v>50</v>
+      </c>
+      <c r="H53" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="I53" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B54" s="34">
+        <v>46230</v>
+      </c>
+      <c r="C54" s="34">
+        <v>46230</v>
+      </c>
+      <c r="D54" s="34">
+        <v>46292</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="F54" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G54" s="37">
+        <v>67</v>
+      </c>
+      <c r="H54" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="I54" s="32" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3485,7 +3961,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I42</xm:sqref>
+          <xm:sqref>I3:I54</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3606,7 +4082,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="E1"/>
     </row>
@@ -4021,15 +4497,47 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{635270C0-88C0-4230-934C-061448031A4A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A85E9B77-2C92-45AF-95F3-81622F4B0A0A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{430DD834-7124-4E64-9722-C8486ADAC12C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3693A623-36B2-4F40-AA66-C4EEB5C02499}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20985313-04A7-4ED1-A6BE-346FA5C191E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14C031CF-DC32-441D-98C4-47929368C47C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jchinn2\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44EDF889-ABD7-4825-A4AB-44908F0B6CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C5DE0D7-195B-4CA2-8997-70DF1C4ECACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="219">
   <si>
     <t>County/Parish</t>
   </si>
@@ -657,6 +657,162 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WARN REPORT -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+01/01/2023 - 07/29/2026
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through H3.</t>
+    </r>
+  </si>
+  <si>
+    <t>Sodexo</t>
+  </si>
+  <si>
+    <t>1020 W Ball Rd.  Anaheim CA 92802</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - San Leandro</t>
+  </si>
+  <si>
+    <t>3041 Teagarden Street  San Leandro CA 94577</t>
+  </si>
+  <si>
+    <t>Kern County</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Bakersfield/Fresno</t>
+  </si>
+  <si>
+    <t>3023 Unicorn Rd.  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC</t>
+  </si>
+  <si>
+    <t>9847 Pioneer Blvd.  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - San Fernando Valley</t>
+  </si>
+  <si>
+    <t>9753 Independence Ave.  Chatsworth CA 91311</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Ana</t>
+  </si>
+  <si>
+    <t>1401 E. Borchard Ave.  Santa Ana CA 92705</t>
+  </si>
+  <si>
+    <t>Riverside County</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Riverside</t>
+  </si>
+  <si>
+    <t>1110 Palmyrita Ave.  Riverside CA 92507</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Sacramento</t>
+  </si>
+  <si>
+    <t>2934 Ramona Ave., Suite 100  Sacramento CA 95826</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - South San Francisco</t>
+  </si>
+  <si>
+    <t>225 Harris Court  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Barbara</t>
+  </si>
+  <si>
+    <t>2373 A Street  Santa Maria CA 93455</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Maria</t>
+  </si>
+  <si>
+    <t>Santa Cruz County</t>
+  </si>
+  <si>
+    <t>Yerba Madre Co., LLC - Santa Cruz</t>
+  </si>
+  <si>
+    <t>1115 Thompson Ave. #6  Santa Cruz CA 95062</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Petaluma</t>
+  </si>
+  <si>
+    <t>775 Southpoint Blvd.  Petaluma CA 94954</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Rosa</t>
+  </si>
+  <si>
+    <t>1536 Hampton Way, Unit B  Santa Rosa CA 95407</t>
+  </si>
+  <si>
+    <t>ServiceNow, Inc.</t>
+  </si>
+  <si>
+    <t>2225 Lawson Lane  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>San Diego County</t>
+  </si>
+  <si>
+    <t>4801 Eastgate Mall  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Silgan Containers</t>
+  </si>
+  <si>
+    <t>430 Doherty Ave.  Modesto CA 95354</t>
+  </si>
+  <si>
+    <t>Tencent America LLC</t>
+  </si>
+  <si>
+    <t>15201 Laguna Canyon Rd.  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>Federal Express Corporation</t>
+  </si>
+  <si>
+    <t>111 Bird Center Dr  Palm Springs CA 92262</t>
+  </si>
+  <si>
+    <t>12212 Industrial Blvd.  Victorville CA 92395</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">WARN REPORT - </t>
     </r>
     <r>
@@ -667,7 +823,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 07/27/2026</t>
+      <t>07/01/26 to 07/29/2026</t>
     </r>
     <r>
       <rPr>
@@ -687,40 +843,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I54.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>WARN REPORT -</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-01/01/2023 - 07/28/2026
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through H3.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I74.</t>
     </r>
   </si>
 </sst>
@@ -1895,8 +2018,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I54" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I54" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I74" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I74" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2317,7 +2440,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>3297</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2326,7 +2449,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2335,7 +2458,7 @@
       </c>
       <c r="B5" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2353,7 +2476,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2385,7 +2508,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
@@ -2406,7 +2529,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -3945,6 +4068,586 @@
       </c>
       <c r="I54" s="32" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="29">
+        <v>46227</v>
+      </c>
+      <c r="C55" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D55" s="29">
+        <v>46295</v>
+      </c>
+      <c r="E55" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G55" s="30">
+        <v>164</v>
+      </c>
+      <c r="H55" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="I55" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C56" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D56" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E56" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="F56" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="30">
+        <v>4</v>
+      </c>
+      <c r="H56" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="I56" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="B57" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C57" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D57" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E57" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="F57" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="30">
+        <v>1</v>
+      </c>
+      <c r="H57" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="I57" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C58" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D58" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E58" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="F58" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="30">
+        <v>6</v>
+      </c>
+      <c r="H58" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="I58" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C59" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D59" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E59" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="F59" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="30">
+        <v>2</v>
+      </c>
+      <c r="H59" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="I59" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B60" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C60" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D60" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E60" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="F60" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="30">
+        <v>1</v>
+      </c>
+      <c r="H60" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="I60" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="B61" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C61" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D61" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="F61" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="30">
+        <v>2</v>
+      </c>
+      <c r="H61" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="I61" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B62" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C62" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D62" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E62" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="F62" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="30">
+        <v>3</v>
+      </c>
+      <c r="H62" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="I62" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C63" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D63" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E63" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="F63" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G63" s="30">
+        <v>1</v>
+      </c>
+      <c r="H63" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="I63" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B64" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C64" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D64" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E64" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="F64" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="30">
+        <v>1</v>
+      </c>
+      <c r="H64" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="I64" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B65" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C65" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D65" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E65" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="F65" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="30">
+        <v>1</v>
+      </c>
+      <c r="H65" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="I65" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="B66" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C66" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D66" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E66" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="F66" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="30">
+        <v>1</v>
+      </c>
+      <c r="H66" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="I66" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B67" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C67" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D67" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="F67" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="30">
+        <v>1</v>
+      </c>
+      <c r="H67" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="I67" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B68" s="29">
+        <v>46230</v>
+      </c>
+      <c r="C68" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D68" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E68" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="F68" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="30">
+        <v>1</v>
+      </c>
+      <c r="H68" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="I68" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B69" s="29">
+        <v>46231</v>
+      </c>
+      <c r="C69" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D69" s="29">
+        <v>46293</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="F69" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G69" s="30">
+        <v>154</v>
+      </c>
+      <c r="H69" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="I69" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B70" s="29">
+        <v>46231</v>
+      </c>
+      <c r="C70" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D70" s="29">
+        <v>46293</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="F70" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="30">
+        <v>133</v>
+      </c>
+      <c r="H70" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="I70" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B71" s="29">
+        <v>46224</v>
+      </c>
+      <c r="C71" s="29">
+        <v>46231</v>
+      </c>
+      <c r="D71" s="29">
+        <v>46286</v>
+      </c>
+      <c r="E71" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="F71" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G71" s="30">
+        <v>55</v>
+      </c>
+      <c r="H71" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="I71" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" s="29">
+        <v>46232</v>
+      </c>
+      <c r="C72" s="29">
+        <v>46232</v>
+      </c>
+      <c r="D72" s="29">
+        <v>46293</v>
+      </c>
+      <c r="E72" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="F72" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="30">
+        <v>68</v>
+      </c>
+      <c r="H72" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="I72" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="B73" s="29">
+        <v>46232</v>
+      </c>
+      <c r="C73" s="29">
+        <v>46232</v>
+      </c>
+      <c r="D73" s="29">
+        <v>46294</v>
+      </c>
+      <c r="E73" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="F73" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G73" s="30">
+        <v>62</v>
+      </c>
+      <c r="H73" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="I73" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="29">
+        <v>46231</v>
+      </c>
+      <c r="C74" s="29">
+        <v>46232</v>
+      </c>
+      <c r="D74" s="29">
+        <v>46293</v>
+      </c>
+      <c r="E74" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="F74" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G74" s="30">
+        <v>54</v>
+      </c>
+      <c r="H74" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="I74" s="32" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -3961,7 +4664,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I54</xm:sqref>
+          <xm:sqref>I3:I74</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4082,7 +4785,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E1"/>
     </row>
@@ -4497,47 +5200,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A85E9B77-2C92-45AF-95F3-81622F4B0A0A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F38B4A7F-259F-478E-A805-61E23EF965F9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3693A623-36B2-4F40-AA66-C4EEB5C02499}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDD4CA5A-DE2F-4950-932D-4ACABD97ADED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14C031CF-DC32-441D-98C4-47929368C47C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B1D744B-E32E-400D-B8F0-5FEA2BD21F09}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jchinn2\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C5DE0D7-195B-4CA2-8997-70DF1C4ECACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4887BE7E-A474-4AC7-B479-29558E67501D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="243">
   <si>
     <t>County/Parish</t>
   </si>
@@ -656,6 +656,129 @@
     <t>4120 Dale Road  Modesto CA 95356</t>
   </si>
   <si>
+    <t>Sodexo</t>
+  </si>
+  <si>
+    <t>1020 W Ball Rd.  Anaheim CA 92802</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - San Leandro</t>
+  </si>
+  <si>
+    <t>3041 Teagarden Street  San Leandro CA 94577</t>
+  </si>
+  <si>
+    <t>Kern County</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Bakersfield/Fresno</t>
+  </si>
+  <si>
+    <t>3023 Unicorn Rd.  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC</t>
+  </si>
+  <si>
+    <t>9847 Pioneer Blvd.  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - San Fernando Valley</t>
+  </si>
+  <si>
+    <t>9753 Independence Ave.  Chatsworth CA 91311</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Ana</t>
+  </si>
+  <si>
+    <t>1401 E. Borchard Ave.  Santa Ana CA 92705</t>
+  </si>
+  <si>
+    <t>Riverside County</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Riverside</t>
+  </si>
+  <si>
+    <t>1110 Palmyrita Ave.  Riverside CA 92507</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Sacramento</t>
+  </si>
+  <si>
+    <t>2934 Ramona Ave., Suite 100  Sacramento CA 95826</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - South San Francisco</t>
+  </si>
+  <si>
+    <t>225 Harris Court  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Barbara</t>
+  </si>
+  <si>
+    <t>2373 A Street  Santa Maria CA 93455</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Maria</t>
+  </si>
+  <si>
+    <t>Santa Cruz County</t>
+  </si>
+  <si>
+    <t>Yerba Madre Co., LLC - Santa Cruz</t>
+  </si>
+  <si>
+    <t>1115 Thompson Ave. #6  Santa Cruz CA 95062</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Petaluma</t>
+  </si>
+  <si>
+    <t>775 Southpoint Blvd.  Petaluma CA 94954</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Rosa</t>
+  </si>
+  <si>
+    <t>1536 Hampton Way, Unit B  Santa Rosa CA 95407</t>
+  </si>
+  <si>
+    <t>ServiceNow, Inc.</t>
+  </si>
+  <si>
+    <t>2225 Lawson Lane  Santa Clara CA 95054</t>
+  </si>
+  <si>
+    <t>San Diego County</t>
+  </si>
+  <si>
+    <t>4801 Eastgate Mall  San Diego CA 92121</t>
+  </si>
+  <si>
+    <t>Silgan Containers</t>
+  </si>
+  <si>
+    <t>430 Doherty Ave.  Modesto CA 95354</t>
+  </si>
+  <si>
+    <t>Tencent America LLC</t>
+  </si>
+  <si>
+    <t>15201 Laguna Canyon Rd.  Irvine CA 92618</t>
+  </si>
+  <si>
+    <t>Federal Express Corporation</t>
+  </si>
+  <si>
+    <t>111 Bird Center Dr  Palm Springs CA 92262</t>
+  </si>
+  <si>
+    <t>12212 Industrial Blvd.  Victorville CA 92395</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -675,7 +798,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 07/29/2026
+01/01/2023 - 08/03/2026
 </t>
     </r>
     <r>
@@ -689,127 +812,76 @@
     </r>
   </si>
   <si>
-    <t>Sodexo</t>
-  </si>
-  <si>
-    <t>1020 W Ball Rd.  Anaheim CA 92802</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - San Leandro</t>
-  </si>
-  <si>
-    <t>3041 Teagarden Street  San Leandro CA 94577</t>
-  </si>
-  <si>
-    <t>Kern County</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Bakersfield/Fresno</t>
-  </si>
-  <si>
-    <t>3023 Unicorn Rd.  Bakersfield CA 93308</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC</t>
-  </si>
-  <si>
-    <t>9847 Pioneer Blvd.  Santa Fe Springs CA 90670</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - San Fernando Valley</t>
-  </si>
-  <si>
-    <t>9753 Independence Ave.  Chatsworth CA 91311</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Santa Ana</t>
-  </si>
-  <si>
-    <t>1401 E. Borchard Ave.  Santa Ana CA 92705</t>
-  </si>
-  <si>
-    <t>Riverside County</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Riverside</t>
-  </si>
-  <si>
-    <t>1110 Palmyrita Ave.  Riverside CA 92507</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Sacramento</t>
-  </si>
-  <si>
-    <t>2934 Ramona Ave., Suite 100  Sacramento CA 95826</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - South San Francisco</t>
-  </si>
-  <si>
-    <t>225 Harris Court  South San Francisco CA 94080</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Santa Barbara</t>
-  </si>
-  <si>
-    <t>2373 A Street  Santa Maria CA 93455</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Santa Maria</t>
-  </si>
-  <si>
-    <t>Santa Cruz County</t>
-  </si>
-  <si>
-    <t>Yerba Madre Co., LLC - Santa Cruz</t>
-  </si>
-  <si>
-    <t>1115 Thompson Ave. #6  Santa Cruz CA 95062</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Petaluma</t>
-  </si>
-  <si>
-    <t>775 Southpoint Blvd.  Petaluma CA 94954</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Santa Rosa</t>
-  </si>
-  <si>
-    <t>1536 Hampton Way, Unit B  Santa Rosa CA 95407</t>
-  </si>
-  <si>
-    <t>ServiceNow, Inc.</t>
-  </si>
-  <si>
-    <t>2225 Lawson Lane  Santa Clara CA 95054</t>
-  </si>
-  <si>
-    <t>San Diego County</t>
-  </si>
-  <si>
-    <t>4801 Eastgate Mall  San Diego CA 92121</t>
-  </si>
-  <si>
-    <t>Silgan Containers</t>
-  </si>
-  <si>
-    <t>430 Doherty Ave.  Modesto CA 95354</t>
-  </si>
-  <si>
-    <t>Tencent America LLC</t>
-  </si>
-  <si>
-    <t>15201 Laguna Canyon Rd.  Irvine CA 92618</t>
-  </si>
-  <si>
-    <t>Federal Express Corporation</t>
-  </si>
-  <si>
-    <t>111 Bird Center Dr  Palm Springs CA 92262</t>
-  </si>
-  <si>
-    <t>12212 Industrial Blvd.  Victorville CA 92395</t>
+    <t>Placer County</t>
+  </si>
+  <si>
+    <t>Sunnyside Restaurant and Lodge</t>
+  </si>
+  <si>
+    <t>1850 West Lake Blvd  Tahoe City CA 96145</t>
+  </si>
+  <si>
+    <t>International Rescue Committee, Inc.</t>
+  </si>
+  <si>
+    <t>2020 Hurley Way, Ste 395  Sacramento CA 95825</t>
+  </si>
+  <si>
+    <t>3446 N. Golden State Blvd, Ste A  Turlock CA 95382</t>
+  </si>
+  <si>
+    <t>WeDriveU, Inc.</t>
+  </si>
+  <si>
+    <t>5438 Victor Street  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>16922 Airport Blvd #25  Mojave CA 93501</t>
+  </si>
+  <si>
+    <t>6075 Lake Isabella Blvd.  Lake Isabella CA 93240</t>
+  </si>
+  <si>
+    <t>1536 Lebec Service Rd.  Lebec CA 92430</t>
+  </si>
+  <si>
+    <t>314 N Hayes St.  Tehachapi CA 93524</t>
+  </si>
+  <si>
+    <t>Visa</t>
+  </si>
+  <si>
+    <t>900 Metro Center Blvd  Foster City CA 94404</t>
+  </si>
+  <si>
+    <t>Veritone, Inc.</t>
+  </si>
+  <si>
+    <t>5291 California Ave., Ste. 350  Irvine CA 92617</t>
+  </si>
+  <si>
+    <t>Yamaha Motor Finance Corporation U.S.A.</t>
+  </si>
+  <si>
+    <t>6555 Katella Avenue  Cypress CA 90630</t>
+  </si>
+  <si>
+    <t>TPE Acquisition, LLC - 5116</t>
+  </si>
+  <si>
+    <t>5116 Chino Hills Parkway  Chino CA 91710</t>
+  </si>
+  <si>
+    <t>TPE Acquisition, LLC - 5026</t>
+  </si>
+  <si>
+    <t>5026 Chino Hills Parkway  Chino CA 91710</t>
+  </si>
+  <si>
+    <t>Chime Financial, Inc.</t>
+  </si>
+  <si>
+    <t>101 California Street, Suite 500  San Francisco CA 94111</t>
   </si>
   <si>
     <r>
@@ -823,7 +895,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 07/29/2026</t>
+      <t>07/01/26 to 08/03/2026</t>
     </r>
     <r>
       <rPr>
@@ -843,7 +915,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I74.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I88.</t>
     </r>
   </si>
 </sst>
@@ -960,7 +1032,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -977,12 +1049,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1107,7 +1173,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1184,6 +1250,9 @@
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1196,34 +1265,19 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -2018,8 +2072,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I74" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I74" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I88" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I88" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2368,7 +2422,7 @@
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="74" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="74.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="135" x14ac:dyDescent="0.25">
@@ -2417,7 +2471,7 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2440,7 +2494,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>4012</v>
+        <v>4719</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2449,7 +2503,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2476,7 +2530,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2508,13 +2562,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.7109375" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
@@ -2529,7 +2583,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -2563,1162 +2617,1162 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="30">
         <v>46203</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="30">
         <v>46204</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="30">
         <v>46266</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="30">
+      <c r="G3" s="31">
         <v>2</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="32" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="30">
         <v>46199</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="30">
         <v>46204</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <v>46232</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="31">
         <v>103</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="32" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="30">
         <v>46203</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="30">
         <v>46204</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>46264</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="31">
         <v>35</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="I5" s="31" t="s">
+      <c r="I5" s="32" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="30">
         <v>46205</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <v>46205</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <v>46269</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="31">
         <v>31</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="30">
         <v>46205</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="30">
         <v>46205</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>46280</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <v>7</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="31" t="s">
+      <c r="I7" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="30">
         <v>46205</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="30">
         <v>46210</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>46268</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <v>33</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>46209</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>46210</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>46269</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <v>52</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="32" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <v>46204</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <v>46211</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>46266</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <v>180</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="32" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <v>46210</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="30">
         <v>46211</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="30">
         <v>46273</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <v>212</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="31" t="s">
+      <c r="I11" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <v>46212</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <v>46212</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <v>46274</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="31">
         <v>80</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="28" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <v>46212</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="30">
         <v>46212</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <v>46272</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <v>96</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="28" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <v>46213</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>46213</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>46265</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <v>6</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="I14" s="32" t="s">
+      <c r="I14" s="28" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <v>46211</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>46213</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>46273</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <v>113</v>
       </c>
-      <c r="H15" s="30" t="s">
+      <c r="H15" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="I15" s="32" t="s">
+      <c r="I15" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <v>46210</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>46216</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>46270</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="F16" s="28" t="s">
+      <c r="F16" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <v>55</v>
       </c>
-      <c r="H16" s="30" t="s">
+      <c r="H16" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="32" t="s">
+      <c r="I16" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="29">
+      <c r="B17" s="30">
         <v>46209</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <v>46216</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <v>46268</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <v>81</v>
       </c>
-      <c r="H17" s="30" t="s">
+      <c r="H17" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="32" t="s">
+      <c r="I17" s="28" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B18" s="30">
         <v>46199</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <v>46217</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <v>46262</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="30">
+      <c r="G18" s="31">
         <v>51</v>
       </c>
-      <c r="H18" s="30" t="s">
+      <c r="H18" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="32" t="s">
+      <c r="I18" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <v>46217</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>46217</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>46279</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="F19" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="31">
         <v>78</v>
       </c>
-      <c r="H19" s="30" t="s">
+      <c r="H19" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="32" t="s">
+      <c r="I19" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="29">
+      <c r="B20" s="30">
         <v>46213</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <v>46217</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <v>46283</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="F20" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="31">
         <v>46</v>
       </c>
-      <c r="H20" s="30" t="s">
+      <c r="H20" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="I20" s="32" t="s">
+      <c r="I20" s="28" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="29">
+      <c r="B21" s="30">
         <v>46217</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>46217</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>46276</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="31">
         <v>28</v>
       </c>
-      <c r="H21" s="30" t="s">
+      <c r="H21" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="I21" s="32" t="s">
+      <c r="I21" s="28" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="29">
+      <c r="B22" s="30">
         <v>46216</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>46217</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>46276</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="31">
         <v>158</v>
       </c>
-      <c r="H22" s="30" t="s">
+      <c r="H22" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="I22" s="32" t="s">
+      <c r="I22" s="28" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="29">
+      <c r="B23" s="30">
         <v>46217</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="30">
         <v>46218</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <v>46276</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="31">
         <v>31</v>
       </c>
-      <c r="H23" s="30" t="s">
+      <c r="H23" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="32" t="s">
+      <c r="I23" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="29">
+      <c r="B24" s="30">
         <v>46217</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>46218</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>46295</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F24" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <v>67</v>
       </c>
-      <c r="H24" s="30" t="s">
+      <c r="H24" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="I24" s="32" t="s">
+      <c r="I24" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="B25" s="29">
+      <c r="B25" s="30">
         <v>46218</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>46218</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>46279</v>
       </c>
-      <c r="E25" s="28" t="s">
+      <c r="E25" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F25" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <v>57</v>
       </c>
-      <c r="H25" s="30" t="s">
+      <c r="H25" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="I25" s="32" t="s">
+      <c r="I25" s="28" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="30">
         <v>46217</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <v>46218</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <v>46265</v>
       </c>
-      <c r="E26" s="28" t="s">
+      <c r="E26" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F26" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G26" s="31">
         <v>37</v>
       </c>
-      <c r="H26" s="30" t="s">
+      <c r="H26" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="I26" s="32" t="s">
+      <c r="I26" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="30">
         <v>46219</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <v>46219</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <v>46281</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="31">
         <v>5</v>
       </c>
-      <c r="H27" s="30" t="s">
+      <c r="H27" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="I27" s="32" t="s">
+      <c r="I27" s="28" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="29">
+      <c r="B28" s="30">
         <v>46220</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="30">
         <v>46220</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="30">
         <v>46262</v>
       </c>
-      <c r="E28" s="28" t="s">
+      <c r="E28" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="31">
         <v>3</v>
       </c>
-      <c r="H28" s="30" t="s">
+      <c r="H28" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="I28" s="32" t="s">
+      <c r="I28" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="30">
         <v>46220</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <v>46220</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <v>46262</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="E29" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="30">
+      <c r="G29" s="31">
         <v>5</v>
       </c>
-      <c r="H29" s="30" t="s">
+      <c r="H29" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="I29" s="32" t="s">
+      <c r="I29" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="30">
         <v>46220</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="30">
         <v>46220</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="30">
         <v>46262</v>
       </c>
-      <c r="E30" s="28" t="s">
+      <c r="E30" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="F30" s="28" t="s">
+      <c r="F30" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="30">
+      <c r="G30" s="31">
         <v>87</v>
       </c>
-      <c r="H30" s="30" t="s">
+      <c r="H30" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="I30" s="32" t="s">
+      <c r="I30" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="29">
+      <c r="B31" s="30">
         <v>46220</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="30">
         <v>46220</v>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="30">
         <v>46262</v>
       </c>
-      <c r="E31" s="28" t="s">
+      <c r="E31" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="F31" s="28" t="s">
+      <c r="F31" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31" s="31">
         <v>55</v>
       </c>
-      <c r="H31" s="30" t="s">
+      <c r="H31" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="I31" s="32" t="s">
+      <c r="I31" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="30">
         <v>46219</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="30">
         <v>46220</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="30">
         <v>46234</v>
       </c>
-      <c r="E32" s="28" t="s">
+      <c r="E32" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="F32" s="28" t="s">
+      <c r="F32" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G32" s="31">
         <v>94</v>
       </c>
-      <c r="H32" s="30" t="s">
+      <c r="H32" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="I32" s="32" t="s">
+      <c r="I32" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="29">
+      <c r="B33" s="30">
         <v>46220</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="30">
         <v>46220</v>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="30">
         <v>46285</v>
       </c>
-      <c r="E33" s="28" t="s">
+      <c r="E33" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="F33" s="28" t="s">
+      <c r="F33" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33" s="31">
         <v>253</v>
       </c>
-      <c r="H33" s="30" t="s">
+      <c r="H33" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="I33" s="32" t="s">
+      <c r="I33" s="28" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="B34" s="29">
+      <c r="B34" s="30">
         <v>46218</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="30">
         <v>46220</v>
       </c>
-      <c r="D34" s="29">
+      <c r="D34" s="30">
         <v>46283</v>
       </c>
-      <c r="E34" s="28" t="s">
+      <c r="E34" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="F34" s="28" t="s">
+      <c r="F34" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="G34" s="30">
+      <c r="G34" s="31">
         <v>71</v>
       </c>
-      <c r="H34" s="30" t="s">
+      <c r="H34" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="I34" s="32" t="s">
+      <c r="I34" s="28" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <v>46220</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="30">
         <v>46223</v>
       </c>
-      <c r="D35" s="29">
+      <c r="D35" s="30">
         <v>46296</v>
       </c>
-      <c r="E35" s="28" t="s">
+      <c r="E35" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="F35" s="28" t="s">
+      <c r="F35" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="31">
         <v>76</v>
       </c>
-      <c r="H35" s="30" t="s">
+      <c r="H35" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="I35" s="32" t="s">
+      <c r="I35" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="30">
         <v>46217</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="30">
         <v>46223</v>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="30">
         <v>46280</v>
       </c>
-      <c r="E36" s="28" t="s">
+      <c r="E36" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="F36" s="28" t="s">
+      <c r="F36" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="30">
+      <c r="G36" s="31">
         <v>198</v>
       </c>
-      <c r="H36" s="30" t="s">
+      <c r="H36" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="I36" s="32" t="s">
+      <c r="I36" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <v>46223</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="30">
         <v>46223</v>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="30">
         <v>46286</v>
       </c>
-      <c r="E37" s="28" t="s">
+      <c r="E37" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="28" t="s">
+      <c r="F37" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="31">
         <v>25</v>
       </c>
-      <c r="H37" s="30" t="s">
+      <c r="H37" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="I37" s="32" t="s">
+      <c r="I37" s="28" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="28" t="s">
+      <c r="A38" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="B38" s="29">
+      <c r="B38" s="30">
         <v>46217</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="30">
         <v>46223</v>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="30">
         <v>46278</v>
       </c>
-      <c r="E38" s="28" t="s">
+      <c r="E38" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="F38" s="28" t="s">
+      <c r="F38" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="30">
+      <c r="G38" s="31">
         <v>49</v>
       </c>
-      <c r="H38" s="30" t="s">
+      <c r="H38" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="I38" s="32" t="s">
+      <c r="I38" s="28" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="28" t="s">
+      <c r="A39" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="29">
+      <c r="B39" s="30">
         <v>46224</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="30">
         <v>46224</v>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="30">
         <v>46285</v>
       </c>
-      <c r="E39" s="28" t="s">
+      <c r="E39" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="F39" s="28" t="s">
+      <c r="F39" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39" s="31">
         <v>61</v>
       </c>
-      <c r="H39" s="30" t="s">
+      <c r="H39" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="I39" s="32" t="s">
+      <c r="I39" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="30">
         <v>46224</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="30">
         <v>46225</v>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="30">
         <v>46291</v>
       </c>
-      <c r="E40" s="28" t="s">
+      <c r="E40" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="F40" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="30">
+      <c r="G40" s="31">
         <v>108</v>
       </c>
-      <c r="H40" s="30" t="s">
+      <c r="H40" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="I40" s="32" t="s">
+      <c r="I40" s="28" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="30">
         <v>46225</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="30">
         <v>46225</v>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="30">
         <v>46285</v>
       </c>
-      <c r="E41" s="28" t="s">
+      <c r="E41" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="F41" s="28" t="s">
+      <c r="F41" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="30">
+      <c r="G41" s="31">
         <v>51</v>
       </c>
-      <c r="H41" s="30" t="s">
+      <c r="H41" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="I41" s="32" t="s">
+      <c r="I41" s="28" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="28" t="s">
+      <c r="A42" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="30">
         <v>46225</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="30">
         <v>46225</v>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="30">
         <v>46285</v>
       </c>
-      <c r="E42" s="28" t="s">
+      <c r="E42" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="30">
+      <c r="G42" s="31">
         <v>7</v>
       </c>
-      <c r="H42" s="30" t="s">
+      <c r="H42" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="I42" s="32" t="s">
+      <c r="I42" s="28" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3747,7 +3801,7 @@
       <c r="H43" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="I43" s="32" t="s">
+      <c r="I43" s="28" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3755,28 +3809,28 @@
       <c r="A44" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="B44" s="38">
+      <c r="B44" s="34">
         <v>46225</v>
       </c>
-      <c r="C44" s="39">
+      <c r="C44" s="35">
         <v>46226</v>
       </c>
-      <c r="D44" s="38">
+      <c r="D44" s="34">
         <v>46286</v>
       </c>
-      <c r="E44" s="40" t="s">
+      <c r="E44" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="F44" s="40" t="s">
+      <c r="F44" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="41">
+      <c r="G44" s="37">
         <v>26</v>
       </c>
-      <c r="H44" s="40" t="s">
+      <c r="H44" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="I44" s="32" t="s">
+      <c r="I44" s="28" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3805,7 +3859,7 @@
       <c r="H45" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="I45" s="32" t="s">
+      <c r="I45" s="28" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3813,28 +3867,28 @@
       <c r="A46" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="B46" s="38">
+      <c r="B46" s="34">
         <v>46225</v>
       </c>
-      <c r="C46" s="39">
+      <c r="C46" s="35">
         <v>46226</v>
       </c>
-      <c r="D46" s="38">
+      <c r="D46" s="34">
         <v>46286</v>
       </c>
-      <c r="E46" s="40" t="s">
+      <c r="E46" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="F46" s="40" t="s">
+      <c r="F46" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="G46" s="41">
+      <c r="G46" s="37">
         <v>14</v>
       </c>
-      <c r="H46" s="40" t="s">
+      <c r="H46" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="I46" s="32" t="s">
+      <c r="I46" s="28" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3863,7 +3917,7 @@
       <c r="H47" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="I47" s="32" t="s">
+      <c r="I47" s="28" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3892,7 +3946,7 @@
       <c r="H48" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="I48" s="32" t="s">
+      <c r="I48" s="28" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3921,7 +3975,7 @@
       <c r="H49" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="I49" s="32" t="s">
+      <c r="I49" s="28" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3929,7 +3983,7 @@
       <c r="A50" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="B50" s="38">
+      <c r="B50" s="34">
         <v>46227</v>
       </c>
       <c r="C50" s="35">
@@ -3938,19 +3992,19 @@
       <c r="D50" s="34">
         <v>46249</v>
       </c>
-      <c r="E50" s="40" t="s">
+      <c r="E50" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="F50" s="40" t="s">
+      <c r="F50" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="G50" s="41">
+      <c r="G50" s="37">
         <v>10</v>
       </c>
-      <c r="H50" s="40" t="s">
+      <c r="H50" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="I50" s="32" t="s">
+      <c r="I50" s="28" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3979,7 +4033,7 @@
       <c r="H51" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="I51" s="32" t="s">
+      <c r="I51" s="28" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3987,28 +4041,28 @@
       <c r="A52" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="38">
+      <c r="B52" s="34">
         <v>46227</v>
       </c>
-      <c r="C52" s="39">
+      <c r="C52" s="35">
         <v>46230</v>
       </c>
-      <c r="D52" s="38">
+      <c r="D52" s="34">
         <v>46249</v>
       </c>
-      <c r="E52" s="40" t="s">
+      <c r="E52" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="F52" s="40" t="s">
+      <c r="F52" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="G52" s="41">
+      <c r="G52" s="37">
         <v>67</v>
       </c>
-      <c r="H52" s="40" t="s">
+      <c r="H52" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="I52" s="32" t="s">
+      <c r="I52" s="28" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4016,28 +4070,28 @@
       <c r="A53" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="B53" s="38">
+      <c r="B53" s="34">
         <v>46230</v>
       </c>
-      <c r="C53" s="38">
+      <c r="C53" s="34">
         <v>46230</v>
       </c>
-      <c r="D53" s="38">
+      <c r="D53" s="34">
         <v>46291</v>
       </c>
-      <c r="E53" s="40" t="s">
+      <c r="E53" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="F53" s="40" t="s">
+      <c r="F53" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G53" s="41">
+      <c r="G53" s="37">
         <v>50</v>
       </c>
-      <c r="H53" s="40" t="s">
+      <c r="H53" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="I53" s="32" t="s">
+      <c r="I53" s="28" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4066,588 +4120,994 @@
       <c r="H54" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="I54" s="32" t="s">
+      <c r="I54" s="28" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="28" t="s">
+      <c r="A55" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="30">
         <v>46227</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="30">
         <v>46231</v>
       </c>
-      <c r="D55" s="29">
+      <c r="D55" s="30">
         <v>46295</v>
       </c>
-      <c r="E55" s="28" t="s">
+      <c r="E55" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="F55" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G55" s="31">
+        <v>164</v>
+      </c>
+      <c r="H55" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="F55" s="28" t="s">
+      <c r="I55" s="28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C56" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D56" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E56" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="F56" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="31">
+        <v>4</v>
+      </c>
+      <c r="H56" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="I56" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="B57" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C57" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D57" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E57" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="F57" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="31">
+        <v>1</v>
+      </c>
+      <c r="H57" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="I57" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C58" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D58" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E58" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="F58" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="31">
+        <v>6</v>
+      </c>
+      <c r="H58" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="I58" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C59" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D59" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E59" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="F59" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="31">
+        <v>2</v>
+      </c>
+      <c r="H59" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="I59" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B60" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C60" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D60" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E60" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="F60" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="31">
+        <v>1</v>
+      </c>
+      <c r="H60" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="I60" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C61" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D61" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E61" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="F61" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="31">
+        <v>2</v>
+      </c>
+      <c r="H61" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="I61" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B62" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C62" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D62" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E62" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="F62" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="31">
+        <v>3</v>
+      </c>
+      <c r="H62" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="I62" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C63" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D63" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E63" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="F63" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G63" s="31">
+        <v>1</v>
+      </c>
+      <c r="H63" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="I63" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B64" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C64" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D64" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E64" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="F64" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="31">
+        <v>1</v>
+      </c>
+      <c r="H64" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="I64" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="B65" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C65" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D65" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E65" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="F65" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="31">
+        <v>1</v>
+      </c>
+      <c r="H65" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="I65" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="29" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C66" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D66" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E66" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="F66" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="31">
+        <v>1</v>
+      </c>
+      <c r="H66" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="I66" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B67" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C67" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D67" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E67" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="F67" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="31">
+        <v>1</v>
+      </c>
+      <c r="H67" s="31" t="s">
+        <v>203</v>
+      </c>
+      <c r="I67" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B68" s="30">
+        <v>46230</v>
+      </c>
+      <c r="C68" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D68" s="30">
+        <v>46266</v>
+      </c>
+      <c r="E68" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="F68" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="31">
+        <v>1</v>
+      </c>
+      <c r="H68" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="I68" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B69" s="30">
+        <v>46231</v>
+      </c>
+      <c r="C69" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D69" s="30">
+        <v>46293</v>
+      </c>
+      <c r="E69" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="F69" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G69" s="31">
+        <v>154</v>
+      </c>
+      <c r="H69" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="I69" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="B70" s="30">
+        <v>46231</v>
+      </c>
+      <c r="C70" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D70" s="30">
+        <v>46293</v>
+      </c>
+      <c r="E70" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="F70" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="31">
+        <v>133</v>
+      </c>
+      <c r="H70" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="I70" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="B71" s="30">
+        <v>46224</v>
+      </c>
+      <c r="C71" s="30">
+        <v>46231</v>
+      </c>
+      <c r="D71" s="30">
+        <v>46286</v>
+      </c>
+      <c r="E71" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="F71" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="G71" s="31">
+        <v>55</v>
+      </c>
+      <c r="H71" s="31" t="s">
+        <v>211</v>
+      </c>
+      <c r="I71" s="28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" s="30">
+        <v>46232</v>
+      </c>
+      <c r="C72" s="30">
+        <v>46232</v>
+      </c>
+      <c r="D72" s="30">
+        <v>46293</v>
+      </c>
+      <c r="E72" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="F72" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="31">
+        <v>68</v>
+      </c>
+      <c r="H72" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="I72" s="28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="B73" s="30">
+        <v>46232</v>
+      </c>
+      <c r="C73" s="30">
+        <v>46232</v>
+      </c>
+      <c r="D73" s="30">
+        <v>46294</v>
+      </c>
+      <c r="E73" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="F73" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="30">
-        <v>164</v>
-      </c>
-      <c r="H55" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="I55" s="32" t="s">
+      <c r="G73" s="31">
+        <v>62</v>
+      </c>
+      <c r="H73" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="I73" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B74" s="30">
+        <v>46231</v>
+      </c>
+      <c r="C74" s="30">
+        <v>46232</v>
+      </c>
+      <c r="D74" s="30">
+        <v>46293</v>
+      </c>
+      <c r="E74" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="F74" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G74" s="31">
+        <v>54</v>
+      </c>
+      <c r="H74" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="I74" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="B75" s="30">
+        <v>46231</v>
+      </c>
+      <c r="C75" s="30">
+        <v>46233</v>
+      </c>
+      <c r="D75" s="30">
+        <v>46299</v>
+      </c>
+      <c r="E75" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="F75" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G75" s="31">
         <v>47</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="B56" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C56" s="29">
+      <c r="H75" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="I75" s="28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B76" s="30">
         <v>46231</v>
       </c>
-      <c r="D56" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E56" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="F56" s="28" t="s">
+      <c r="C76" s="30">
+        <v>46233</v>
+      </c>
+      <c r="D76" s="30">
+        <v>46295</v>
+      </c>
+      <c r="E76" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="F76" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G56" s="30">
-        <v>4</v>
-      </c>
-      <c r="H56" s="30" t="s">
+      <c r="G76" s="31">
+        <v>41</v>
+      </c>
+      <c r="H76" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="I76" s="28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="30">
+        <v>46231</v>
+      </c>
+      <c r="C77" s="30">
+        <v>46233</v>
+      </c>
+      <c r="D77" s="30">
+        <v>46295</v>
+      </c>
+      <c r="E77" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="F77" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="31">
+        <v>15</v>
+      </c>
+      <c r="H77" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="I77" s="28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="I56" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="B57" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C57" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D57" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E57" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="F57" s="28" t="s">
+      <c r="B78" s="30">
+        <v>46234</v>
+      </c>
+      <c r="C78" s="30">
+        <v>46234</v>
+      </c>
+      <c r="D78" s="30">
+        <v>46296</v>
+      </c>
+      <c r="E78" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="F78" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G78" s="31">
+        <v>34</v>
+      </c>
+      <c r="H78" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="I78" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="B79" s="30">
+        <v>46234</v>
+      </c>
+      <c r="C79" s="30">
+        <v>46234</v>
+      </c>
+      <c r="D79" s="30">
+        <v>46296</v>
+      </c>
+      <c r="E79" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="F79" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G79" s="31">
+        <v>12</v>
+      </c>
+      <c r="H79" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="I79" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="B80" s="30">
+        <v>46234</v>
+      </c>
+      <c r="C80" s="30">
+        <v>46234</v>
+      </c>
+      <c r="D80" s="30">
+        <v>46296</v>
+      </c>
+      <c r="E80" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="F80" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G80" s="31">
+        <v>15</v>
+      </c>
+      <c r="H80" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="I80" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="B81" s="30">
+        <v>46234</v>
+      </c>
+      <c r="C81" s="30">
+        <v>46234</v>
+      </c>
+      <c r="D81" s="30">
+        <v>46296</v>
+      </c>
+      <c r="E81" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="F81" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G81" s="31">
+        <v>1</v>
+      </c>
+      <c r="H81" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="I81" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="B82" s="30">
+        <v>46234</v>
+      </c>
+      <c r="C82" s="30">
+        <v>46234</v>
+      </c>
+      <c r="D82" s="30">
+        <v>46296</v>
+      </c>
+      <c r="E82" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="F82" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G82" s="31">
+        <v>1</v>
+      </c>
+      <c r="H82" s="31" t="s">
+        <v>229</v>
+      </c>
+      <c r="I82" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B83" s="30">
+        <v>46234</v>
+      </c>
+      <c r="C83" s="30">
+        <v>46234</v>
+      </c>
+      <c r="D83" s="30">
+        <v>46296</v>
+      </c>
+      <c r="E83" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="F83" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G57" s="30">
-        <v>1</v>
-      </c>
-      <c r="H57" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="I57" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B58" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C58" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D58" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E58" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="F58" s="28" t="s">
+      <c r="G83" s="31">
+        <v>320</v>
+      </c>
+      <c r="H83" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="I83" s="28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B84" s="30">
+        <v>46233</v>
+      </c>
+      <c r="C84" s="30">
+        <v>46234</v>
+      </c>
+      <c r="D84" s="30">
+        <v>46293</v>
+      </c>
+      <c r="E84" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="F84" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="G58" s="30">
+      <c r="G84" s="31">
+        <v>10</v>
+      </c>
+      <c r="H84" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="I84" s="28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B85" s="30">
+        <v>46234</v>
+      </c>
+      <c r="C85" s="30">
+        <v>46234</v>
+      </c>
+      <c r="D85" s="30">
+        <v>46296</v>
+      </c>
+      <c r="E85" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="F85" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G85" s="31">
+        <v>61</v>
+      </c>
+      <c r="H85" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="I85" s="28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B86" s="30">
+        <v>46234</v>
+      </c>
+      <c r="C86" s="30">
+        <v>46237</v>
+      </c>
+      <c r="D86" s="30">
+        <v>46295</v>
+      </c>
+      <c r="E86" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="F86" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G86" s="31">
+        <v>3</v>
+      </c>
+      <c r="H86" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="I86" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B87" s="30">
+        <v>46234</v>
+      </c>
+      <c r="C87" s="30">
+        <v>46237</v>
+      </c>
+      <c r="D87" s="30">
+        <v>46295</v>
+      </c>
+      <c r="E87" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="F87" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G87" s="31">
+        <v>12</v>
+      </c>
+      <c r="H87" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="I87" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B88" s="30">
+        <v>46234</v>
+      </c>
+      <c r="C88" s="30">
+        <v>46237</v>
+      </c>
+      <c r="D88" s="30">
+        <v>46295</v>
+      </c>
+      <c r="E88" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="F88" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="H58" s="30" t="s">
-        <v>185</v>
-      </c>
-      <c r="I58" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B59" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C59" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D59" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E59" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="F59" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" s="30">
-        <v>2</v>
-      </c>
-      <c r="H59" s="30" t="s">
-        <v>187</v>
-      </c>
-      <c r="I59" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C60" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D60" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E60" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="F60" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G60" s="30">
-        <v>1</v>
-      </c>
-      <c r="H60" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="I60" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="B61" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C61" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D61" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E61" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="F61" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G61" s="30">
-        <v>2</v>
-      </c>
-      <c r="H61" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="I61" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C62" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D62" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E62" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="F62" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G62" s="30">
-        <v>3</v>
-      </c>
-      <c r="H62" s="30" t="s">
-        <v>194</v>
-      </c>
-      <c r="I62" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C63" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D63" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E63" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="F63" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G63" s="30">
-        <v>1</v>
-      </c>
-      <c r="H63" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="I63" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="B64" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C64" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D64" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E64" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="F64" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" s="30">
-        <v>1</v>
-      </c>
-      <c r="H64" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="I64" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="B65" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C65" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D65" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E65" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="F65" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="30">
-        <v>1</v>
-      </c>
-      <c r="H65" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="I65" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="B66" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C66" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D66" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E66" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="F66" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G66" s="30">
-        <v>1</v>
-      </c>
-      <c r="H66" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="I66" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="B67" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C67" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D67" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E67" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="F67" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G67" s="30">
-        <v>1</v>
-      </c>
-      <c r="H67" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="I67" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="B68" s="29">
-        <v>46230</v>
-      </c>
-      <c r="C68" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D68" s="29">
-        <v>46266</v>
-      </c>
-      <c r="E68" s="28" t="s">
-        <v>205</v>
-      </c>
-      <c r="F68" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G68" s="30">
-        <v>1</v>
-      </c>
-      <c r="H68" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="I68" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="B69" s="29">
-        <v>46231</v>
-      </c>
-      <c r="C69" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D69" s="29">
-        <v>46293</v>
-      </c>
-      <c r="E69" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="F69" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G69" s="30">
-        <v>154</v>
-      </c>
-      <c r="H69" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="I69" s="32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="B70" s="29">
-        <v>46231</v>
-      </c>
-      <c r="C70" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D70" s="29">
-        <v>46293</v>
-      </c>
-      <c r="E70" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="F70" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G70" s="30">
-        <v>133</v>
-      </c>
-      <c r="H70" s="30" t="s">
-        <v>210</v>
-      </c>
-      <c r="I70" s="32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="B71" s="29">
-        <v>46224</v>
-      </c>
-      <c r="C71" s="29">
-        <v>46231</v>
-      </c>
-      <c r="D71" s="29">
-        <v>46286</v>
-      </c>
-      <c r="E71" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="F71" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="G71" s="30">
-        <v>55</v>
-      </c>
-      <c r="H71" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="I71" s="32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B72" s="29">
-        <v>46232</v>
-      </c>
-      <c r="C72" s="29">
-        <v>46232</v>
-      </c>
-      <c r="D72" s="29">
-        <v>46293</v>
-      </c>
-      <c r="E72" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="F72" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="30">
-        <v>68</v>
-      </c>
-      <c r="H72" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="I72" s="32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="B73" s="29">
-        <v>46232</v>
-      </c>
-      <c r="C73" s="29">
-        <v>46232</v>
-      </c>
-      <c r="D73" s="29">
-        <v>46294</v>
-      </c>
-      <c r="E73" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="F73" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="G73" s="30">
-        <v>62</v>
-      </c>
-      <c r="H73" s="30" t="s">
-        <v>216</v>
-      </c>
-      <c r="I73" s="32" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="B74" s="29">
-        <v>46231</v>
-      </c>
-      <c r="C74" s="29">
-        <v>46232</v>
-      </c>
-      <c r="D74" s="29">
-        <v>46293</v>
-      </c>
-      <c r="E74" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="F74" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="G74" s="30">
-        <v>54</v>
-      </c>
-      <c r="H74" s="30" t="s">
-        <v>217</v>
-      </c>
-      <c r="I74" s="32" t="s">
-        <v>37</v>
+      <c r="G88" s="31">
+        <v>135</v>
+      </c>
+      <c r="H88" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="I88" s="28" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -4664,7 +5124,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I74</xm:sqref>
+          <xm:sqref>I3:I88</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4776,7 +5236,7 @@
     <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" style="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
@@ -4785,7 +5245,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="E1"/>
     </row>
@@ -5200,15 +5660,47 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F38B4A7F-259F-478E-A805-61E23EF965F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1857C4B4-7999-4C2D-AC48-24F916F1F539}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDD4CA5A-DE2F-4950-932D-4ACABD97ADED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0A027E7-D676-4CA5-B18E-07F77CCEDBBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B1D744B-E32E-400D-B8F0-5FEA2BD21F09}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2857766C-E7F4-45B8-996B-0092792850F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4887BE7E-A474-4AC7-B479-29558E67501D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA3ADFB7-02FE-4466-9A8E-62C41DFDBA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="251">
   <si>
     <t>County/Parish</t>
   </si>
@@ -728,9 +728,6 @@
     <t>Santa Cruz County</t>
   </si>
   <si>
-    <t>Yerba Madre Co., LLC - Santa Cruz</t>
-  </si>
-  <si>
     <t>1115 Thompson Ave. #6  Santa Cruz CA 95062</t>
   </si>
   <si>
@@ -777,6 +774,78 @@
   </si>
   <si>
     <t>12212 Industrial Blvd.  Victorville CA 92395</t>
+  </si>
+  <si>
+    <t>Placer County</t>
+  </si>
+  <si>
+    <t>Sunnyside Restaurant and Lodge</t>
+  </si>
+  <si>
+    <t>1850 West Lake Blvd  Tahoe City CA 96145</t>
+  </si>
+  <si>
+    <t>International Rescue Committee, Inc.</t>
+  </si>
+  <si>
+    <t>2020 Hurley Way, Ste 395  Sacramento CA 95825</t>
+  </si>
+  <si>
+    <t>3446 N. Golden State Blvd, Ste A  Turlock CA 95382</t>
+  </si>
+  <si>
+    <t>WeDriveU, Inc.</t>
+  </si>
+  <si>
+    <t>5438 Victor Street  Bakersfield CA 93308</t>
+  </si>
+  <si>
+    <t>16922 Airport Blvd #25  Mojave CA 93501</t>
+  </si>
+  <si>
+    <t>6075 Lake Isabella Blvd.  Lake Isabella CA 93240</t>
+  </si>
+  <si>
+    <t>1536 Lebec Service Rd.  Lebec CA 92430</t>
+  </si>
+  <si>
+    <t>314 N Hayes St.  Tehachapi CA 93524</t>
+  </si>
+  <si>
+    <t>Visa</t>
+  </si>
+  <si>
+    <t>900 Metro Center Blvd  Foster City CA 94404</t>
+  </si>
+  <si>
+    <t>Veritone, Inc.</t>
+  </si>
+  <si>
+    <t>5291 California Ave., Ste. 350  Irvine CA 92617</t>
+  </si>
+  <si>
+    <t>Yamaha Motor Finance Corporation U.S.A.</t>
+  </si>
+  <si>
+    <t>6555 Katella Avenue  Cypress CA 90630</t>
+  </si>
+  <si>
+    <t>TPE Acquisition, LLC - 5116</t>
+  </si>
+  <si>
+    <t>5116 Chino Hills Parkway  Chino CA 91710</t>
+  </si>
+  <si>
+    <t>TPE Acquisition, LLC - 5026</t>
+  </si>
+  <si>
+    <t>5026 Chino Hills Parkway  Chino CA 91710</t>
+  </si>
+  <si>
+    <t>Chime Financial, Inc.</t>
+  </si>
+  <si>
+    <t>101 California Street, Suite 500  San Francisco CA 94111</t>
   </si>
   <si>
     <r>
@@ -798,7 +867,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 08/03/2026
+01/01/2023 - 08/05/2026
 </t>
     </r>
     <r>
@@ -812,76 +881,31 @@
     </r>
   </si>
   <si>
-    <t>Placer County</t>
-  </si>
-  <si>
-    <t>Sunnyside Restaurant and Lodge</t>
-  </si>
-  <si>
-    <t>1850 West Lake Blvd  Tahoe City CA 96145</t>
-  </si>
-  <si>
-    <t>International Rescue Committee, Inc.</t>
-  </si>
-  <si>
-    <t>2020 Hurley Way, Ste 395  Sacramento CA 95825</t>
-  </si>
-  <si>
-    <t>3446 N. Golden State Blvd, Ste A  Turlock CA 95382</t>
-  </si>
-  <si>
-    <t>WeDriveU, Inc.</t>
-  </si>
-  <si>
-    <t>5438 Victor Street  Bakersfield CA 93308</t>
-  </si>
-  <si>
-    <t>16922 Airport Blvd #25  Mojave CA 93501</t>
-  </si>
-  <si>
-    <t>6075 Lake Isabella Blvd.  Lake Isabella CA 93240</t>
-  </si>
-  <si>
-    <t>1536 Lebec Service Rd.  Lebec CA 92430</t>
-  </si>
-  <si>
-    <t>314 N Hayes St.  Tehachapi CA 93524</t>
-  </si>
-  <si>
-    <t>Visa</t>
-  </si>
-  <si>
-    <t>900 Metro Center Blvd  Foster City CA 94404</t>
-  </si>
-  <si>
-    <t>Veritone, Inc.</t>
-  </si>
-  <si>
-    <t>5291 California Ave., Ste. 350  Irvine CA 92617</t>
-  </si>
-  <si>
-    <t>Yamaha Motor Finance Corporation U.S.A.</t>
-  </si>
-  <si>
-    <t>6555 Katella Avenue  Cypress CA 90630</t>
-  </si>
-  <si>
-    <t>TPE Acquisition, LLC - 5116</t>
-  </si>
-  <si>
-    <t>5116 Chino Hills Parkway  Chino CA 91710</t>
-  </si>
-  <si>
-    <t>TPE Acquisition, LLC - 5026</t>
-  </si>
-  <si>
-    <t>5026 Chino Hills Parkway  Chino CA 91710</t>
-  </si>
-  <si>
-    <t>Chime Financial, Inc.</t>
-  </si>
-  <si>
-    <t>101 California Street, Suite 500  San Francisco CA 94111</t>
+    <t>San Francisico Pretrial Diversion Project, Inc.</t>
+  </si>
+  <si>
+    <t>1200 Folsom Street  San Francisco CA 94103</t>
+  </si>
+  <si>
+    <t>Nutanix, Inc.</t>
+  </si>
+  <si>
+    <t>1740 Technology Drive  San Jose CA 95110</t>
+  </si>
+  <si>
+    <t>Eclipse Advantage, LLC</t>
+  </si>
+  <si>
+    <t>5540 East 4th Street  Ontario CA 91764</t>
+  </si>
+  <si>
+    <t>Salesforce, Inc.</t>
+  </si>
+  <si>
+    <t>415 Mission Street  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Cruz</t>
   </si>
   <si>
     <r>
@@ -895,7 +919,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 08/03/2026</t>
+      <t>07/01/26 to 08/05/2026</t>
     </r>
     <r>
       <rPr>
@@ -915,7 +939,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I88.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I92.</t>
     </r>
   </si>
 </sst>
@@ -2072,8 +2096,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I88" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I88" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I92" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I92" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2422,7 +2446,7 @@
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="74.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="74" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="135" x14ac:dyDescent="0.25">
@@ -2471,7 +2495,7 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2494,7 +2518,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>4719</v>
+        <v>4958</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2503,7 +2527,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2530,7 +2554,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2562,13 +2586,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.7109375" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
@@ -2583,7 +2607,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -4457,7 +4481,7 @@
         <v>46266</v>
       </c>
       <c r="E66" s="29" t="s">
-        <v>200</v>
+        <v>249</v>
       </c>
       <c r="F66" s="29" t="s">
         <v>6</v>
@@ -4466,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I66" s="28" t="s">
         <v>35</v>
@@ -4486,7 +4510,7 @@
         <v>46266</v>
       </c>
       <c r="E67" s="29" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F67" s="29" t="s">
         <v>6</v>
@@ -4495,7 +4519,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I67" s="28" t="s">
         <v>35</v>
@@ -4515,7 +4539,7 @@
         <v>46266</v>
       </c>
       <c r="E68" s="29" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F68" s="29" t="s">
         <v>6</v>
@@ -4524,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="31" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I68" s="28" t="s">
         <v>35</v>
@@ -4544,7 +4568,7 @@
         <v>46293</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F69" s="29" t="s">
         <v>6</v>
@@ -4553,7 +4577,7 @@
         <v>154</v>
       </c>
       <c r="H69" s="31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I69" s="28" t="s">
         <v>41</v>
@@ -4561,7 +4585,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B70" s="30">
         <v>46231</v>
@@ -4573,7 +4597,7 @@
         <v>46293</v>
       </c>
       <c r="E70" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F70" s="29" t="s">
         <v>6</v>
@@ -4582,7 +4606,7 @@
         <v>133</v>
       </c>
       <c r="H70" s="31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I70" s="28" t="s">
         <v>41</v>
@@ -4602,7 +4626,7 @@
         <v>46286</v>
       </c>
       <c r="E71" s="29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F71" s="29" t="s">
         <v>129</v>
@@ -4611,7 +4635,7 @@
         <v>55</v>
       </c>
       <c r="H71" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I71" s="28" t="s">
         <v>43</v>
@@ -4631,7 +4655,7 @@
         <v>46293</v>
       </c>
       <c r="E72" s="29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F72" s="29" t="s">
         <v>6</v>
@@ -4640,7 +4664,7 @@
         <v>68</v>
       </c>
       <c r="H72" s="31" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I72" s="28" t="s">
         <v>38</v>
@@ -4660,7 +4684,7 @@
         <v>46294</v>
       </c>
       <c r="E73" s="29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F73" s="29" t="s">
         <v>52</v>
@@ -4669,7 +4693,7 @@
         <v>62</v>
       </c>
       <c r="H73" s="31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I73" s="28" t="s">
         <v>37</v>
@@ -4689,7 +4713,7 @@
         <v>46293</v>
       </c>
       <c r="E74" s="29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F74" s="29" t="s">
         <v>52</v>
@@ -4698,7 +4722,7 @@
         <v>54</v>
       </c>
       <c r="H74" s="31" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I74" s="28" t="s">
         <v>37</v>
@@ -4706,7 +4730,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B75" s="30">
         <v>46231</v>
@@ -4718,7 +4742,7 @@
         <v>46299</v>
       </c>
       <c r="E75" s="29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F75" s="29" t="s">
         <v>52</v>
@@ -4727,7 +4751,7 @@
         <v>47</v>
       </c>
       <c r="H75" s="31" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I75" s="28" t="s">
         <v>47</v>
@@ -4747,7 +4771,7 @@
         <v>46295</v>
       </c>
       <c r="E76" s="29" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F76" s="29" t="s">
         <v>6</v>
@@ -4756,7 +4780,7 @@
         <v>41</v>
       </c>
       <c r="H76" s="31" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I76" s="28" t="s">
         <v>45</v>
@@ -4776,7 +4800,7 @@
         <v>46295</v>
       </c>
       <c r="E77" s="29" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F77" s="29" t="s">
         <v>6</v>
@@ -4785,7 +4809,7 @@
         <v>15</v>
       </c>
       <c r="H77" s="31" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I77" s="28" t="s">
         <v>45</v>
@@ -4805,7 +4829,7 @@
         <v>46296</v>
       </c>
       <c r="E78" s="29" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F78" s="29" t="s">
         <v>52</v>
@@ -4814,7 +4838,7 @@
         <v>34</v>
       </c>
       <c r="H78" s="31" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I78" s="28" t="s">
         <v>37</v>
@@ -4834,7 +4858,7 @@
         <v>46296</v>
       </c>
       <c r="E79" s="29" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F79" s="29" t="s">
         <v>52</v>
@@ -4843,7 +4867,7 @@
         <v>12</v>
       </c>
       <c r="H79" s="31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I79" s="28" t="s">
         <v>37</v>
@@ -4863,7 +4887,7 @@
         <v>46296</v>
       </c>
       <c r="E80" s="29" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F80" s="29" t="s">
         <v>52</v>
@@ -4872,7 +4896,7 @@
         <v>15</v>
       </c>
       <c r="H80" s="31" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I80" s="28" t="s">
         <v>37</v>
@@ -4892,7 +4916,7 @@
         <v>46296</v>
       </c>
       <c r="E81" s="29" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F81" s="29" t="s">
         <v>52</v>
@@ -4901,7 +4925,7 @@
         <v>1</v>
       </c>
       <c r="H81" s="31" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I81" s="28" t="s">
         <v>37</v>
@@ -4921,7 +4945,7 @@
         <v>46296</v>
       </c>
       <c r="E82" s="29" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F82" s="29" t="s">
         <v>52</v>
@@ -4930,7 +4954,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="31" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I82" s="28" t="s">
         <v>37</v>
@@ -4950,7 +4974,7 @@
         <v>46296</v>
       </c>
       <c r="E83" s="29" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F83" s="29" t="s">
         <v>6</v>
@@ -4959,7 +4983,7 @@
         <v>320</v>
       </c>
       <c r="H83" s="31" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="I83" s="28" t="s">
         <v>39</v>
@@ -4979,7 +5003,7 @@
         <v>46293</v>
       </c>
       <c r="E84" s="29" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F84" s="29" t="s">
         <v>6</v>
@@ -4988,7 +5012,7 @@
         <v>10</v>
       </c>
       <c r="H84" s="31" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I84" s="28" t="s">
         <v>41</v>
@@ -5008,7 +5032,7 @@
         <v>46296</v>
       </c>
       <c r="E85" s="29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F85" s="29" t="s">
         <v>52</v>
@@ -5017,7 +5041,7 @@
         <v>61</v>
       </c>
       <c r="H85" s="31" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I85" s="28" t="s">
         <v>39</v>
@@ -5037,7 +5061,7 @@
         <v>46295</v>
       </c>
       <c r="E86" s="29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F86" s="29" t="s">
         <v>52</v>
@@ -5046,7 +5070,7 @@
         <v>3</v>
       </c>
       <c r="H86" s="31" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I86" s="28" t="s">
         <v>37</v>
@@ -5066,7 +5090,7 @@
         <v>46295</v>
       </c>
       <c r="E87" s="29" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F87" s="29" t="s">
         <v>52</v>
@@ -5075,7 +5099,7 @@
         <v>12</v>
       </c>
       <c r="H87" s="31" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I87" s="28" t="s">
         <v>37</v>
@@ -5095,7 +5119,7 @@
         <v>46295</v>
       </c>
       <c r="E88" s="29" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F88" s="29" t="s">
         <v>6</v>
@@ -5104,10 +5128,126 @@
         <v>135</v>
       </c>
       <c r="H88" s="31" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I88" s="28" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B89" s="30">
+        <v>46233</v>
+      </c>
+      <c r="C89" s="30">
+        <v>46238</v>
+      </c>
+      <c r="D89" s="30">
+        <v>46339</v>
+      </c>
+      <c r="E89" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="F89" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="G89" s="31">
+        <v>82</v>
+      </c>
+      <c r="H89" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="I89" s="28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B90" s="30">
+        <v>46238</v>
+      </c>
+      <c r="C90" s="30">
+        <v>46238</v>
+      </c>
+      <c r="D90" s="30">
+        <v>46300</v>
+      </c>
+      <c r="E90" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="F90" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G90" s="31">
+        <v>65</v>
+      </c>
+      <c r="H90" s="31" t="s">
+        <v>244</v>
+      </c>
+      <c r="I90" s="28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B91" s="30">
+        <v>46239</v>
+      </c>
+      <c r="C91" s="30">
+        <v>46239</v>
+      </c>
+      <c r="D91" s="30">
+        <v>46300</v>
+      </c>
+      <c r="E91" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="F91" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G91" s="31">
+        <v>18</v>
+      </c>
+      <c r="H91" s="31" t="s">
+        <v>246</v>
+      </c>
+      <c r="I91" s="28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B92" s="30">
+        <v>46239</v>
+      </c>
+      <c r="C92" s="30">
+        <v>46239</v>
+      </c>
+      <c r="D92" s="30">
+        <v>46300</v>
+      </c>
+      <c r="E92" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="F92" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="G92" s="31">
+        <v>74</v>
+      </c>
+      <c r="H92" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="I92" s="28" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -5124,7 +5264,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I88</xm:sqref>
+          <xm:sqref>I3:I92</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5236,7 +5376,7 @@
     <col min="1" max="1" width="31.140625" customWidth="1"/>
     <col min="2" max="2" width="8.42578125" style="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
@@ -5245,7 +5385,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E1"/>
     </row>
@@ -5660,7 +5800,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1857C4B4-7999-4C2D-AC48-24F916F1F539}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{048538A6-0B10-4D3A-B99D-737C2F241CB8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -5679,7 +5819,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0A027E7-D676-4CA5-B18E-07F77CCEDBBC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E35467DD-C711-463C-ABEE-9093F8F123DA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -5687,16 +5827,16 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2857766C-E7F4-45B8-996B-0092792850F1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A67F7B33-A08D-49E6-8712-D8D01041F356}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
@@ -5705,6 +5845,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" contentBits="0" removed="0"/>
+  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" removed="0"/>
 </clbl:labelList>
 </file>
--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA3ADFB7-02FE-4466-9A8E-62C41DFDBA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5793131E-7C4B-4084-A004-C65E68000160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="268">
   <si>
     <t>County/Parish</t>
   </si>
@@ -848,6 +848,119 @@
     <t>101 California Street, Suite 500  San Francisco CA 94111</t>
   </si>
   <si>
+    <t>San Francisico Pretrial Diversion Project, Inc.</t>
+  </si>
+  <si>
+    <t>1200 Folsom Street  San Francisco CA 94103</t>
+  </si>
+  <si>
+    <t>Nutanix, Inc.</t>
+  </si>
+  <si>
+    <t>1740 Technology Drive  San Jose CA 95110</t>
+  </si>
+  <si>
+    <t>Eclipse Advantage, LLC</t>
+  </si>
+  <si>
+    <t>5540 East 4th Street  Ontario CA 91764</t>
+  </si>
+  <si>
+    <t>Salesforce, Inc.</t>
+  </si>
+  <si>
+    <t>415 Mission Street  San Francisco CA 94105</t>
+  </si>
+  <si>
+    <t>Yerba Mate Co., LLC - Santa Cruz</t>
+  </si>
+  <si>
+    <t>LAZ Parking California (9610 Sky Way)</t>
+  </si>
+  <si>
+    <t>9610 Sky Way  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>LAZ Parking California (5455 West 111th Street)</t>
+  </si>
+  <si>
+    <t>5455 West 111th Street  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>LAZ Parking California (5251 West 98th Street)</t>
+  </si>
+  <si>
+    <t>5251 West 98th Street  Los Angeles CA 90045</t>
+  </si>
+  <si>
+    <t>Staples Fulfillment Center</t>
+  </si>
+  <si>
+    <t>16501 Trojan Way  La Mirada CA 90638</t>
+  </si>
+  <si>
+    <t>Essendant Co.</t>
+  </si>
+  <si>
+    <t>4555 Redlands Ave.  Perris CA 92571</t>
+  </si>
+  <si>
+    <t>7021 Roseville Rd.  Sacramento CA 95842</t>
+  </si>
+  <si>
+    <t>567 S Riverside Drive  Modesto CA 95354</t>
+  </si>
+  <si>
+    <t>Napa County</t>
+  </si>
+  <si>
+    <t>Renteria Vineyard Management</t>
+  </si>
+  <si>
+    <t>462 Devlin Road  Napa CA 94558</t>
+  </si>
+  <si>
+    <t>G3 Enterprises</t>
+  </si>
+  <si>
+    <t>500 S. Santa Rosa  Modesto CA 95354</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">WARN REPORT - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>07/01/26 to 08/10/2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I101.</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -867,7 +980,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 08/05/2026
+01/01/2023 - 08/10/2026
 </t>
     </r>
     <r>
@@ -878,68 +991,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through H3.</t>
-    </r>
-  </si>
-  <si>
-    <t>San Francisico Pretrial Diversion Project, Inc.</t>
-  </si>
-  <si>
-    <t>1200 Folsom Street  San Francisco CA 94103</t>
-  </si>
-  <si>
-    <t>Nutanix, Inc.</t>
-  </si>
-  <si>
-    <t>1740 Technology Drive  San Jose CA 95110</t>
-  </si>
-  <si>
-    <t>Eclipse Advantage, LLC</t>
-  </si>
-  <si>
-    <t>5540 East 4th Street  Ontario CA 91764</t>
-  </si>
-  <si>
-    <t>Salesforce, Inc.</t>
-  </si>
-  <si>
-    <t>415 Mission Street  San Francisco CA 94105</t>
-  </si>
-  <si>
-    <t>Yerba Mate Co., LLC - Santa Cruz</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">WARN REPORT - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>07/01/26 to 08/05/2026</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I92.</t>
     </r>
   </si>
 </sst>
@@ -1056,7 +1107,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1073,6 +1124,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0F0"/>
+        <bgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1197,7 +1254,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1302,6 +1359,36 @@
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -2096,8 +2183,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I92" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I92" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I101" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I101" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2518,7 +2605,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>4958</v>
+        <v>5634</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2527,7 +2614,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2536,7 +2623,7 @@
       </c>
       <c r="B5" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2554,7 +2641,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2586,14 +2673,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="50.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -2607,7 +2694,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -4481,7 +4568,7 @@
         <v>46266</v>
       </c>
       <c r="E66" s="29" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F66" s="29" t="s">
         <v>6</v>
@@ -5148,7 +5235,7 @@
         <v>46339</v>
       </c>
       <c r="E89" s="29" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F89" s="29" t="s">
         <v>52</v>
@@ -5157,7 +5244,7 @@
         <v>82</v>
       </c>
       <c r="H89" s="31" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I89" s="28" t="s">
         <v>45</v>
@@ -5177,7 +5264,7 @@
         <v>46300</v>
       </c>
       <c r="E90" s="29" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F90" s="29" t="s">
         <v>6</v>
@@ -5186,7 +5273,7 @@
         <v>65</v>
       </c>
       <c r="H90" s="31" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I90" s="28" t="s">
         <v>38</v>
@@ -5206,7 +5293,7 @@
         <v>46300</v>
       </c>
       <c r="E91" s="29" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F91" s="29" t="s">
         <v>6</v>
@@ -5215,7 +5302,7 @@
         <v>18</v>
       </c>
       <c r="H91" s="31" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I91" s="28" t="s">
         <v>43</v>
@@ -5235,7 +5322,7 @@
         <v>46300</v>
       </c>
       <c r="E92" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F92" s="29" t="s">
         <v>6</v>
@@ -5244,10 +5331,271 @@
         <v>74</v>
       </c>
       <c r="H92" s="31" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="I92" s="28" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93" s="38">
+        <v>46240</v>
+      </c>
+      <c r="C93" s="38">
+        <v>46240</v>
+      </c>
+      <c r="D93" s="38">
+        <v>46301</v>
+      </c>
+      <c r="E93" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="F93" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="G93" s="41">
+        <v>139</v>
+      </c>
+      <c r="H93" s="42" t="s">
+        <v>250</v>
+      </c>
+      <c r="I93" s="28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" s="43">
+        <v>46240</v>
+      </c>
+      <c r="C94" s="43">
+        <v>46240</v>
+      </c>
+      <c r="D94" s="43">
+        <v>46301</v>
+      </c>
+      <c r="E94" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="F94" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="G94" s="46">
+        <v>58</v>
+      </c>
+      <c r="H94" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="I94" s="28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" s="38">
+        <v>46240</v>
+      </c>
+      <c r="C95" s="38">
+        <v>46240</v>
+      </c>
+      <c r="D95" s="38">
+        <v>46301</v>
+      </c>
+      <c r="E95" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="F95" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="G95" s="41">
+        <v>50</v>
+      </c>
+      <c r="H95" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="I95" s="28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" s="38">
+        <v>46239</v>
+      </c>
+      <c r="C96" s="38">
+        <v>46240</v>
+      </c>
+      <c r="D96" s="38">
+        <v>46304</v>
+      </c>
+      <c r="E96" s="39" t="s">
+        <v>255</v>
+      </c>
+      <c r="F96" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="G96" s="41">
+        <v>109</v>
+      </c>
+      <c r="H96" s="42" t="s">
+        <v>256</v>
+      </c>
+      <c r="I96" s="28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="B97" s="38">
+        <v>46237</v>
+      </c>
+      <c r="C97" s="38">
+        <v>46240</v>
+      </c>
+      <c r="D97" s="38">
+        <v>46298</v>
+      </c>
+      <c r="E97" s="39" t="s">
+        <v>257</v>
+      </c>
+      <c r="F97" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="G97" s="41">
+        <v>4</v>
+      </c>
+      <c r="H97" s="42" t="s">
+        <v>258</v>
+      </c>
+      <c r="I97" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B98" s="38">
+        <v>46237</v>
+      </c>
+      <c r="C98" s="38">
+        <v>46240</v>
+      </c>
+      <c r="D98" s="38">
+        <v>46298</v>
+      </c>
+      <c r="E98" s="39" t="s">
+        <v>257</v>
+      </c>
+      <c r="F98" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="G98" s="41">
+        <v>99</v>
+      </c>
+      <c r="H98" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="I98" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B99" s="43">
+        <v>46224</v>
+      </c>
+      <c r="C99" s="43">
+        <v>46240</v>
+      </c>
+      <c r="D99" s="43">
+        <v>46224</v>
+      </c>
+      <c r="E99" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="F99" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="G99" s="46">
+        <v>60</v>
+      </c>
+      <c r="H99" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="I99" s="28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="B100" s="43">
+        <v>46241</v>
+      </c>
+      <c r="C100" s="43">
+        <v>46241</v>
+      </c>
+      <c r="D100" s="43">
+        <v>46310</v>
+      </c>
+      <c r="E100" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="F100" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="G100" s="46">
+        <v>91</v>
+      </c>
+      <c r="H100" s="47" t="s">
+        <v>263</v>
+      </c>
+      <c r="I100" s="28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B101" s="38">
+        <v>46241</v>
+      </c>
+      <c r="C101" s="38">
+        <v>46244</v>
+      </c>
+      <c r="D101" s="38">
+        <v>46301</v>
+      </c>
+      <c r="E101" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="F101" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="G101" s="41">
+        <v>66</v>
+      </c>
+      <c r="H101" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="I101" s="28" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -5264,7 +5612,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I92</xm:sqref>
+          <xm:sqref>I3:I101</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5385,7 +5733,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="E1"/>
     </row>
@@ -5800,7 +6148,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{048538A6-0B10-4D3A-B99D-737C2F241CB8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27E898B2-03D8-47E5-80B6-68CE85636EAC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -5819,7 +6167,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E35467DD-C711-463C-ABEE-9093F8F123DA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{963127C5-89B2-4462-8394-89B9B2B78CD6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -5827,24 +6175,24 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A67F7B33-A08D-49E6-8712-D8D01041F356}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37BCDC0A-E466-427F-8667-A5FCD14D403E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" removed="0"/>
+  <clbl:label id="{651480e4-deb2-4da5-bc64-7d1e9e1df8e4}" enabled="1" method="Standard" siteId="{06cac249-57c6-4eed-94fd-256abde82b4e}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>
--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5793131E-7C4B-4084-A004-C65E68000160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE6B85FA-6502-4C50-8A39-B9B917ECC02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="323">
   <si>
     <t>County/Parish</t>
   </si>
@@ -848,9 +848,6 @@
     <t>101 California Street, Suite 500  San Francisco CA 94111</t>
   </si>
   <si>
-    <t>San Francisico Pretrial Diversion Project, Inc.</t>
-  </si>
-  <si>
     <t>1200 Folsom Street  San Francisco CA 94103</t>
   </si>
   <si>
@@ -924,6 +921,207 @@
   </si>
   <si>
     <t>500 S. Santa Rosa  Modesto CA 95354</t>
+  </si>
+  <si>
+    <t>San Francisco Pretrial Diversion Project, Inc.</t>
+  </si>
+  <si>
+    <t>Bumble Bee Foods, LLC</t>
+  </si>
+  <si>
+    <t>13100 Arctic Circle  Santa Fe Springs CA 90670</t>
+  </si>
+  <si>
+    <t>ZOLL Medical Corporation</t>
+  </si>
+  <si>
+    <t>1100 Bird Center Drive  Palm Springs CA 92262</t>
+  </si>
+  <si>
+    <t>Sharp Metropolitan Medical Campus  - Sharp Memorial Hospital</t>
+  </si>
+  <si>
+    <t>7901 Frost Street  San Diego CA 92123</t>
+  </si>
+  <si>
+    <t>Sharp Metropolitan Medical Campus - Sharp Mesa Vista</t>
+  </si>
+  <si>
+    <t>Sharp Metropolitan Medical Group - Sharp McDonald Center</t>
+  </si>
+  <si>
+    <t>Sharp Metropolitan Medical Campus - Sharp Mary Birch Hospital</t>
+  </si>
+  <si>
+    <t>Sharp Metropolitan Medical Campus - Sharp Outpatient Pavilion</t>
+  </si>
+  <si>
+    <t>Adventist Health Glendale</t>
+  </si>
+  <si>
+    <t>600 S Central Ave.  Glendale CA 91205</t>
+  </si>
+  <si>
+    <t>EBALDC (100 9th Street)</t>
+  </si>
+  <si>
+    <t>100 9th Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (121 E 12th Street)</t>
+  </si>
+  <si>
+    <t>121 E 12th Street  Oakland CA 94606</t>
+  </si>
+  <si>
+    <t>EBALDC (1448 10th Street)</t>
+  </si>
+  <si>
+    <t>1448 10th Street 829 East 19th Street Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (1825 San Pablo Ave., Suite 200)</t>
+  </si>
+  <si>
+    <t>1825 San Pablo Ave., Suite 200  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>EBALDC (188 11th Street)</t>
+  </si>
+  <si>
+    <t>188 11th Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (1935 Seminary Ave)</t>
+  </si>
+  <si>
+    <t>1935 Seminary Ave 2530 International BLVD Oakland CA 94621</t>
+  </si>
+  <si>
+    <t>EBALDC (1955 San Pablo Ave)</t>
+  </si>
+  <si>
+    <t>1955 San Pablo Ave  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>EBALDC (2201 Brush St.)</t>
+  </si>
+  <si>
+    <t>2201 Brush St.  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>EBALDC (2555 International BLVD)</t>
+  </si>
+  <si>
+    <t>2555 International BLVD  Oakland CA 94601</t>
+  </si>
+  <si>
+    <t>EBALDC (283 13th Street)</t>
+  </si>
+  <si>
+    <t>283 13th Street  Oakland CA 94612</t>
+  </si>
+  <si>
+    <t>EBALDC (2946 International BLVD)</t>
+  </si>
+  <si>
+    <t>2946 International BLVD 2618 East 16th Street Oakland CA 94601</t>
+  </si>
+  <si>
+    <t>EBALDC (3501 San Pablo Ave)</t>
+  </si>
+  <si>
+    <t>3501 San Pablo Ave  Oakland CA 94608</t>
+  </si>
+  <si>
+    <t>EBALDC (3850 San Pablo Ave)</t>
+  </si>
+  <si>
+    <t>3850 San Pablo Ave  Emeryville CA 94608</t>
+  </si>
+  <si>
+    <t>EBALDC (700 Willow Street)</t>
+  </si>
+  <si>
+    <t>700 Willow Street 721 Wood Street Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (801 Pine Street)</t>
+  </si>
+  <si>
+    <t>801 Pine Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (918 Clay Street)</t>
+  </si>
+  <si>
+    <t>918 Clay Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>EBALDC (989 Brush Street)</t>
+  </si>
+  <si>
+    <t>989 Brush Street  Oakland CA 94610</t>
+  </si>
+  <si>
+    <t>EBALDC (120 Macdonald Ave)</t>
+  </si>
+  <si>
+    <t>120 Macdonald Ave 907 Lake Street Richmond CA 94801</t>
+  </si>
+  <si>
+    <t>EBALDC (907 Lake Street)</t>
+  </si>
+  <si>
+    <t>907 Lake Street  San Pablo CA 94806</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>WARN REPORT -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+01/01/2023 - 08/17/2026
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through H3.</t>
+    </r>
+  </si>
+  <si>
+    <t>Universal City Studios Productions LLLP</t>
+  </si>
+  <si>
+    <t>Netflix, Inc.</t>
+  </si>
+  <si>
+    <t>5808 W. Sunset Blvd  Los Angeles CA 90028</t>
+  </si>
+  <si>
+    <t>Roskam Baking Company dba Organic Milling</t>
+  </si>
+  <si>
+    <t>305 South Acacia Street  San Dimas CA 91773</t>
   </si>
   <si>
     <r>
@@ -937,7 +1135,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 08/10/2026</t>
+      <t>07/01/26 to 08/17/2026</t>
     </r>
     <r>
       <rPr>
@@ -957,40 +1155,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I101.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>WARN REPORT -</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-01/01/2023 - 08/10/2026
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through H3.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I131.</t>
     </r>
   </si>
 </sst>
@@ -1107,7 +1272,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1124,12 +1289,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F0F0"/>
-        <bgColor rgb="FFF0F0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1254,7 +1413,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1331,9 +1490,6 @@
     <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1344,6 +1500,9 @@
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1361,35 +1520,14 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2183,8 +2321,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I101" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I101" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I131" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I131" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2605,7 +2743,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>5634</v>
+        <v>6354</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2614,7 +2752,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>53</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2641,7 +2779,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2673,14 +2811,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.85546875" style="10" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="50.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -2694,7 +2832,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>266</v>
+        <v>322</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -2728,1162 +2866,1162 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="29">
         <v>46203</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="29">
         <v>46204</v>
       </c>
-      <c r="D3" s="30">
+      <c r="D3" s="29">
         <v>46266</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="30">
         <v>2</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="31" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="29">
         <v>46199</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="29">
         <v>46204</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="29">
         <v>46232</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="31">
+      <c r="F4" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="30">
         <v>103</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="I4" s="32" t="s">
+      <c r="I4" s="31" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="29">
         <v>46203</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="29">
         <v>46204</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>46264</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="31">
+      <c r="F5" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="30">
         <v>35</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="I5" s="32" t="s">
+      <c r="I5" s="31" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>46205</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <v>46205</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <v>46269</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="30">
         <v>31</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="I6" s="31" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>46205</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="29">
         <v>46205</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>46280</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="30">
         <v>7</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="32" t="s">
+      <c r="I7" s="31" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>46205</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>46210</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="29">
         <v>46268</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="30">
         <v>33</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="H8" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="I8" s="32" t="s">
+      <c r="I8" s="31" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <v>46209</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <v>46210</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>46269</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="31">
+      <c r="F9" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="30">
         <v>52</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="I9" s="31" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="29">
         <v>46204</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="29">
         <v>46211</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="29">
         <v>46266</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="31">
+      <c r="F10" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="30">
         <v>180</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="32" t="s">
+      <c r="I10" s="31" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <v>46210</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="29">
         <v>46211</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="29">
         <v>46273</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="30">
         <v>212</v>
       </c>
-      <c r="H11" s="29" t="s">
+      <c r="H11" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="32" t="s">
+      <c r="I11" s="31" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="29">
         <v>46212</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <v>46212</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <v>46274</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="30">
         <v>80</v>
       </c>
-      <c r="H12" s="31" t="s">
+      <c r="H12" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <v>46212</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="29">
         <v>46212</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="29">
         <v>46272</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="30">
         <v>96</v>
       </c>
-      <c r="H13" s="31" t="s">
+      <c r="H13" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="28" t="s">
+      <c r="I13" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="29">
         <v>46213</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="29">
         <v>46213</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>46265</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="31">
-        <v>6</v>
-      </c>
-      <c r="H14" s="31" t="s">
+      <c r="G14" s="30">
+        <v>6</v>
+      </c>
+      <c r="H14" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I14" s="32" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="29">
         <v>46211</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="29">
         <v>46213</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <v>46273</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="30">
         <v>113</v>
       </c>
-      <c r="H15" s="31" t="s">
+      <c r="H15" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="I15" s="32" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="29">
         <v>46210</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="29">
         <v>46216</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <v>46270</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="F16" s="29" t="s">
+      <c r="F16" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="30">
         <v>55</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="32" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="29">
         <v>46209</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="29">
         <v>46216</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="29">
         <v>46268</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="30">
         <v>81</v>
       </c>
-      <c r="H17" s="31" t="s">
+      <c r="H17" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="28" t="s">
+      <c r="I17" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="29">
         <v>46199</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="29">
         <v>46217</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="29">
         <v>46262</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="31">
+      <c r="F18" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="30">
         <v>51</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="I18" s="28" t="s">
+      <c r="I18" s="32" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="29">
         <v>46217</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="29">
         <v>46217</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <v>46279</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="30">
         <v>78</v>
       </c>
-      <c r="H19" s="31" t="s">
+      <c r="H19" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="I19" s="28" t="s">
+      <c r="I19" s="32" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="29">
         <v>46213</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="29">
         <v>46217</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="29">
         <v>46283</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="E20" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="29" t="s">
+      <c r="F20" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="30">
         <v>46</v>
       </c>
-      <c r="H20" s="31" t="s">
+      <c r="H20" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="I20" s="28" t="s">
+      <c r="I20" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="29">
         <v>46217</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="29">
         <v>46217</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="29">
         <v>46276</v>
       </c>
-      <c r="E21" s="29" t="s">
+      <c r="E21" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="31">
+      <c r="F21" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="30">
         <v>28</v>
       </c>
-      <c r="H21" s="31" t="s">
+      <c r="H21" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="I21" s="28" t="s">
+      <c r="I21" s="32" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="29">
         <v>46216</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="29">
         <v>46217</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="29">
         <v>46276</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="30">
         <v>158</v>
       </c>
-      <c r="H22" s="31" t="s">
+      <c r="H22" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="I22" s="28" t="s">
+      <c r="I22" s="32" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="29">
         <v>46217</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="29">
         <v>46218</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="29">
         <v>46276</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="F23" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="31">
+      <c r="F23" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="30">
         <v>31</v>
       </c>
-      <c r="H23" s="31" t="s">
+      <c r="H23" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="28" t="s">
+      <c r="I23" s="32" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="29">
         <v>46217</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="29">
         <v>46218</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="29">
         <v>46295</v>
       </c>
-      <c r="E24" s="29" t="s">
+      <c r="E24" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="30">
         <v>67</v>
       </c>
-      <c r="H24" s="31" t="s">
+      <c r="H24" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="I24" s="28" t="s">
+      <c r="I24" s="32" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="29">
         <v>46218</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="29">
         <v>46218</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="29">
         <v>46279</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="F25" s="29" t="s">
+      <c r="F25" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="30">
         <v>57</v>
       </c>
-      <c r="H25" s="31" t="s">
+      <c r="H25" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="I25" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="29">
         <v>46217</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="29">
         <v>46218</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="29">
         <v>46265</v>
       </c>
-      <c r="E26" s="29" t="s">
+      <c r="E26" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="F26" s="29" t="s">
+      <c r="F26" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="31">
+      <c r="G26" s="30">
         <v>37</v>
       </c>
-      <c r="H26" s="31" t="s">
+      <c r="H26" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="I26" s="28" t="s">
+      <c r="I26" s="32" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="29">
         <v>46219</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="29">
         <v>46219</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="29">
         <v>46281</v>
       </c>
-      <c r="E27" s="29" t="s">
+      <c r="E27" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="30">
         <v>5</v>
       </c>
-      <c r="H27" s="31" t="s">
+      <c r="H27" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="I27" s="28" t="s">
+      <c r="I27" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="29">
         <v>46220</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="29">
         <v>46220</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="29">
         <v>46262</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="F28" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G28" s="31">
+      <c r="F28" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G28" s="30">
         <v>3</v>
       </c>
-      <c r="H28" s="31" t="s">
+      <c r="H28" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="I28" s="28" t="s">
+      <c r="I28" s="32" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="29">
         <v>46220</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="29">
         <v>46220</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="29">
         <v>46262</v>
       </c>
-      <c r="E29" s="29" t="s">
+      <c r="E29" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="31">
+      <c r="F29" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="30">
         <v>5</v>
       </c>
-      <c r="H29" s="31" t="s">
+      <c r="H29" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="I29" s="28" t="s">
+      <c r="I29" s="32" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="29">
         <v>46220</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="29">
         <v>46220</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="29">
         <v>46262</v>
       </c>
-      <c r="E30" s="29" t="s">
+      <c r="E30" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="F30" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="31">
+      <c r="F30" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30" s="30">
         <v>87</v>
       </c>
-      <c r="H30" s="31" t="s">
+      <c r="H30" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="I30" s="28" t="s">
+      <c r="I30" s="32" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="29">
         <v>46220</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="29">
         <v>46220</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="29">
         <v>46262</v>
       </c>
-      <c r="E31" s="29" t="s">
+      <c r="E31" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="F31" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" s="31">
+      <c r="F31" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="30">
         <v>55</v>
       </c>
-      <c r="H31" s="31" t="s">
+      <c r="H31" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="I31" s="28" t="s">
+      <c r="I31" s="32" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="29">
         <v>46219</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="29">
         <v>46220</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="29">
         <v>46234</v>
       </c>
-      <c r="E32" s="29" t="s">
+      <c r="E32" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="F32" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" s="31">
+      <c r="F32" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="30">
         <v>94</v>
       </c>
-      <c r="H32" s="31" t="s">
+      <c r="H32" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="I32" s="28" t="s">
+      <c r="I32" s="32" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="29">
         <v>46220</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="29">
         <v>46220</v>
       </c>
-      <c r="D33" s="30">
+      <c r="D33" s="29">
         <v>46285</v>
       </c>
-      <c r="E33" s="29" t="s">
+      <c r="E33" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="F33" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G33" s="31">
+      <c r="F33" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G33" s="30">
         <v>253</v>
       </c>
-      <c r="H33" s="31" t="s">
+      <c r="H33" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="I33" s="28" t="s">
+      <c r="I33" s="32" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="29">
         <v>46218</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="29">
         <v>46220</v>
       </c>
-      <c r="D34" s="30">
+      <c r="D34" s="29">
         <v>46283</v>
       </c>
-      <c r="E34" s="29" t="s">
+      <c r="E34" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="F34" s="29" t="s">
+      <c r="F34" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="30">
         <v>71</v>
       </c>
-      <c r="H34" s="31" t="s">
+      <c r="H34" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="I34" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <v>46220</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="29">
         <v>46223</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="29">
         <v>46296</v>
       </c>
-      <c r="E35" s="29" t="s">
+      <c r="E35" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="F35" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G35" s="31">
+      <c r="F35" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G35" s="30">
         <v>76</v>
       </c>
-      <c r="H35" s="31" t="s">
+      <c r="H35" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="I35" s="28" t="s">
+      <c r="I35" s="32" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="29">
         <v>46217</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="29">
         <v>46223</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="29">
         <v>46280</v>
       </c>
-      <c r="E36" s="29" t="s">
+      <c r="E36" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F36" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="31">
+      <c r="G36" s="30">
         <v>198</v>
       </c>
-      <c r="H36" s="31" t="s">
+      <c r="H36" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="I36" s="28" t="s">
+      <c r="I36" s="32" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <v>46223</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="29">
         <v>46223</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="29">
         <v>46286</v>
       </c>
-      <c r="E37" s="29" t="s">
+      <c r="E37" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="F37" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G37" s="31">
+      <c r="F37" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G37" s="30">
         <v>25</v>
       </c>
-      <c r="H37" s="31" t="s">
+      <c r="H37" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="I37" s="28" t="s">
+      <c r="I37" s="32" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="29">
         <v>46217</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="29">
         <v>46223</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="29">
         <v>46278</v>
       </c>
-      <c r="E38" s="29" t="s">
+      <c r="E38" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="30">
         <v>49</v>
       </c>
-      <c r="H38" s="31" t="s">
+      <c r="H38" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="I38" s="28" t="s">
+      <c r="I38" s="32" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="29">
         <v>46224</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="29">
         <v>46224</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="29">
         <v>46285</v>
       </c>
-      <c r="E39" s="29" t="s">
+      <c r="E39" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="F39" s="29" t="s">
+      <c r="F39" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="30">
         <v>61</v>
       </c>
-      <c r="H39" s="31" t="s">
+      <c r="H39" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="I39" s="28" t="s">
+      <c r="I39" s="32" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="29">
         <v>46224</v>
       </c>
-      <c r="C40" s="30">
+      <c r="C40" s="29">
         <v>46225</v>
       </c>
-      <c r="D40" s="30">
+      <c r="D40" s="29">
         <v>46291</v>
       </c>
-      <c r="E40" s="29" t="s">
+      <c r="E40" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="F40" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G40" s="31">
+      <c r="F40" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G40" s="30">
         <v>108</v>
       </c>
-      <c r="H40" s="31" t="s">
+      <c r="H40" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="I40" s="28" t="s">
+      <c r="I40" s="32" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="29">
         <v>46225</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="29">
         <v>46225</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="29">
         <v>46285</v>
       </c>
-      <c r="E41" s="29" t="s">
+      <c r="E41" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="F41" s="29" t="s">
+      <c r="F41" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="30">
         <v>51</v>
       </c>
-      <c r="H41" s="31" t="s">
+      <c r="H41" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="I41" s="28" t="s">
+      <c r="I41" s="32" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="29">
         <v>46225</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="29">
         <v>46225</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="29">
         <v>46285</v>
       </c>
-      <c r="E42" s="29" t="s">
+      <c r="E42" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="F42" s="29" t="s">
+      <c r="F42" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="30">
         <v>7</v>
       </c>
-      <c r="H42" s="31" t="s">
+      <c r="H42" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="I42" s="28" t="s">
+      <c r="I42" s="32" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3912,7 +4050,7 @@
       <c r="H43" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="I43" s="28" t="s">
+      <c r="I43" s="32" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3941,7 +4079,7 @@
       <c r="H44" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="I44" s="28" t="s">
+      <c r="I44" s="32" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3970,7 +4108,7 @@
       <c r="H45" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="I45" s="28" t="s">
+      <c r="I45" s="32" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3999,7 +4137,7 @@
       <c r="H46" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="I46" s="28" t="s">
+      <c r="I46" s="32" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4028,7 +4166,7 @@
       <c r="H47" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="I47" s="28" t="s">
+      <c r="I47" s="32" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4057,7 +4195,7 @@
       <c r="H48" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="I48" s="28" t="s">
+      <c r="I48" s="32" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4086,7 +4224,7 @@
       <c r="H49" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="I49" s="28" t="s">
+      <c r="I49" s="32" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4115,7 +4253,7 @@
       <c r="H50" s="36" t="s">
         <v>166</v>
       </c>
-      <c r="I50" s="28" t="s">
+      <c r="I50" s="32" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4144,7 +4282,7 @@
       <c r="H51" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="I51" s="28" t="s">
+      <c r="I51" s="32" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4173,7 +4311,7 @@
       <c r="H52" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="I52" s="28" t="s">
+      <c r="I52" s="32" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4202,7 +4340,7 @@
       <c r="H53" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="I53" s="28" t="s">
+      <c r="I53" s="32" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4231,1109 +4369,1109 @@
       <c r="H54" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="I54" s="28" t="s">
+      <c r="I54" s="32" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="29" t="s">
+      <c r="A55" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="30">
+      <c r="B55" s="29">
         <v>46227</v>
       </c>
-      <c r="C55" s="30">
+      <c r="C55" s="29">
         <v>46231</v>
       </c>
-      <c r="D55" s="30">
+      <c r="D55" s="29">
         <v>46295</v>
       </c>
-      <c r="E55" s="29" t="s">
+      <c r="E55" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="F55" s="29" t="s">
+      <c r="F55" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G55" s="31">
+      <c r="G55" s="30">
         <v>164</v>
       </c>
-      <c r="H55" s="31" t="s">
+      <c r="H55" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="I55" s="28" t="s">
+      <c r="I55" s="32" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="B56" s="30">
+      <c r="B56" s="29">
         <v>46230</v>
       </c>
-      <c r="C56" s="30">
+      <c r="C56" s="29">
         <v>46231</v>
       </c>
-      <c r="D56" s="30">
+      <c r="D56" s="29">
         <v>46266</v>
       </c>
-      <c r="E56" s="29" t="s">
+      <c r="E56" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="F56" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="31">
+      <c r="F56" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="30">
         <v>4</v>
       </c>
-      <c r="H56" s="31" t="s">
+      <c r="H56" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="I56" s="28" t="s">
+      <c r="I56" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="29" t="s">
+      <c r="A57" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="B57" s="30">
+      <c r="B57" s="29">
         <v>46230</v>
       </c>
-      <c r="C57" s="30">
+      <c r="C57" s="29">
         <v>46231</v>
       </c>
-      <c r="D57" s="30">
+      <c r="D57" s="29">
         <v>46266</v>
       </c>
-      <c r="E57" s="29" t="s">
+      <c r="E57" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="F57" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G57" s="31">
+      <c r="F57" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="30">
         <v>1</v>
       </c>
-      <c r="H57" s="31" t="s">
+      <c r="H57" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="I57" s="28" t="s">
+      <c r="I57" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B58" s="30">
+      <c r="B58" s="29">
         <v>46230</v>
       </c>
-      <c r="C58" s="30">
+      <c r="C58" s="29">
         <v>46231</v>
       </c>
-      <c r="D58" s="30">
+      <c r="D58" s="29">
         <v>46266</v>
       </c>
-      <c r="E58" s="29" t="s">
+      <c r="E58" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="F58" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G58" s="31">
-        <v>6</v>
-      </c>
-      <c r="H58" s="31" t="s">
+      <c r="F58" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="30">
+        <v>6</v>
+      </c>
+      <c r="H58" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="I58" s="28" t="s">
+      <c r="I58" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="29" t="s">
+      <c r="A59" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B59" s="30">
+      <c r="B59" s="29">
         <v>46230</v>
       </c>
-      <c r="C59" s="30">
+      <c r="C59" s="29">
         <v>46231</v>
       </c>
-      <c r="D59" s="30">
+      <c r="D59" s="29">
         <v>46266</v>
       </c>
-      <c r="E59" s="29" t="s">
+      <c r="E59" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="F59" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" s="31">
+      <c r="F59" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="30">
         <v>2</v>
       </c>
-      <c r="H59" s="31" t="s">
+      <c r="H59" s="30" t="s">
         <v>186</v>
       </c>
-      <c r="I59" s="28" t="s">
+      <c r="I59" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="29" t="s">
+      <c r="A60" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B60" s="30">
+      <c r="B60" s="29">
         <v>46230</v>
       </c>
-      <c r="C60" s="30">
+      <c r="C60" s="29">
         <v>46231</v>
       </c>
-      <c r="D60" s="30">
+      <c r="D60" s="29">
         <v>46266</v>
       </c>
-      <c r="E60" s="29" t="s">
+      <c r="E60" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="F60" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G60" s="31">
+      <c r="F60" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="30">
         <v>1</v>
       </c>
-      <c r="H60" s="31" t="s">
+      <c r="H60" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="I60" s="28" t="s">
+      <c r="I60" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="29" t="s">
+      <c r="A61" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="B61" s="30">
+      <c r="B61" s="29">
         <v>46230</v>
       </c>
-      <c r="C61" s="30">
+      <c r="C61" s="29">
         <v>46231</v>
       </c>
-      <c r="D61" s="30">
+      <c r="D61" s="29">
         <v>46266</v>
       </c>
-      <c r="E61" s="29" t="s">
+      <c r="E61" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="F61" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G61" s="31">
+      <c r="F61" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="30">
         <v>2</v>
       </c>
-      <c r="H61" s="31" t="s">
+      <c r="H61" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="I61" s="28" t="s">
+      <c r="I61" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="29" t="s">
+      <c r="A62" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="30">
+      <c r="B62" s="29">
         <v>46230</v>
       </c>
-      <c r="C62" s="30">
+      <c r="C62" s="29">
         <v>46231</v>
       </c>
-      <c r="D62" s="30">
+      <c r="D62" s="29">
         <v>46266</v>
       </c>
-      <c r="E62" s="29" t="s">
+      <c r="E62" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="F62" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G62" s="31">
+      <c r="F62" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="30">
         <v>3</v>
       </c>
-      <c r="H62" s="31" t="s">
+      <c r="H62" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="I62" s="28" t="s">
+      <c r="I62" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="29" t="s">
+      <c r="A63" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B63" s="30">
+      <c r="B63" s="29">
         <v>46230</v>
       </c>
-      <c r="C63" s="30">
+      <c r="C63" s="29">
         <v>46231</v>
       </c>
-      <c r="D63" s="30">
+      <c r="D63" s="29">
         <v>46266</v>
       </c>
-      <c r="E63" s="29" t="s">
+      <c r="E63" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="F63" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G63" s="31">
+      <c r="F63" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G63" s="30">
         <v>1</v>
       </c>
-      <c r="H63" s="31" t="s">
+      <c r="H63" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="I63" s="28" t="s">
+      <c r="I63" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="B64" s="30">
+      <c r="B64" s="29">
         <v>46230</v>
       </c>
-      <c r="C64" s="30">
+      <c r="C64" s="29">
         <v>46231</v>
       </c>
-      <c r="D64" s="30">
+      <c r="D64" s="29">
         <v>46266</v>
       </c>
-      <c r="E64" s="29" t="s">
+      <c r="E64" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="F64" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" s="31">
+      <c r="F64" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="30">
         <v>1</v>
       </c>
-      <c r="H64" s="31" t="s">
+      <c r="H64" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="I64" s="28" t="s">
+      <c r="I64" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="29" t="s">
+      <c r="A65" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="B65" s="30">
+      <c r="B65" s="29">
         <v>46230</v>
       </c>
-      <c r="C65" s="30">
+      <c r="C65" s="29">
         <v>46231</v>
       </c>
-      <c r="D65" s="30">
+      <c r="D65" s="29">
         <v>46266</v>
       </c>
-      <c r="E65" s="29" t="s">
+      <c r="E65" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="F65" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="31">
+      <c r="F65" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="30">
         <v>1</v>
       </c>
-      <c r="H65" s="31" t="s">
+      <c r="H65" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="I65" s="28" t="s">
+      <c r="I65" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="B66" s="30">
+      <c r="B66" s="29">
         <v>46230</v>
       </c>
-      <c r="C66" s="30">
+      <c r="C66" s="29">
         <v>46231</v>
       </c>
-      <c r="D66" s="30">
+      <c r="D66" s="29">
         <v>46266</v>
       </c>
-      <c r="E66" s="29" t="s">
-        <v>248</v>
-      </c>
-      <c r="F66" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G66" s="31">
+      <c r="E66" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="F66" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="30">
         <v>1</v>
       </c>
-      <c r="H66" s="31" t="s">
+      <c r="H66" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="I66" s="28" t="s">
+      <c r="I66" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="29" t="s">
+      <c r="A67" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B67" s="30">
+      <c r="B67" s="29">
         <v>46230</v>
       </c>
-      <c r="C67" s="30">
+      <c r="C67" s="29">
         <v>46231</v>
       </c>
-      <c r="D67" s="30">
+      <c r="D67" s="29">
         <v>46266</v>
       </c>
-      <c r="E67" s="29" t="s">
+      <c r="E67" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="F67" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G67" s="31">
+      <c r="F67" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="30">
         <v>1</v>
       </c>
-      <c r="H67" s="31" t="s">
+      <c r="H67" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="I67" s="28" t="s">
+      <c r="I67" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="B68" s="30">
+      <c r="B68" s="29">
         <v>46230</v>
       </c>
-      <c r="C68" s="30">
+      <c r="C68" s="29">
         <v>46231</v>
       </c>
-      <c r="D68" s="30">
+      <c r="D68" s="29">
         <v>46266</v>
       </c>
-      <c r="E68" s="29" t="s">
+      <c r="E68" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="F68" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G68" s="31">
+      <c r="F68" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="30">
         <v>1</v>
       </c>
-      <c r="H68" s="31" t="s">
+      <c r="H68" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="I68" s="28" t="s">
+      <c r="I68" s="32" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="B69" s="30">
+      <c r="B69" s="29">
         <v>46231</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C69" s="29">
         <v>46231</v>
       </c>
-      <c r="D69" s="30">
+      <c r="D69" s="29">
         <v>46293</v>
       </c>
-      <c r="E69" s="29" t="s">
+      <c r="E69" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="F69" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G69" s="31">
+      <c r="F69" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G69" s="30">
         <v>154</v>
       </c>
-      <c r="H69" s="31" t="s">
+      <c r="H69" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="I69" s="28" t="s">
+      <c r="I69" s="32" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="29" t="s">
+      <c r="A70" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="B70" s="30">
+      <c r="B70" s="29">
         <v>46231</v>
       </c>
-      <c r="C70" s="30">
+      <c r="C70" s="29">
         <v>46231</v>
       </c>
-      <c r="D70" s="30">
+      <c r="D70" s="29">
         <v>46293</v>
       </c>
-      <c r="E70" s="29" t="s">
+      <c r="E70" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="F70" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G70" s="31">
+      <c r="F70" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="30">
         <v>133</v>
       </c>
-      <c r="H70" s="31" t="s">
+      <c r="H70" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="I70" s="28" t="s">
+      <c r="I70" s="32" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="29" t="s">
+      <c r="A71" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="B71" s="30">
+      <c r="B71" s="29">
         <v>46224</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C71" s="29">
         <v>46231</v>
       </c>
-      <c r="D71" s="30">
+      <c r="D71" s="29">
         <v>46286</v>
       </c>
-      <c r="E71" s="29" t="s">
+      <c r="E71" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="F71" s="29" t="s">
+      <c r="F71" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="G71" s="31">
+      <c r="G71" s="30">
         <v>55</v>
       </c>
-      <c r="H71" s="31" t="s">
+      <c r="H71" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="I71" s="28" t="s">
+      <c r="I71" s="32" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="29" t="s">
+      <c r="A72" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B72" s="30">
+      <c r="B72" s="29">
         <v>46232</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C72" s="29">
         <v>46232</v>
       </c>
-      <c r="D72" s="30">
+      <c r="D72" s="29">
         <v>46293</v>
       </c>
-      <c r="E72" s="29" t="s">
+      <c r="E72" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="F72" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="31">
+      <c r="F72" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="30">
         <v>68</v>
       </c>
-      <c r="H72" s="31" t="s">
+      <c r="H72" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="I72" s="28" t="s">
+      <c r="I72" s="32" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="29" t="s">
+      <c r="A73" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="B73" s="30">
+      <c r="B73" s="29">
         <v>46232</v>
       </c>
-      <c r="C73" s="30">
+      <c r="C73" s="29">
         <v>46232</v>
       </c>
-      <c r="D73" s="30">
+      <c r="D73" s="29">
         <v>46294</v>
       </c>
-      <c r="E73" s="29" t="s">
+      <c r="E73" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="F73" s="29" t="s">
+      <c r="F73" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G73" s="31">
+      <c r="G73" s="30">
         <v>62</v>
       </c>
-      <c r="H73" s="31" t="s">
+      <c r="H73" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="I73" s="28" t="s">
+      <c r="I73" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="29" t="s">
+      <c r="A74" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B74" s="30">
+      <c r="B74" s="29">
         <v>46231</v>
       </c>
-      <c r="C74" s="30">
+      <c r="C74" s="29">
         <v>46232</v>
       </c>
-      <c r="D74" s="30">
+      <c r="D74" s="29">
         <v>46293</v>
       </c>
-      <c r="E74" s="29" t="s">
+      <c r="E74" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="F74" s="29" t="s">
+      <c r="F74" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G74" s="31">
+      <c r="G74" s="30">
         <v>54</v>
       </c>
-      <c r="H74" s="31" t="s">
+      <c r="H74" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="I74" s="28" t="s">
+      <c r="I74" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="29" t="s">
+      <c r="A75" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="B75" s="30">
+      <c r="B75" s="29">
         <v>46231</v>
       </c>
-      <c r="C75" s="30">
+      <c r="C75" s="29">
         <v>46233</v>
       </c>
-      <c r="D75" s="30">
+      <c r="D75" s="29">
         <v>46299</v>
       </c>
-      <c r="E75" s="29" t="s">
+      <c r="E75" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="F75" s="29" t="s">
+      <c r="F75" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G75" s="31">
+      <c r="G75" s="30">
         <v>47</v>
       </c>
-      <c r="H75" s="31" t="s">
+      <c r="H75" s="30" t="s">
         <v>218</v>
       </c>
-      <c r="I75" s="28" t="s">
+      <c r="I75" s="32" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="29" t="s">
+      <c r="A76" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B76" s="30">
+      <c r="B76" s="29">
         <v>46231</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C76" s="29">
         <v>46233</v>
       </c>
-      <c r="D76" s="30">
+      <c r="D76" s="29">
         <v>46295</v>
       </c>
-      <c r="E76" s="29" t="s">
+      <c r="E76" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="F76" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G76" s="31">
+      <c r="F76" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G76" s="30">
         <v>41</v>
       </c>
-      <c r="H76" s="31" t="s">
+      <c r="H76" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="I76" s="28" t="s">
+      <c r="I76" s="32" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="29" t="s">
+      <c r="A77" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="B77" s="30">
+      <c r="B77" s="29">
         <v>46231</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C77" s="29">
         <v>46233</v>
       </c>
-      <c r="D77" s="30">
+      <c r="D77" s="29">
         <v>46295</v>
       </c>
-      <c r="E77" s="29" t="s">
+      <c r="E77" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="F77" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G77" s="31">
+      <c r="F77" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="30">
         <v>15</v>
       </c>
-      <c r="H77" s="31" t="s">
+      <c r="H77" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="I77" s="28" t="s">
+      <c r="I77" s="32" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="29" t="s">
+      <c r="A78" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="B78" s="30">
+      <c r="B78" s="29">
         <v>46234</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C78" s="29">
         <v>46234</v>
       </c>
-      <c r="D78" s="30">
+      <c r="D78" s="29">
         <v>46296</v>
       </c>
-      <c r="E78" s="29" t="s">
+      <c r="E78" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="F78" s="29" t="s">
+      <c r="F78" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G78" s="31">
+      <c r="G78" s="30">
         <v>34</v>
       </c>
-      <c r="H78" s="31" t="s">
+      <c r="H78" s="30" t="s">
         <v>223</v>
       </c>
-      <c r="I78" s="28" t="s">
+      <c r="I78" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="29" t="s">
+      <c r="A79" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="B79" s="30">
+      <c r="B79" s="29">
         <v>46234</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C79" s="29">
         <v>46234</v>
       </c>
-      <c r="D79" s="30">
+      <c r="D79" s="29">
         <v>46296</v>
       </c>
-      <c r="E79" s="29" t="s">
+      <c r="E79" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="F79" s="29" t="s">
+      <c r="F79" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G79" s="31">
+      <c r="G79" s="30">
         <v>12</v>
       </c>
-      <c r="H79" s="31" t="s">
+      <c r="H79" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="I79" s="28" t="s">
+      <c r="I79" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="29" t="s">
+      <c r="A80" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="B80" s="30">
+      <c r="B80" s="29">
         <v>46234</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C80" s="29">
         <v>46234</v>
       </c>
-      <c r="D80" s="30">
+      <c r="D80" s="29">
         <v>46296</v>
       </c>
-      <c r="E80" s="29" t="s">
+      <c r="E80" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="F80" s="29" t="s">
+      <c r="F80" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G80" s="31">
+      <c r="G80" s="30">
         <v>15</v>
       </c>
-      <c r="H80" s="31" t="s">
+      <c r="H80" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="I80" s="28" t="s">
+      <c r="I80" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="29" t="s">
+      <c r="A81" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="B81" s="30">
+      <c r="B81" s="29">
         <v>46234</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C81" s="29">
         <v>46234</v>
       </c>
-      <c r="D81" s="30">
+      <c r="D81" s="29">
         <v>46296</v>
       </c>
-      <c r="E81" s="29" t="s">
+      <c r="E81" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="F81" s="29" t="s">
+      <c r="F81" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G81" s="31">
+      <c r="G81" s="30">
         <v>1</v>
       </c>
-      <c r="H81" s="31" t="s">
+      <c r="H81" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="I81" s="28" t="s">
+      <c r="I81" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="29" t="s">
+      <c r="A82" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="B82" s="30">
+      <c r="B82" s="29">
         <v>46234</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C82" s="29">
         <v>46234</v>
       </c>
-      <c r="D82" s="30">
+      <c r="D82" s="29">
         <v>46296</v>
       </c>
-      <c r="E82" s="29" t="s">
+      <c r="E82" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="F82" s="29" t="s">
+      <c r="F82" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G82" s="31">
+      <c r="G82" s="30">
         <v>1</v>
       </c>
-      <c r="H82" s="31" t="s">
+      <c r="H82" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="I82" s="28" t="s">
+      <c r="I82" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="29" t="s">
+      <c r="A83" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B83" s="30">
+      <c r="B83" s="29">
         <v>46234</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C83" s="29">
         <v>46234</v>
       </c>
-      <c r="D83" s="30">
+      <c r="D83" s="29">
         <v>46296</v>
       </c>
-      <c r="E83" s="29" t="s">
+      <c r="E83" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="F83" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G83" s="31">
+      <c r="F83" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G83" s="30">
         <v>320</v>
       </c>
-      <c r="H83" s="31" t="s">
+      <c r="H83" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="I83" s="28" t="s">
+      <c r="I83" s="32" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="29" t="s">
+      <c r="A84" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B84" s="30">
+      <c r="B84" s="29">
         <v>46233</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C84" s="29">
         <v>46234</v>
       </c>
-      <c r="D84" s="30">
+      <c r="D84" s="29">
         <v>46293</v>
       </c>
-      <c r="E84" s="29" t="s">
+      <c r="E84" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="F84" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G84" s="31">
+      <c r="F84" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G84" s="30">
         <v>10</v>
       </c>
-      <c r="H84" s="31" t="s">
+      <c r="H84" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="I84" s="28" t="s">
+      <c r="I84" s="32" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="29" t="s">
+      <c r="A85" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="B85" s="30">
+      <c r="B85" s="29">
         <v>46234</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C85" s="29">
         <v>46234</v>
       </c>
-      <c r="D85" s="30">
+      <c r="D85" s="29">
         <v>46296</v>
       </c>
-      <c r="E85" s="29" t="s">
+      <c r="E85" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="F85" s="29" t="s">
+      <c r="F85" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G85" s="31">
+      <c r="G85" s="30">
         <v>61</v>
       </c>
-      <c r="H85" s="31" t="s">
+      <c r="H85" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="I85" s="28" t="s">
+      <c r="I85" s="32" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="29" t="s">
+      <c r="A86" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B86" s="30">
+      <c r="B86" s="29">
         <v>46234</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C86" s="29">
         <v>46237</v>
       </c>
-      <c r="D86" s="30">
+      <c r="D86" s="29">
         <v>46295</v>
       </c>
-      <c r="E86" s="29" t="s">
+      <c r="E86" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="F86" s="29" t="s">
+      <c r="F86" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G86" s="31">
+      <c r="G86" s="30">
         <v>3</v>
       </c>
-      <c r="H86" s="31" t="s">
+      <c r="H86" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="I86" s="28" t="s">
+      <c r="I86" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="29" t="s">
+      <c r="A87" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="B87" s="30">
+      <c r="B87" s="29">
         <v>46234</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C87" s="29">
         <v>46237</v>
       </c>
-      <c r="D87" s="30">
+      <c r="D87" s="29">
         <v>46295</v>
       </c>
-      <c r="E87" s="29" t="s">
+      <c r="E87" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="F87" s="29" t="s">
+      <c r="F87" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G87" s="31">
+      <c r="G87" s="30">
         <v>12</v>
       </c>
-      <c r="H87" s="31" t="s">
+      <c r="H87" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="I87" s="28" t="s">
+      <c r="I87" s="32" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="29" t="s">
+      <c r="A88" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B88" s="30">
+      <c r="B88" s="29">
         <v>46234</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C88" s="29">
         <v>46237</v>
       </c>
-      <c r="D88" s="30">
+      <c r="D88" s="29">
         <v>46295</v>
       </c>
-      <c r="E88" s="29" t="s">
+      <c r="E88" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="F88" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G88" s="31">
+      <c r="F88" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G88" s="30">
         <v>135</v>
       </c>
-      <c r="H88" s="31" t="s">
+      <c r="H88" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="I88" s="28" t="s">
+      <c r="I88" s="32" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="29" t="s">
+      <c r="A89" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B89" s="30">
+      <c r="B89" s="29">
         <v>46233</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C89" s="29">
         <v>46238</v>
       </c>
-      <c r="D89" s="30">
+      <c r="D89" s="29">
         <v>46339</v>
       </c>
-      <c r="E89" s="29" t="s">
+      <c r="E89" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="F89" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G89" s="30">
+        <v>82</v>
+      </c>
+      <c r="H89" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="F89" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="G89" s="31">
-        <v>82</v>
-      </c>
-      <c r="H89" s="31" t="s">
+      <c r="I89" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B90" s="29">
+        <v>46238</v>
+      </c>
+      <c r="C90" s="29">
+        <v>46238</v>
+      </c>
+      <c r="D90" s="29">
+        <v>46300</v>
+      </c>
+      <c r="E90" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="I89" s="28" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="B90" s="30">
-        <v>46238</v>
-      </c>
-      <c r="C90" s="30">
-        <v>46238</v>
-      </c>
-      <c r="D90" s="30">
+      <c r="F90" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G90" s="30">
+        <v>65</v>
+      </c>
+      <c r="H90" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="I90" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B91" s="29">
+        <v>46239</v>
+      </c>
+      <c r="C91" s="29">
+        <v>46239</v>
+      </c>
+      <c r="D91" s="29">
         <v>46300</v>
       </c>
-      <c r="E90" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="F90" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G90" s="31">
-        <v>65</v>
-      </c>
-      <c r="H90" s="31" t="s">
+      <c r="E91" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="I90" s="28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="B91" s="30">
+      <c r="F91" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G91" s="30">
+        <v>18</v>
+      </c>
+      <c r="H91" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="I91" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B92" s="29">
         <v>46239</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C92" s="29">
         <v>46239</v>
       </c>
-      <c r="D91" s="30">
+      <c r="D92" s="29">
         <v>46300</v>
       </c>
-      <c r="E91" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="F91" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G91" s="31">
-        <v>18</v>
-      </c>
-      <c r="H91" s="31" t="s">
+      <c r="E92" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="I91" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="B92" s="30">
-        <v>46239</v>
-      </c>
-      <c r="C92" s="30">
-        <v>46239</v>
-      </c>
-      <c r="D92" s="30">
-        <v>46300</v>
-      </c>
-      <c r="E92" s="29" t="s">
+      <c r="F92" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G92" s="30">
+        <v>74</v>
+      </c>
+      <c r="H92" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="F92" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="G92" s="31">
-        <v>74</v>
-      </c>
-      <c r="H92" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="I92" s="28" t="s">
+      <c r="I92" s="32" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5351,18 +5489,18 @@
         <v>46301</v>
       </c>
       <c r="E93" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="F93" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G93" s="40">
+        <v>139</v>
+      </c>
+      <c r="H93" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="F93" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="G93" s="41">
-        <v>139</v>
-      </c>
-      <c r="H93" s="42" t="s">
-        <v>250</v>
-      </c>
-      <c r="I93" s="28" t="s">
+      <c r="I93" s="32" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5370,28 +5508,28 @@
       <c r="A94" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B94" s="43">
+      <c r="B94" s="38">
         <v>46240</v>
       </c>
-      <c r="C94" s="43">
+      <c r="C94" s="38">
         <v>46240</v>
       </c>
-      <c r="D94" s="43">
+      <c r="D94" s="38">
         <v>46301</v>
       </c>
-      <c r="E94" s="44" t="s">
+      <c r="E94" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="F94" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G94" s="40">
+        <v>58</v>
+      </c>
+      <c r="H94" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="F94" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="G94" s="46">
-        <v>58</v>
-      </c>
-      <c r="H94" s="47" t="s">
-        <v>252</v>
-      </c>
-      <c r="I94" s="28" t="s">
+      <c r="I94" s="32" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5409,18 +5547,18 @@
         <v>46301</v>
       </c>
       <c r="E95" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="F95" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G95" s="40">
+        <v>50</v>
+      </c>
+      <c r="H95" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="F95" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="G95" s="41">
-        <v>50</v>
-      </c>
-      <c r="H95" s="42" t="s">
-        <v>254</v>
-      </c>
-      <c r="I95" s="28" t="s">
+      <c r="I95" s="32" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5438,18 +5576,18 @@
         <v>46304</v>
       </c>
       <c r="E96" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="F96" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G96" s="40">
+        <v>109</v>
+      </c>
+      <c r="H96" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="F96" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="G96" s="41">
-        <v>109</v>
-      </c>
-      <c r="H96" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="I96" s="28" t="s">
+      <c r="I96" s="32" t="s">
         <v>36</v>
       </c>
     </row>
@@ -5467,18 +5605,18 @@
         <v>46298</v>
       </c>
       <c r="E97" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="F97" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G97" s="40">
+        <v>4</v>
+      </c>
+      <c r="H97" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="F97" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="G97" s="41">
-        <v>4</v>
-      </c>
-      <c r="H97" s="42" t="s">
-        <v>258</v>
-      </c>
-      <c r="I97" s="28" t="s">
+      <c r="I97" s="32" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5496,18 +5634,18 @@
         <v>46298</v>
       </c>
       <c r="E98" s="39" t="s">
-        <v>257</v>
-      </c>
-      <c r="F98" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="F98" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="G98" s="41">
+      <c r="G98" s="40">
         <v>99</v>
       </c>
-      <c r="H98" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="I98" s="28" t="s">
+      <c r="H98" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="I98" s="32" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5515,57 +5653,57 @@
       <c r="A99" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="B99" s="43">
+      <c r="B99" s="38">
         <v>46224</v>
       </c>
-      <c r="C99" s="43">
+      <c r="C99" s="38">
         <v>46240</v>
       </c>
-      <c r="D99" s="43">
+      <c r="D99" s="38">
         <v>46224</v>
       </c>
-      <c r="E99" s="44" t="s">
+      <c r="E99" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="F99" s="45" t="s">
+      <c r="F99" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="G99" s="46">
+      <c r="G99" s="40">
         <v>60</v>
       </c>
-      <c r="H99" s="47" t="s">
-        <v>260</v>
-      </c>
-      <c r="I99" s="28" t="s">
+      <c r="H99" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="I99" s="32" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="B100" s="38">
+        <v>46241</v>
+      </c>
+      <c r="C100" s="38">
+        <v>46241</v>
+      </c>
+      <c r="D100" s="38">
+        <v>46310</v>
+      </c>
+      <c r="E100" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="B100" s="43">
-        <v>46241</v>
-      </c>
-      <c r="C100" s="43">
-        <v>46241</v>
-      </c>
-      <c r="D100" s="43">
-        <v>46310</v>
-      </c>
-      <c r="E100" s="44" t="s">
+      <c r="F100" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="G100" s="40">
+        <v>91</v>
+      </c>
+      <c r="H100" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="F100" s="45" t="s">
-        <v>129</v>
-      </c>
-      <c r="G100" s="46">
-        <v>91</v>
-      </c>
-      <c r="H100" s="47" t="s">
-        <v>263</v>
-      </c>
-      <c r="I100" s="28" t="s">
+      <c r="I100" s="32" t="s">
         <v>30</v>
       </c>
     </row>
@@ -5583,18 +5721,888 @@
         <v>46301</v>
       </c>
       <c r="E101" s="39" t="s">
+        <v>263</v>
+      </c>
+      <c r="F101" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="G101" s="40">
+        <v>66</v>
+      </c>
+      <c r="H101" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="F101" s="40" t="s">
-        <v>6</v>
-      </c>
-      <c r="G101" s="41">
-        <v>66</v>
-      </c>
-      <c r="H101" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="I101" s="28" t="s">
+      <c r="I101" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B102" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C102" s="29">
+        <v>46245</v>
+      </c>
+      <c r="D102" s="29">
+        <v>46345</v>
+      </c>
+      <c r="E102" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="F102" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G102" s="30">
+        <v>197</v>
+      </c>
+      <c r="H102" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="I102" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B103" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C103" s="29">
+        <v>46245</v>
+      </c>
+      <c r="D103" s="29">
+        <v>46419</v>
+      </c>
+      <c r="E103" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="F103" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G103" s="30">
+        <v>78</v>
+      </c>
+      <c r="H103" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="I103" s="32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B104" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C104" s="29">
+        <v>46245</v>
+      </c>
+      <c r="D104" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E104" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="F104" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G104" s="30">
+        <v>20</v>
+      </c>
+      <c r="H104" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="I104" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B105" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C105" s="29">
+        <v>46245</v>
+      </c>
+      <c r="D105" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E105" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="F105" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G105" s="30">
+        <v>134</v>
+      </c>
+      <c r="H105" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="I105" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B106" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C106" s="29">
+        <v>46245</v>
+      </c>
+      <c r="D106" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E106" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="F106" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" s="30">
+        <v>2</v>
+      </c>
+      <c r="H106" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="I106" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B107" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C107" s="29">
+        <v>46245</v>
+      </c>
+      <c r="D107" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E107" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="F107" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" s="30">
+        <v>7</v>
+      </c>
+      <c r="H107" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="I107" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B108" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C108" s="29">
+        <v>46245</v>
+      </c>
+      <c r="D108" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E108" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="F108" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G108" s="30">
+        <v>5</v>
+      </c>
+      <c r="H108" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="I108" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B109" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C109" s="29">
+        <v>46245</v>
+      </c>
+      <c r="D109" s="29">
+        <v>46266</v>
+      </c>
+      <c r="E109" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="F109" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G109" s="30">
+        <v>7</v>
+      </c>
+      <c r="H109" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="I109" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B110" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C110" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D110" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E110" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="F110" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G110" s="30">
+        <v>4</v>
+      </c>
+      <c r="H110" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="I110" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B111" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C111" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D111" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E111" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="F111" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G111" s="30">
+        <v>2</v>
+      </c>
+      <c r="H111" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="I111" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B112" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C112" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D112" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E112" s="28" t="s">
+        <v>282</v>
+      </c>
+      <c r="F112" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G112" s="30">
+        <v>2</v>
+      </c>
+      <c r="H112" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="I112" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B113" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C113" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D113" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E113" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="F113" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G113" s="30">
+        <v>20</v>
+      </c>
+      <c r="H113" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="I113" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B114" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C114" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D114" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E114" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="F114" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G114" s="30">
+        <v>4</v>
+      </c>
+      <c r="H114" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="I114" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B115" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C115" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D115" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E115" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="F115" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G115" s="30">
+        <v>2</v>
+      </c>
+      <c r="H115" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="I115" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B116" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C116" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D116" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E116" s="28" t="s">
+        <v>290</v>
+      </c>
+      <c r="F116" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" s="30">
+        <v>9</v>
+      </c>
+      <c r="H116" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="I116" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B117" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C117" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D117" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E117" s="28" t="s">
+        <v>292</v>
+      </c>
+      <c r="F117" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G117" s="30">
+        <v>5</v>
+      </c>
+      <c r="H117" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="I117" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B118" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C118" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D118" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E118" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="F118" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G118" s="30">
+        <v>5</v>
+      </c>
+      <c r="H118" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="I118" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B119" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C119" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D119" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E119" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="F119" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G119" s="30">
+        <v>4</v>
+      </c>
+      <c r="H119" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="I119" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B120" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C120" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D120" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E120" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="F120" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G120" s="30">
+        <v>2</v>
+      </c>
+      <c r="H120" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="I120" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B121" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C121" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D121" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E121" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="F121" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G121" s="30">
+        <v>9</v>
+      </c>
+      <c r="H121" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="I121" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B122" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C122" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D122" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E122" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="F122" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G122" s="30">
+        <v>1</v>
+      </c>
+      <c r="H122" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="I122" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B123" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C123" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D123" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E123" s="28" t="s">
+        <v>304</v>
+      </c>
+      <c r="F123" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G123" s="30">
+        <v>2</v>
+      </c>
+      <c r="H123" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="I123" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B124" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C124" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D124" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E124" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="F124" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G124" s="30">
+        <v>4</v>
+      </c>
+      <c r="H124" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="I124" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B125" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C125" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D125" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E125" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="F125" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G125" s="30">
+        <v>2</v>
+      </c>
+      <c r="H125" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="I125" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B126" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C126" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D126" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E126" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="F126" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G126" s="30">
+        <v>2</v>
+      </c>
+      <c r="H126" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="I126" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B127" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C127" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D127" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E127" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="F127" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G127" s="30">
+        <v>1</v>
+      </c>
+      <c r="H127" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="I127" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B128" s="29">
+        <v>46245</v>
+      </c>
+      <c r="C128" s="29">
+        <v>46246</v>
+      </c>
+      <c r="D128" s="29">
+        <v>46305</v>
+      </c>
+      <c r="E128" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="F128" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G128" s="30">
+        <v>2</v>
+      </c>
+      <c r="H128" s="30" t="s">
+        <v>315</v>
+      </c>
+      <c r="I128" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B129" s="29">
+        <v>46247</v>
+      </c>
+      <c r="C129" s="29">
+        <v>46247</v>
+      </c>
+      <c r="D129" s="29">
+        <v>46308</v>
+      </c>
+      <c r="E129" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="F129" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G129" s="30">
+        <v>14</v>
+      </c>
+      <c r="H129" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="I129" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B130" s="29">
+        <v>46247</v>
+      </c>
+      <c r="C130" s="29">
+        <v>46248</v>
+      </c>
+      <c r="D130" s="29">
+        <v>46217</v>
+      </c>
+      <c r="E130" s="28" t="s">
+        <v>318</v>
+      </c>
+      <c r="F130" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G130" s="30">
+        <v>59</v>
+      </c>
+      <c r="H130" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="I130" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B131" s="29">
+        <v>46251</v>
+      </c>
+      <c r="C131" s="29">
+        <v>46251</v>
+      </c>
+      <c r="D131" s="29">
+        <v>46297</v>
+      </c>
+      <c r="E131" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="F131" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G131" s="30">
+        <v>115</v>
+      </c>
+      <c r="H131" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="I131" s="32" t="s">
         <v>34</v>
       </c>
     </row>
@@ -5612,7 +6620,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I101</xm:sqref>
+          <xm:sqref>I3:I131</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5733,7 +6741,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>267</v>
+        <v>316</v>
       </c>
       <c r="E1"/>
     </row>
@@ -6148,7 +7156,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27E898B2-03D8-47E5-80B6-68CE85636EAC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D160E30-BC30-4B6D-ACC5-72FBA8F9F1F1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -6167,7 +7175,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{963127C5-89B2-4462-8394-89B9B2B78CD6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C46929A-3DE1-4C62-9238-C2B188611275}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -6175,18 +7183,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37BCDC0A-E466-427F-8667-A5FCD14D403E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD289F2-34C9-4527-98E3-ED4CBE06E698}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE6B85FA-6502-4C50-8A39-B9B917ECC02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9C3697B-36EF-4E1D-816F-E31B4510F204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="367">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1076,6 +1076,63 @@
     <t>907 Lake Street  San Pablo CA 94806</t>
   </si>
   <si>
+    <t>Universal City Studios Productions LLLP</t>
+  </si>
+  <si>
+    <t>Netflix, Inc.</t>
+  </si>
+  <si>
+    <t>5808 W. Sunset Blvd  Los Angeles CA 90028</t>
+  </si>
+  <si>
+    <t>Roskam Baking Company dba Organic Milling</t>
+  </si>
+  <si>
+    <t>305 South Acacia Street  San Dimas CA 91773</t>
+  </si>
+  <si>
+    <t>Corteva Agriscience LLC</t>
+  </si>
+  <si>
+    <t>901 Loveridge Road  Pittsburg CA 94565</t>
+  </si>
+  <si>
+    <t>San Joaquin County</t>
+  </si>
+  <si>
+    <t>Stockton Truss LLC</t>
+  </si>
+  <si>
+    <t>4408 E Fremont St  Stockton CA 95215</t>
+  </si>
+  <si>
+    <t>Ventura County</t>
+  </si>
+  <si>
+    <t>Volume Services, Inc. (Sodexo)</t>
+  </si>
+  <si>
+    <t>40 Presidential Drive  Simi Valley CA 93065</t>
+  </si>
+  <si>
+    <t>Stone Brewing Co., LLC - Executive Place</t>
+  </si>
+  <si>
+    <t>2865 Executive Place  Escondido CA 92029</t>
+  </si>
+  <si>
+    <t>Stone Brewing Co., LLC - Harmony Grove</t>
+  </si>
+  <si>
+    <t>2005 Harmony Grove Rd.  Escondido CA 92029</t>
+  </si>
+  <si>
+    <t>Stone Brewing CO., LLC - Citracado Parkway</t>
+  </si>
+  <si>
+    <t>1999 Citracado Parkway  Escondido CA 92029</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1095,7 +1152,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 08/17/2026
+01/01/2023 - 08/24/2026
 </t>
     </r>
     <r>
@@ -1109,19 +1166,94 @@
     </r>
   </si>
   <si>
-    <t>Universal City Studios Productions LLLP</t>
-  </si>
-  <si>
-    <t>Netflix, Inc.</t>
-  </si>
-  <si>
-    <t>5808 W. Sunset Blvd  Los Angeles CA 90028</t>
-  </si>
-  <si>
-    <t>Roskam Baking Company dba Organic Milling</t>
-  </si>
-  <si>
-    <t>305 South Acacia Street  San Dimas CA 91773</t>
+    <t>Flying Food Group, LLC</t>
+  </si>
+  <si>
+    <t>50 Adrian Ct  Burlingame CA 94010</t>
+  </si>
+  <si>
+    <t>3250 Patterson Road  Riverbank CA 95367</t>
+  </si>
+  <si>
+    <t>Haas Automation, Inc.</t>
+  </si>
+  <si>
+    <t>2800 Sturgis Road  Oxnard CA 93030</t>
+  </si>
+  <si>
+    <t>Blue Shield of California</t>
+  </si>
+  <si>
+    <t>601 12th Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>El Dorado County</t>
+  </si>
+  <si>
+    <t>Blue Shield of California (Building C)</t>
+  </si>
+  <si>
+    <t>4203 Town Center Blvd., Building C  El Dorado Hills CA 95762</t>
+  </si>
+  <si>
+    <t>Blue Shield of California (Building B)</t>
+  </si>
+  <si>
+    <t>4203 Town Center Blvd., Building B  El Dorado Hills CA 95672</t>
+  </si>
+  <si>
+    <t>3840 Kilroy Airport Way  Long Beach CA 90806</t>
+  </si>
+  <si>
+    <t>6300 Canoga Avenue  Woodland Hills CA 91367</t>
+  </si>
+  <si>
+    <t>3300 Zinfandel Drive  Rancho Cordova CA 95670</t>
+  </si>
+  <si>
+    <t>3131 Camino Del Rio, Suite #1300  San Diego CA 92108</t>
+  </si>
+  <si>
+    <t>3021 Reynolds Ranch Parkway  Lodi CA 95240</t>
+  </si>
+  <si>
+    <t>Cellares Corporation</t>
+  </si>
+  <si>
+    <t>1100 Veterans Boulevard  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Apple, Inc. - Cupertino</t>
+  </si>
+  <si>
+    <t>One Apple Park Way  Cupertino CA 95014</t>
+  </si>
+  <si>
+    <t>Apple, Inc. - Sunnyvale</t>
+  </si>
+  <si>
+    <t>599 N. Mathilda Ave.  Sunnyvale CA 94085</t>
+  </si>
+  <si>
+    <t>Apple, Inc. - Maude Ave.</t>
+  </si>
+  <si>
+    <t>605 W. Maude Ave.  Sunnyvale CA 94085</t>
+  </si>
+  <si>
+    <t>Jabil Inc.</t>
+  </si>
+  <si>
+    <t>30 Great Oaks Boulevard  San Jose CA 95119</t>
+  </si>
+  <si>
+    <t>BFG Supply Co., LLC</t>
+  </si>
+  <si>
+    <t>2552 Shenandoah Way  San Bernardino CA 92407</t>
+  </si>
+  <si>
+    <t>3740 Seaport Boulevard, Suite 10  West Sacramento CA 95691</t>
   </si>
   <si>
     <r>
@@ -1135,7 +1267,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 08/17/2026</t>
+      <t>07/01/26 to 08/24/2026</t>
     </r>
     <r>
       <rPr>
@@ -1155,7 +1287,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I131.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I156.</t>
     </r>
   </si>
 </sst>
@@ -2321,8 +2453,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I131" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I131" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I156" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I156" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2669,37 +2801,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D341DFFF-02D2-4572-95F5-BB3221952133}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="74" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="73.90625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="135" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.5">
       <c r="A2" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>24</v>
       </c>
@@ -2718,18 +2850,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832896D-8AFB-4FFC-957E-910308F3BC0C}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.36328125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="76.5" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>16</v>
       </c>
@@ -2737,34 +2869,34 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>6354</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7770</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Temporary")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -2773,25 +2905,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Temporary")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -2811,32 +2943,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I131"/>
-  <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I156"/>
+  <sheetFormatPr defaultColWidth="161.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="50.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.5703125" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" customWidth="1"/>
+    <col min="1" max="1" width="28.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="49.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.54296875" customWidth="1"/>
+    <col min="11" max="11" width="13.1796875" customWidth="1"/>
+    <col min="12" max="12" width="12.7265625" customWidth="1"/>
+    <col min="13" max="13" width="11.81640625" customWidth="1"/>
     <col min="14" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="100" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>322</v>
+        <v>366</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="24" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
@@ -2865,7 +2997,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="28" t="s">
         <v>5</v>
       </c>
@@ -2894,7 +3026,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
         <v>55</v>
       </c>
@@ -2923,7 +3055,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
         <v>54</v>
       </c>
@@ -2952,7 +3084,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
         <v>56</v>
       </c>
@@ -2981,7 +3113,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="28" t="s">
         <v>5</v>
       </c>
@@ -3010,7 +3142,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="28" t="s">
         <v>53</v>
       </c>
@@ -3039,7 +3171,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="28" t="s">
         <v>53</v>
       </c>
@@ -3068,7 +3200,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="28" t="s">
         <v>57</v>
       </c>
@@ -3097,7 +3229,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
         <v>55</v>
       </c>
@@ -3126,7 +3258,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="28" t="s">
         <v>76</v>
       </c>
@@ -3155,7 +3287,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="28" t="s">
         <v>79</v>
       </c>
@@ -3184,7 +3316,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="28" t="s">
         <v>82</v>
       </c>
@@ -3213,7 +3345,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
         <v>53</v>
       </c>
@@ -3242,7 +3374,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="28" t="s">
         <v>5</v>
       </c>
@@ -3271,7 +3403,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="28" t="s">
         <v>54</v>
       </c>
@@ -3300,7 +3432,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="28" t="s">
         <v>53</v>
       </c>
@@ -3329,7 +3461,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="28" t="s">
         <v>53</v>
       </c>
@@ -3358,7 +3490,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="28" t="s">
         <v>54</v>
       </c>
@@ -3387,7 +3519,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="28" t="s">
         <v>79</v>
       </c>
@@ -3416,7 +3548,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="28" t="s">
         <v>99</v>
       </c>
@@ -3445,7 +3577,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="28" t="s">
         <v>103</v>
       </c>
@@ -3474,7 +3606,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="28" t="s">
         <v>53</v>
       </c>
@@ -3503,7 +3635,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="28" t="s">
         <v>103</v>
       </c>
@@ -3532,7 +3664,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="28" t="s">
         <v>110</v>
       </c>
@@ -3561,7 +3693,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="28" t="s">
         <v>5</v>
       </c>
@@ -3590,7 +3722,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="28" t="s">
         <v>5</v>
       </c>
@@ -3619,7 +3751,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="28" t="s">
         <v>5</v>
       </c>
@@ -3648,7 +3780,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="28" t="s">
         <v>5</v>
       </c>
@@ -3677,7 +3809,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="28" t="s">
         <v>5</v>
       </c>
@@ -3706,7 +3838,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="28" t="s">
         <v>54</v>
       </c>
@@ -3735,7 +3867,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="28" t="s">
         <v>103</v>
       </c>
@@ -3764,7 +3896,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="28" t="s">
         <v>127</v>
       </c>
@@ -3793,7 +3925,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="28" t="s">
         <v>103</v>
       </c>
@@ -3822,7 +3954,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="28" t="s">
         <v>53</v>
       </c>
@@ -3851,7 +3983,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="28" t="s">
         <v>135</v>
       </c>
@@ -3880,7 +4012,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="28" t="s">
         <v>138</v>
       </c>
@@ -3909,7 +4041,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="28" t="s">
         <v>103</v>
       </c>
@@ -3938,7 +4070,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="28" t="s">
         <v>76</v>
       </c>
@@ -3967,7 +4099,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="28" t="s">
         <v>138</v>
       </c>
@@ -3996,7 +4128,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="28" t="s">
         <v>138</v>
       </c>
@@ -4025,7 +4157,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="33" t="s">
         <v>149</v>
       </c>
@@ -4054,7 +4186,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="33" t="s">
         <v>79</v>
       </c>
@@ -4083,7 +4215,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="33" t="s">
         <v>79</v>
       </c>
@@ -4112,7 +4244,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="33" t="s">
         <v>79</v>
       </c>
@@ -4141,7 +4273,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="33" t="s">
         <v>5</v>
       </c>
@@ -4170,7 +4302,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="33" t="s">
         <v>160</v>
       </c>
@@ -4199,7 +4331,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="33" t="s">
         <v>103</v>
       </c>
@@ -4228,7 +4360,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="33" t="s">
         <v>103</v>
       </c>
@@ -4257,7 +4389,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="33" t="s">
         <v>103</v>
       </c>
@@ -4286,7 +4418,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="33" t="s">
         <v>103</v>
       </c>
@@ -4315,7 +4447,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="33" t="s">
         <v>171</v>
       </c>
@@ -4344,7 +4476,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="33" t="s">
         <v>171</v>
       </c>
@@ -4373,7 +4505,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="28" t="s">
         <v>53</v>
       </c>
@@ -4402,7 +4534,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="28" t="s">
         <v>76</v>
       </c>
@@ -4431,7 +4563,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="28" t="s">
         <v>180</v>
       </c>
@@ -4460,7 +4592,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="28" t="s">
         <v>5</v>
       </c>
@@ -4489,7 +4621,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="28" t="s">
         <v>5</v>
       </c>
@@ -4518,7 +4650,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="28" t="s">
         <v>53</v>
       </c>
@@ -4547,7 +4679,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="28" t="s">
         <v>189</v>
       </c>
@@ -4576,7 +4708,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="28" t="s">
         <v>56</v>
       </c>
@@ -4605,7 +4737,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="28" t="s">
         <v>55</v>
       </c>
@@ -4634,7 +4766,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="28" t="s">
         <v>110</v>
       </c>
@@ -4663,7 +4795,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="28" t="s">
         <v>110</v>
       </c>
@@ -4692,7 +4824,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="28" t="s">
         <v>199</v>
       </c>
@@ -4721,7 +4853,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="28" t="s">
         <v>138</v>
       </c>
@@ -4750,7 +4882,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="28" t="s">
         <v>138</v>
       </c>
@@ -4779,7 +4911,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="28" t="s">
         <v>103</v>
       </c>
@@ -4808,7 +4940,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="28" t="s">
         <v>207</v>
       </c>
@@ -4837,7 +4969,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="28" t="s">
         <v>171</v>
       </c>
@@ -4866,7 +4998,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="28" t="s">
         <v>53</v>
       </c>
@@ -4895,7 +5027,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="28" t="s">
         <v>189</v>
       </c>
@@ -4924,7 +5056,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="28" t="s">
         <v>54</v>
       </c>
@@ -4953,7 +5085,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="28" t="s">
         <v>216</v>
       </c>
@@ -4982,7 +5114,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="28" t="s">
         <v>56</v>
       </c>
@@ -5011,7 +5143,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="28" t="s">
         <v>171</v>
       </c>
@@ -5040,7 +5172,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="28" t="s">
         <v>180</v>
       </c>
@@ -5069,7 +5201,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="28" t="s">
         <v>180</v>
       </c>
@@ -5098,7 +5230,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="28" t="s">
         <v>180</v>
       </c>
@@ -5127,7 +5259,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="28" t="s">
         <v>180</v>
       </c>
@@ -5156,7 +5288,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="28" t="s">
         <v>180</v>
       </c>
@@ -5185,7 +5317,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="28" t="s">
         <v>55</v>
       </c>
@@ -5214,7 +5346,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="28" t="s">
         <v>53</v>
       </c>
@@ -5243,7 +5375,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="28" t="s">
         <v>53</v>
       </c>
@@ -5272,7 +5404,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="28" t="s">
         <v>54</v>
       </c>
@@ -5301,7 +5433,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="28" t="s">
         <v>54</v>
       </c>
@@ -5330,7 +5462,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="28" t="s">
         <v>79</v>
       </c>
@@ -5359,7 +5491,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="28" t="s">
         <v>79</v>
       </c>
@@ -5388,7 +5520,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="28" t="s">
         <v>103</v>
       </c>
@@ -5417,7 +5549,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="28" t="s">
         <v>54</v>
       </c>
@@ -5446,7 +5578,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="28" t="s">
         <v>79</v>
       </c>
@@ -5475,7 +5607,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="33" t="s">
         <v>5</v>
       </c>
@@ -5504,7 +5636,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="33" t="s">
         <v>5</v>
       </c>
@@ -5533,7 +5665,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="33" t="s">
         <v>5</v>
       </c>
@@ -5562,7 +5694,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="33" t="s">
         <v>5</v>
       </c>
@@ -5591,7 +5723,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="33" t="s">
         <v>189</v>
       </c>
@@ -5620,7 +5752,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="33" t="s">
         <v>56</v>
       </c>
@@ -5649,7 +5781,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="33" t="s">
         <v>171</v>
       </c>
@@ -5678,7 +5810,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="33" t="s">
         <v>260</v>
       </c>
@@ -5707,7 +5839,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="33" t="s">
         <v>171</v>
       </c>
@@ -5736,7 +5868,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="28" t="s">
         <v>5</v>
       </c>
@@ -5765,7 +5897,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="28" t="s">
         <v>189</v>
       </c>
@@ -5794,7 +5926,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="28" t="s">
         <v>207</v>
       </c>
@@ -5823,7 +5955,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="28" t="s">
         <v>207</v>
       </c>
@@ -5852,7 +5984,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="28" t="s">
         <v>207</v>
       </c>
@@ -5881,7 +6013,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="28" t="s">
         <v>207</v>
       </c>
@@ -5910,7 +6042,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="28" t="s">
         <v>207</v>
       </c>
@@ -5939,7 +6071,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="28" t="s">
         <v>5</v>
       </c>
@@ -5968,7 +6100,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="28" t="s">
         <v>76</v>
       </c>
@@ -5997,7 +6129,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="28" t="s">
         <v>76</v>
       </c>
@@ -6026,7 +6158,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="28" t="s">
         <v>76</v>
       </c>
@@ -6055,7 +6187,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="28" t="s">
         <v>76</v>
       </c>
@@ -6084,7 +6216,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="28" t="s">
         <v>76</v>
       </c>
@@ -6113,7 +6245,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="28" t="s">
         <v>76</v>
       </c>
@@ -6142,7 +6274,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="28" t="s">
         <v>76</v>
       </c>
@@ -6171,7 +6303,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="28" t="s">
         <v>76</v>
       </c>
@@ -6200,7 +6332,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="28" t="s">
         <v>76</v>
       </c>
@@ -6229,7 +6361,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="28" t="s">
         <v>76</v>
       </c>
@@ -6258,7 +6390,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="28" t="s">
         <v>76</v>
       </c>
@@ -6287,7 +6419,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="28" t="s">
         <v>76</v>
       </c>
@@ -6316,7 +6448,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="28" t="s">
         <v>76</v>
       </c>
@@ -6345,7 +6477,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="28" t="s">
         <v>76</v>
       </c>
@@ -6374,7 +6506,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="28" t="s">
         <v>76</v>
       </c>
@@ -6403,7 +6535,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="28" t="s">
         <v>76</v>
       </c>
@@ -6432,7 +6564,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="28" t="s">
         <v>76</v>
       </c>
@@ -6461,7 +6593,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="28" t="s">
         <v>57</v>
       </c>
@@ -6490,7 +6622,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="28" t="s">
         <v>57</v>
       </c>
@@ -6519,7 +6651,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="28" t="s">
         <v>5</v>
       </c>
@@ -6533,7 +6665,7 @@
         <v>46308</v>
       </c>
       <c r="E129" s="28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F129" s="28" t="s">
         <v>6</v>
@@ -6548,7 +6680,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="28" t="s">
         <v>5</v>
       </c>
@@ -6562,7 +6694,7 @@
         <v>46217</v>
       </c>
       <c r="E130" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F130" s="28" t="s">
         <v>6</v>
@@ -6571,13 +6703,13 @@
         <v>59</v>
       </c>
       <c r="H130" s="30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I130" s="32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="28" t="s">
         <v>5</v>
       </c>
@@ -6591,7 +6723,7 @@
         <v>46297</v>
       </c>
       <c r="E131" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F131" s="28" t="s">
         <v>6</v>
@@ -6600,10 +6732,735 @@
         <v>115</v>
       </c>
       <c r="H131" s="30" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I131" s="32" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A132" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B132" s="29">
+        <v>46251</v>
+      </c>
+      <c r="C132" s="29">
+        <v>46251</v>
+      </c>
+      <c r="D132" s="29">
+        <v>46311</v>
+      </c>
+      <c r="E132" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F132" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G132" s="30">
+        <v>205</v>
+      </c>
+      <c r="H132" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="I132" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A133" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B133" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C133" s="29">
+        <v>46252</v>
+      </c>
+      <c r="D133" s="29">
+        <v>46325</v>
+      </c>
+      <c r="E133" s="28" t="s">
+        <v>321</v>
+      </c>
+      <c r="F133" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G133" s="30">
+        <v>2</v>
+      </c>
+      <c r="H133" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="I133" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A134" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="B134" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C134" s="29">
+        <v>46252</v>
+      </c>
+      <c r="D134" s="29">
+        <v>46313</v>
+      </c>
+      <c r="E134" s="28" t="s">
+        <v>324</v>
+      </c>
+      <c r="F134" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G134" s="30">
+        <v>65</v>
+      </c>
+      <c r="H134" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="I134" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A135" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B135" s="29">
+        <v>46251</v>
+      </c>
+      <c r="C135" s="29">
+        <v>46252</v>
+      </c>
+      <c r="D135" s="29">
+        <v>46311</v>
+      </c>
+      <c r="E135" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="F135" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G135" s="30">
+        <v>93</v>
+      </c>
+      <c r="H135" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="I135" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A136" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B136" s="29">
+        <v>46253</v>
+      </c>
+      <c r="C136" s="29">
+        <v>46253</v>
+      </c>
+      <c r="D136" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E136" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="F136" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G136" s="30">
+        <v>6</v>
+      </c>
+      <c r="H136" s="30" t="s">
+        <v>330</v>
+      </c>
+      <c r="I136" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A137" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B137" s="29">
+        <v>46253</v>
+      </c>
+      <c r="C137" s="29">
+        <v>46253</v>
+      </c>
+      <c r="D137" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E137" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="F137" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G137" s="30">
+        <v>2</v>
+      </c>
+      <c r="H137" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="I137" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A138" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B138" s="29">
+        <v>46253</v>
+      </c>
+      <c r="C138" s="29">
+        <v>46253</v>
+      </c>
+      <c r="D138" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E138" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="F138" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G138" s="30">
+        <v>50</v>
+      </c>
+      <c r="H138" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="I138" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A139" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B139" s="29">
+        <v>46248</v>
+      </c>
+      <c r="C139" s="29">
+        <v>46254</v>
+      </c>
+      <c r="D139" s="29">
+        <v>46308</v>
+      </c>
+      <c r="E139" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="F139" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G139" s="30">
+        <v>72</v>
+      </c>
+      <c r="H139" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="I139" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A140" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B140" s="29">
+        <v>46246</v>
+      </c>
+      <c r="C140" s="29">
+        <v>46254</v>
+      </c>
+      <c r="D140" s="29">
+        <v>46307</v>
+      </c>
+      <c r="E140" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="F140" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G140" s="30">
+        <v>120</v>
+      </c>
+      <c r="H140" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="I140" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A141" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B141" s="29">
+        <v>46253</v>
+      </c>
+      <c r="C141" s="29">
+        <v>46254</v>
+      </c>
+      <c r="D141" s="29">
+        <v>46328</v>
+      </c>
+      <c r="E141" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="F141" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G141" s="30">
+        <v>73</v>
+      </c>
+      <c r="H141" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="I141" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A142" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B142" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C142" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D142" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E142" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F142" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G142" s="30">
+        <v>25</v>
+      </c>
+      <c r="H142" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="I142" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A143" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="B143" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C143" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D143" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E143" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="F143" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G143" s="30">
+        <v>1</v>
+      </c>
+      <c r="H143" s="30" t="s">
+        <v>345</v>
+      </c>
+      <c r="I143" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A144" s="28" t="s">
+        <v>343</v>
+      </c>
+      <c r="B144" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C144" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D144" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E144" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="F144" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G144" s="30">
+        <v>12</v>
+      </c>
+      <c r="H144" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="I144" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A145" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B145" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C145" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D145" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E145" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F145" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G145" s="30">
+        <v>8</v>
+      </c>
+      <c r="H145" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="I145" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A146" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B146" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C146" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D146" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E146" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F146" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G146" s="30">
+        <v>3</v>
+      </c>
+      <c r="H146" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="I146" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A147" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B147" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C147" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D147" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E147" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F147" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G147" s="30">
+        <v>5</v>
+      </c>
+      <c r="H147" s="30" t="s">
+        <v>350</v>
+      </c>
+      <c r="I147" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A148" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="B148" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C148" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D148" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E148" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F148" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G148" s="30">
+        <v>4</v>
+      </c>
+      <c r="H148" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="I148" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A149" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="B149" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C149" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D149" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E149" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="F149" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G149" s="30">
+        <v>2</v>
+      </c>
+      <c r="H149" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="I149" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A150" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B150" s="29">
+        <v>46255</v>
+      </c>
+      <c r="C150" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D150" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E150" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="F150" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G150" s="30">
+        <v>100</v>
+      </c>
+      <c r="H150" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="I150" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A151" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B151" s="29">
+        <v>46254</v>
+      </c>
+      <c r="C151" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D151" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E151" s="28" t="s">
+        <v>355</v>
+      </c>
+      <c r="F151" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G151" s="30">
+        <v>79</v>
+      </c>
+      <c r="H151" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="I151" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A152" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B152" s="29">
+        <v>46254</v>
+      </c>
+      <c r="C152" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D152" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E152" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="F152" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G152" s="30">
+        <v>28</v>
+      </c>
+      <c r="H152" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="I152" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A153" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B153" s="29">
+        <v>46254</v>
+      </c>
+      <c r="C153" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D153" s="29">
+        <v>46314</v>
+      </c>
+      <c r="E153" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="F153" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G153" s="30">
+        <v>40</v>
+      </c>
+      <c r="H153" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="I153" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A154" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B154" s="29">
+        <v>46254</v>
+      </c>
+      <c r="C154" s="29">
+        <v>46255</v>
+      </c>
+      <c r="D154" s="29">
+        <v>46349</v>
+      </c>
+      <c r="E154" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="F154" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G154" s="30">
+        <v>382</v>
+      </c>
+      <c r="H154" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="I154" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A155" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B155" s="29">
+        <v>46258</v>
+      </c>
+      <c r="C155" s="29">
+        <v>46258</v>
+      </c>
+      <c r="D155" s="29">
+        <v>46320</v>
+      </c>
+      <c r="E155" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="F155" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G155" s="30">
+        <v>37</v>
+      </c>
+      <c r="H155" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="I155" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A156" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B156" s="29">
+        <v>46258</v>
+      </c>
+      <c r="C156" s="29">
+        <v>46258</v>
+      </c>
+      <c r="D156" s="29">
+        <v>46320</v>
+      </c>
+      <c r="E156" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="F156" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G156" s="30">
+        <v>2</v>
+      </c>
+      <c r="H156" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="I156" s="32" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -6620,7 +7477,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I131</xm:sqref>
+          <xm:sqref>I3:I156</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6631,18 +7488,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC03875-3DF4-4258-8762-7FFE2A7D620D}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.453125" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="97.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="95" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>16</v>
       </c>
@@ -6650,7 +7507,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="s">
         <v>17</v>
       </c>
@@ -6659,7 +7516,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>9</v>
       </c>
@@ -6668,7 +7525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="s">
         <v>10</v>
       </c>
@@ -6677,7 +7534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>11</v>
       </c>
@@ -6686,7 +7543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="17" t="s">
         <v>12</v>
       </c>
@@ -6695,7 +7552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
         <v>13</v>
       </c>
@@ -6704,7 +7561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>14</v>
       </c>
@@ -6727,25 +7584,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE76718-798E-45ED-8CA1-01AA760CE5F1}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7265625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="98.5" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="E1"/>
     </row>
-    <row r="2" spans="1:8" ht="24.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="24" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
@@ -6771,7 +7628,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -6808,117 +7665,117 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E81B0C9-EE0D-4672-99B4-ACA7D2D31E92}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="67.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="67.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -7156,7 +8013,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D160E30-BC30-4B6D-ACC5-72FBA8F9F1F1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B82B9673-ED21-4933-9A9C-773CB2F4FD2E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -7175,7 +8032,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C46929A-3DE1-4C62-9238-C2B188611275}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BCADA38-B649-43B5-8987-30F05437E106}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -7183,18 +8040,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD289F2-34C9-4527-98E3-ED4CBE06E698}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BE6D488-2A3F-46E6-B9DE-C01E1051C417}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9C3697B-36EF-4E1D-816F-E31B4510F204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD45D7F5-8BFC-478A-A7EB-2725E928A57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="369">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1133,6 +1133,96 @@
     <t>1999 Citracado Parkway  Escondido CA 92029</t>
   </si>
   <si>
+    <t>Flying Food Group, LLC</t>
+  </si>
+  <si>
+    <t>50 Adrian Ct  Burlingame CA 94010</t>
+  </si>
+  <si>
+    <t>3250 Patterson Road  Riverbank CA 95367</t>
+  </si>
+  <si>
+    <t>Haas Automation, Inc.</t>
+  </si>
+  <si>
+    <t>2800 Sturgis Road  Oxnard CA 93030</t>
+  </si>
+  <si>
+    <t>Blue Shield of California</t>
+  </si>
+  <si>
+    <t>601 12th Street  Oakland CA 94607</t>
+  </si>
+  <si>
+    <t>El Dorado County</t>
+  </si>
+  <si>
+    <t>Blue Shield of California (Building C)</t>
+  </si>
+  <si>
+    <t>4203 Town Center Blvd., Building C  El Dorado Hills CA 95762</t>
+  </si>
+  <si>
+    <t>Blue Shield of California (Building B)</t>
+  </si>
+  <si>
+    <t>4203 Town Center Blvd., Building B  El Dorado Hills CA 95672</t>
+  </si>
+  <si>
+    <t>3840 Kilroy Airport Way  Long Beach CA 90806</t>
+  </si>
+  <si>
+    <t>6300 Canoga Avenue  Woodland Hills CA 91367</t>
+  </si>
+  <si>
+    <t>3300 Zinfandel Drive  Rancho Cordova CA 95670</t>
+  </si>
+  <si>
+    <t>3131 Camino Del Rio, Suite #1300  San Diego CA 92108</t>
+  </si>
+  <si>
+    <t>3021 Reynolds Ranch Parkway  Lodi CA 95240</t>
+  </si>
+  <si>
+    <t>Cellares Corporation</t>
+  </si>
+  <si>
+    <t>1100 Veterans Boulevard  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>Apple, Inc. - Cupertino</t>
+  </si>
+  <si>
+    <t>One Apple Park Way  Cupertino CA 95014</t>
+  </si>
+  <si>
+    <t>Apple, Inc. - Sunnyvale</t>
+  </si>
+  <si>
+    <t>599 N. Mathilda Ave.  Sunnyvale CA 94085</t>
+  </si>
+  <si>
+    <t>Apple, Inc. - Maude Ave.</t>
+  </si>
+  <si>
+    <t>605 W. Maude Ave.  Sunnyvale CA 94085</t>
+  </si>
+  <si>
+    <t>Jabil Inc.</t>
+  </si>
+  <si>
+    <t>30 Great Oaks Boulevard  San Jose CA 95119</t>
+  </si>
+  <si>
+    <t>BFG Supply Co., LLC</t>
+  </si>
+  <si>
+    <t>2552 Shenandoah Way  San Bernardino CA 92407</t>
+  </si>
+  <si>
+    <t>3740 Seaport Boulevard, Suite 10  West Sacramento CA 95691</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1152,7 +1242,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 08/24/2026
+01/01/2023 - 08/26/2026
 </t>
     </r>
     <r>
@@ -1166,94 +1256,10 @@
     </r>
   </si>
   <si>
-    <t>Flying Food Group, LLC</t>
-  </si>
-  <si>
-    <t>50 Adrian Ct  Burlingame CA 94010</t>
-  </si>
-  <si>
-    <t>3250 Patterson Road  Riverbank CA 95367</t>
-  </si>
-  <si>
-    <t>Haas Automation, Inc.</t>
-  </si>
-  <si>
-    <t>2800 Sturgis Road  Oxnard CA 93030</t>
-  </si>
-  <si>
-    <t>Blue Shield of California</t>
-  </si>
-  <si>
-    <t>601 12th Street  Oakland CA 94607</t>
-  </si>
-  <si>
-    <t>El Dorado County</t>
-  </si>
-  <si>
-    <t>Blue Shield of California (Building C)</t>
-  </si>
-  <si>
-    <t>4203 Town Center Blvd., Building C  El Dorado Hills CA 95762</t>
-  </si>
-  <si>
-    <t>Blue Shield of California (Building B)</t>
-  </si>
-  <si>
-    <t>4203 Town Center Blvd., Building B  El Dorado Hills CA 95672</t>
-  </si>
-  <si>
-    <t>3840 Kilroy Airport Way  Long Beach CA 90806</t>
-  </si>
-  <si>
-    <t>6300 Canoga Avenue  Woodland Hills CA 91367</t>
-  </si>
-  <si>
-    <t>3300 Zinfandel Drive  Rancho Cordova CA 95670</t>
-  </si>
-  <si>
-    <t>3131 Camino Del Rio, Suite #1300  San Diego CA 92108</t>
-  </si>
-  <si>
-    <t>3021 Reynolds Ranch Parkway  Lodi CA 95240</t>
-  </si>
-  <si>
-    <t>Cellares Corporation</t>
-  </si>
-  <si>
-    <t>1100 Veterans Boulevard  South San Francisco CA 94080</t>
-  </si>
-  <si>
-    <t>Apple, Inc. - Cupertino</t>
-  </si>
-  <si>
-    <t>One Apple Park Way  Cupertino CA 95014</t>
-  </si>
-  <si>
-    <t>Apple, Inc. - Sunnyvale</t>
-  </si>
-  <si>
-    <t>599 N. Mathilda Ave.  Sunnyvale CA 94085</t>
-  </si>
-  <si>
-    <t>Apple, Inc. - Maude Ave.</t>
-  </si>
-  <si>
-    <t>605 W. Maude Ave.  Sunnyvale CA 94085</t>
-  </si>
-  <si>
-    <t>Jabil Inc.</t>
-  </si>
-  <si>
-    <t>30 Great Oaks Boulevard  San Jose CA 95119</t>
-  </si>
-  <si>
-    <t>BFG Supply Co., LLC</t>
-  </si>
-  <si>
-    <t>2552 Shenandoah Way  San Bernardino CA 92407</t>
-  </si>
-  <si>
-    <t>3740 Seaport Boulevard, Suite 10  West Sacramento CA 95691</t>
+    <t>Levine Management Group, Inc.</t>
+  </si>
+  <si>
+    <t>822 S. Robertson Suite #200  Los Angeles CA 90035</t>
   </si>
   <si>
     <r>
@@ -1267,7 +1273,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 08/24/2026</t>
+      <t>07/01/26 to 08/26/2026</t>
     </r>
     <r>
       <rPr>
@@ -1287,7 +1293,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I156.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I157.</t>
     </r>
   </si>
 </sst>
@@ -2453,8 +2459,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I156" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I156" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I157" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I157" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2875,7 +2881,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>7770</v>
+        <v>7842</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -2884,7 +2890,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2943,7 +2949,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr defaultColWidth="161.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.6328125" style="3" bestFit="1" customWidth="1"/>
@@ -2964,7 +2970,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="100" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -6955,7 +6961,7 @@
         <v>46308</v>
       </c>
       <c r="E139" s="28" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F139" s="28" t="s">
         <v>52</v>
@@ -6964,7 +6970,7 @@
         <v>72</v>
       </c>
       <c r="H139" s="30" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I139" s="32" t="s">
         <v>47</v>
@@ -6993,7 +6999,7 @@
         <v>120</v>
       </c>
       <c r="H140" s="30" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I140" s="32" t="s">
         <v>34</v>
@@ -7013,7 +7019,7 @@
         <v>46328</v>
       </c>
       <c r="E141" s="28" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F141" s="28" t="s">
         <v>6</v>
@@ -7022,7 +7028,7 @@
         <v>73</v>
       </c>
       <c r="H141" s="30" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I141" s="32" t="s">
         <v>34</v>
@@ -7042,7 +7048,7 @@
         <v>46315</v>
       </c>
       <c r="E142" s="28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F142" s="28" t="s">
         <v>6</v>
@@ -7051,7 +7057,7 @@
         <v>25</v>
       </c>
       <c r="H142" s="30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I142" s="32" t="s">
         <v>39</v>
@@ -7059,7 +7065,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="28" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B143" s="29">
         <v>46255</v>
@@ -7071,7 +7077,7 @@
         <v>46315</v>
       </c>
       <c r="E143" s="28" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F143" s="28" t="s">
         <v>6</v>
@@ -7080,7 +7086,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="30" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I143" s="32" t="s">
         <v>39</v>
@@ -7088,7 +7094,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="28" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B144" s="29">
         <v>46255</v>
@@ -7100,7 +7106,7 @@
         <v>46315</v>
       </c>
       <c r="E144" s="28" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F144" s="28" t="s">
         <v>6</v>
@@ -7109,7 +7115,7 @@
         <v>12</v>
       </c>
       <c r="H144" s="30" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I144" s="32" t="s">
         <v>39</v>
@@ -7129,7 +7135,7 @@
         <v>46315</v>
       </c>
       <c r="E145" s="28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F145" s="28" t="s">
         <v>6</v>
@@ -7138,7 +7144,7 @@
         <v>8</v>
       </c>
       <c r="H145" s="30" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I145" s="32" t="s">
         <v>39</v>
@@ -7158,7 +7164,7 @@
         <v>46315</v>
       </c>
       <c r="E146" s="28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F146" s="28" t="s">
         <v>6</v>
@@ -7167,7 +7173,7 @@
         <v>3</v>
       </c>
       <c r="H146" s="30" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I146" s="32" t="s">
         <v>39</v>
@@ -7187,7 +7193,7 @@
         <v>46315</v>
       </c>
       <c r="E147" s="28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F147" s="28" t="s">
         <v>6</v>
@@ -7196,7 +7202,7 @@
         <v>5</v>
       </c>
       <c r="H147" s="30" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I147" s="32" t="s">
         <v>39</v>
@@ -7216,7 +7222,7 @@
         <v>46315</v>
       </c>
       <c r="E148" s="28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F148" s="28" t="s">
         <v>6</v>
@@ -7225,7 +7231,7 @@
         <v>4</v>
       </c>
       <c r="H148" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I148" s="32" t="s">
         <v>39</v>
@@ -7245,7 +7251,7 @@
         <v>46315</v>
       </c>
       <c r="E149" s="28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F149" s="28" t="s">
         <v>6</v>
@@ -7254,7 +7260,7 @@
         <v>2</v>
       </c>
       <c r="H149" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I149" s="32" t="s">
         <v>39</v>
@@ -7274,7 +7280,7 @@
         <v>46315</v>
       </c>
       <c r="E150" s="28" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F150" s="28" t="s">
         <v>6</v>
@@ -7283,7 +7289,7 @@
         <v>100</v>
       </c>
       <c r="H150" s="30" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I150" s="32" t="s">
         <v>41</v>
@@ -7303,7 +7309,7 @@
         <v>46314</v>
       </c>
       <c r="E151" s="28" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F151" s="28" t="s">
         <v>6</v>
@@ -7312,7 +7318,7 @@
         <v>79</v>
       </c>
       <c r="H151" s="30" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I151" s="32" t="s">
         <v>34</v>
@@ -7332,7 +7338,7 @@
         <v>46314</v>
       </c>
       <c r="E152" s="28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F152" s="28" t="s">
         <v>6</v>
@@ -7341,7 +7347,7 @@
         <v>28</v>
       </c>
       <c r="H152" s="30" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I152" s="32" t="s">
         <v>34</v>
@@ -7361,7 +7367,7 @@
         <v>46314</v>
       </c>
       <c r="E153" s="28" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F153" s="28" t="s">
         <v>6</v>
@@ -7370,7 +7376,7 @@
         <v>40</v>
       </c>
       <c r="H153" s="30" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I153" s="32" t="s">
         <v>34</v>
@@ -7390,7 +7396,7 @@
         <v>46349</v>
       </c>
       <c r="E154" s="28" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F154" s="28" t="s">
         <v>101</v>
@@ -7399,7 +7405,7 @@
         <v>382</v>
       </c>
       <c r="H154" s="30" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I154" s="32" t="s">
         <v>34</v>
@@ -7419,7 +7425,7 @@
         <v>46320</v>
       </c>
       <c r="E155" s="28" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F155" s="28" t="s">
         <v>6</v>
@@ -7428,7 +7434,7 @@
         <v>37</v>
       </c>
       <c r="H155" s="30" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I155" s="32" t="s">
         <v>35</v>
@@ -7448,7 +7454,7 @@
         <v>46320</v>
       </c>
       <c r="E156" s="28" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F156" s="28" t="s">
         <v>6</v>
@@ -7457,10 +7463,39 @@
         <v>2</v>
       </c>
       <c r="H156" s="30" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I156" s="32" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A157" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B157" s="29">
+        <v>46252</v>
+      </c>
+      <c r="C157" s="29">
+        <v>46260</v>
+      </c>
+      <c r="D157" s="29">
+        <v>46251</v>
+      </c>
+      <c r="E157" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="F157" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G157" s="30">
+        <v>72</v>
+      </c>
+      <c r="H157" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="I157" s="32" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -7477,7 +7512,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I156</xm:sqref>
+          <xm:sqref>I3:I157</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7598,7 +7633,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="98.5" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="E1"/>
     </row>
@@ -8013,7 +8048,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B82B9673-ED21-4933-9A9C-773CB2F4FD2E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21F0FBF6-0451-40C8-B423-889C41FA7726}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -8032,7 +8067,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BCADA38-B649-43B5-8987-30F05437E106}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADA0CAA6-D12E-4D7C-AAB9-4AA029DA1713}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -8040,18 +8075,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BE6D488-2A3F-46E6-B9DE-C01E1051C417}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F72A2010-86B8-46BF-B92C-C618682A2A19}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD45D7F5-8BFC-478A-A7EB-2725E928A57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8E4DB3A-3E82-4E0F-8548-C666ABE3A79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="422">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1223,6 +1223,15 @@
     <t>3740 Seaport Boulevard, Suite 10  West Sacramento CA 95691</t>
   </si>
   <si>
+    <t>Levine Management Group, Inc.</t>
+  </si>
+  <si>
+    <t>822 S. Robertson Suite #200  Los Angeles CA 90035</t>
+  </si>
+  <si>
+    <t>Relocation Permanent</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1242,7 +1251,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 08/26/2026
+01/01/2023 - 08/31/2026
 </t>
     </r>
     <r>
@@ -1256,10 +1265,160 @@
     </r>
   </si>
   <si>
-    <t>Levine Management Group, Inc.</t>
-  </si>
-  <si>
-    <t>822 S. Robertson Suite #200  Los Angeles CA 90035</t>
+    <t>John Muir Physician Network - 5860 Owens Drive</t>
+  </si>
+  <si>
+    <t>5860 Owens Drive  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>John Muir Health - Treat Blvd.</t>
+  </si>
+  <si>
+    <t>1400 Treat Boulevard  Walnut Creek CA 94597</t>
+  </si>
+  <si>
+    <t>John Muir Health - 1450 Treat Blvd.</t>
+  </si>
+  <si>
+    <t>1450 Treat Boulevard  Walnut Creek CA 94597</t>
+  </si>
+  <si>
+    <t>John Muir Health - 1601 Ygnacio Valley Road</t>
+  </si>
+  <si>
+    <t>1601 Ygnacio Valley Road  Walnut Creek CA 94597</t>
+  </si>
+  <si>
+    <t>John Muir Health - 177 La Casa Via</t>
+  </si>
+  <si>
+    <t>177 La Casa Via  Walnut Creek CA 94598</t>
+  </si>
+  <si>
+    <t>John Muir Health - 2540 East Street</t>
+  </si>
+  <si>
+    <t>2540 East Street  Concord CA 94520</t>
+  </si>
+  <si>
+    <t>John Muir Health - 2740 Grant Street</t>
+  </si>
+  <si>
+    <t>2740 Grant Street  Concord CA 94520</t>
+  </si>
+  <si>
+    <t>John Muir Health - 3480 Buskirk Ave.</t>
+  </si>
+  <si>
+    <t>3480 Buskirk Avenue  Pleasant Hill CA 94523</t>
+  </si>
+  <si>
+    <t>John Muir Health - 5003 Commercial Circle</t>
+  </si>
+  <si>
+    <t>5003 Commercial Circle  Concord CA 94520</t>
+  </si>
+  <si>
+    <t>John Muir Physician Network - 1450 Treat Blvd.</t>
+  </si>
+  <si>
+    <t>John Muir Physician Network - 1601 Ygnacio Valley Road</t>
+  </si>
+  <si>
+    <t>John Muir Physician Network - 2700 Grant Street</t>
+  </si>
+  <si>
+    <t>2700 Grant Street  Concord CA 94520</t>
+  </si>
+  <si>
+    <t>John Muir Behavioral Health - 2740 Grant Street</t>
+  </si>
+  <si>
+    <t>John Muir Health - 2700 Grant Street</t>
+  </si>
+  <si>
+    <t>RTX</t>
+  </si>
+  <si>
+    <t>2012 E El Segundo Blvd BLDG E07  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>Raley's Store No. 336</t>
+  </si>
+  <si>
+    <t>2400 Sand Creek Rd.  Brentwood CA 94513</t>
+  </si>
+  <si>
+    <t>Stanford Health Care - 1830 Embarcadero Rd.</t>
+  </si>
+  <si>
+    <t>1830 Embarcadero Rd  Palo Alto CA 94304</t>
+  </si>
+  <si>
+    <t>Stanford Health Care - 1840 Embarcadero Rd.</t>
+  </si>
+  <si>
+    <t>1840 Embarcadero Rd.  Palo Alto CA 94304</t>
+  </si>
+  <si>
+    <t>Power Safety Service, LLC</t>
+  </si>
+  <si>
+    <t>5440 E. Harney Lane  Lodi CA 95240</t>
+  </si>
+  <si>
+    <t>Telecare Corporation - Brighter Tomorrow, Program 162</t>
+  </si>
+  <si>
+    <t>1750 B South Lewis Road  Camarillo CA 93012</t>
+  </si>
+  <si>
+    <t>Telecare Corporation - House of Transitions</t>
+  </si>
+  <si>
+    <t>1750 C South Lewis Road  Camarillo CA 93012</t>
+  </si>
+  <si>
+    <t>Telecare Corporation - Recovery Starship</t>
+  </si>
+  <si>
+    <t>1760 South Lewis Road  Camarillo CA 93012</t>
+  </si>
+  <si>
+    <t>Telecare Corporation - Stonehedge</t>
+  </si>
+  <si>
+    <t>1758 South Lewis Road  Camarillo CA 93012</t>
+  </si>
+  <si>
+    <t>Astrion</t>
+  </si>
+  <si>
+    <t>305 E Popson Ave  Edwards CA 93524</t>
+  </si>
+  <si>
+    <t>Amazon - SJC13</t>
+  </si>
+  <si>
+    <t>1160 Enterprise Way  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>Synopsys, Inc.</t>
+  </si>
+  <si>
+    <t>675 Almanor Ave  Sunnyvale CA 94085</t>
+  </si>
+  <si>
+    <t>Amazon - SF019</t>
+  </si>
+  <si>
+    <t>350 Bush Street  San Francisco CA 94104</t>
+  </si>
+  <si>
+    <t>24Hr Homecare, LLC</t>
+  </si>
+  <si>
+    <t>200 N. Pacific Coast Highway, Suite 300  El Segundo CA 90245</t>
   </si>
   <si>
     <r>
@@ -1273,7 +1432,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 08/26/2026</t>
+      <t>07/01/26 to 08/31/2026</t>
     </r>
     <r>
       <rPr>
@@ -1293,7 +1452,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I157.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I187.</t>
     </r>
   </si>
 </sst>
@@ -2459,8 +2618,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I157" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I157" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I187" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I187" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2881,7 +3040,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>7842</v>
+        <v>9425</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -2890,7 +3049,7 @@
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>101</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2917,7 +3076,7 @@
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -2949,7 +3108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I157"/>
+  <dimension ref="A1:I187"/>
   <sheetFormatPr defaultColWidth="161.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.6328125" style="3" bestFit="1" customWidth="1"/>
@@ -2957,7 +3116,7 @@
     <col min="3" max="3" width="11.7265625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="43.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.08984375" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="48.08984375" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="49.453125" style="3" bestFit="1" customWidth="1"/>
@@ -2970,7 +3129,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="100" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
       <c r="E1" s="3"/>
     </row>
@@ -7022,7 +7181,7 @@
         <v>338</v>
       </c>
       <c r="F141" s="28" t="s">
-        <v>6</v>
+        <v>367</v>
       </c>
       <c r="G141" s="30">
         <v>73</v>
@@ -7483,7 +7642,7 @@
         <v>46251</v>
       </c>
       <c r="E157" s="28" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F157" s="28" t="s">
         <v>6</v>
@@ -7492,10 +7651,880 @@
         <v>72</v>
       </c>
       <c r="H157" s="30" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I157" s="32" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A158" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B158" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C158" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D158" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E158" s="28" t="s">
+        <v>369</v>
+      </c>
+      <c r="F158" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G158" s="30">
+        <v>1</v>
+      </c>
+      <c r="H158" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="I158" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A159" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B159" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C159" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D159" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E159" s="28" t="s">
+        <v>371</v>
+      </c>
+      <c r="F159" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G159" s="30">
+        <v>23</v>
+      </c>
+      <c r="H159" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="I159" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A160" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B160" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C160" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D160" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E160" s="28" t="s">
+        <v>373</v>
+      </c>
+      <c r="F160" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G160" s="30">
+        <v>4</v>
+      </c>
+      <c r="H160" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="I160" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A161" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B161" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C161" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D161" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E161" s="28" t="s">
+        <v>375</v>
+      </c>
+      <c r="F161" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G161" s="30">
+        <v>15</v>
+      </c>
+      <c r="H161" s="30" t="s">
+        <v>376</v>
+      </c>
+      <c r="I161" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A162" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B162" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C162" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D162" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E162" s="28" t="s">
+        <v>377</v>
+      </c>
+      <c r="F162" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G162" s="30">
+        <v>2</v>
+      </c>
+      <c r="H162" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="I162" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A163" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B163" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C163" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D163" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E163" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="F163" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G163" s="30">
+        <v>15</v>
+      </c>
+      <c r="H163" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="I163" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A164" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B164" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C164" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D164" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E164" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="F164" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G164" s="30">
+        <v>3</v>
+      </c>
+      <c r="H164" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="I164" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A165" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B165" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C165" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D165" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E165" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="F165" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G165" s="30">
+        <v>2</v>
+      </c>
+      <c r="H165" s="30" t="s">
+        <v>382</v>
+      </c>
+      <c r="I165" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A166" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B166" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C166" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D166" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E166" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="F166" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G166" s="30">
+        <v>1</v>
+      </c>
+      <c r="H166" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="I166" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A167" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B167" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C167" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D167" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E167" s="28" t="s">
+        <v>385</v>
+      </c>
+      <c r="F167" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G167" s="30">
+        <v>2</v>
+      </c>
+      <c r="H167" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="I167" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A168" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B168" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C168" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D168" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E168" s="28" t="s">
+        <v>387</v>
+      </c>
+      <c r="F168" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G168" s="30">
+        <v>6</v>
+      </c>
+      <c r="H168" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="I168" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A169" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B169" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C169" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D169" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E169" s="28" t="s">
+        <v>388</v>
+      </c>
+      <c r="F169" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G169" s="30">
+        <v>1</v>
+      </c>
+      <c r="H169" s="30" t="s">
+        <v>376</v>
+      </c>
+      <c r="I169" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A170" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B170" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C170" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D170" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E170" s="28" t="s">
+        <v>389</v>
+      </c>
+      <c r="F170" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G170" s="30">
+        <v>1</v>
+      </c>
+      <c r="H170" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="I170" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A171" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B171" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C171" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D171" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E171" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="F171" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G171" s="30">
+        <v>1</v>
+      </c>
+      <c r="H171" s="30" t="s">
+        <v>382</v>
+      </c>
+      <c r="I171" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A172" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B172" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C172" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D172" s="29">
+        <v>46323</v>
+      </c>
+      <c r="E172" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="F172" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G172" s="30">
+        <v>1</v>
+      </c>
+      <c r="H172" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="I172" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A173" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B173" s="29">
+        <v>46259</v>
+      </c>
+      <c r="C173" s="29">
+        <v>46261</v>
+      </c>
+      <c r="D173" s="29">
+        <v>46318</v>
+      </c>
+      <c r="E173" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="F173" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G173" s="30">
+        <v>7</v>
+      </c>
+      <c r="H173" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="I173" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A174" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B174" s="29">
+        <v>46261</v>
+      </c>
+      <c r="C174" s="29">
+        <v>46262</v>
+      </c>
+      <c r="D174" s="29">
+        <v>46329</v>
+      </c>
+      <c r="E174" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="F174" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G174" s="30">
+        <v>51</v>
+      </c>
+      <c r="H174" s="30" t="s">
+        <v>396</v>
+      </c>
+      <c r="I174" s="32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A175" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B175" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C175" s="29">
+        <v>46262</v>
+      </c>
+      <c r="D175" s="29">
+        <v>46328</v>
+      </c>
+      <c r="E175" s="28" t="s">
+        <v>397</v>
+      </c>
+      <c r="F175" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G175" s="30">
+        <v>79</v>
+      </c>
+      <c r="H175" s="30" t="s">
+        <v>398</v>
+      </c>
+      <c r="I175" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A176" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B176" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C176" s="29">
+        <v>46262</v>
+      </c>
+      <c r="D176" s="29">
+        <v>46328</v>
+      </c>
+      <c r="E176" s="28" t="s">
+        <v>399</v>
+      </c>
+      <c r="F176" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G176" s="30">
+        <v>16</v>
+      </c>
+      <c r="H176" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="I176" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A177" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B177" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C177" s="29">
+        <v>46262</v>
+      </c>
+      <c r="D177" s="29">
+        <v>46325</v>
+      </c>
+      <c r="E177" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="F177" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G177" s="30">
+        <v>53</v>
+      </c>
+      <c r="H177" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="I177" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A178" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="B178" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C178" s="29">
+        <v>46262</v>
+      </c>
+      <c r="D178" s="29">
+        <v>46332</v>
+      </c>
+      <c r="E178" s="28" t="s">
+        <v>401</v>
+      </c>
+      <c r="F178" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G178" s="30">
+        <v>189</v>
+      </c>
+      <c r="H178" s="30" t="s">
+        <v>402</v>
+      </c>
+      <c r="I178" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A179" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B179" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C179" s="29">
+        <v>46262</v>
+      </c>
+      <c r="D179" s="29">
+        <v>46324</v>
+      </c>
+      <c r="E179" s="28" t="s">
+        <v>403</v>
+      </c>
+      <c r="F179" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G179" s="30">
+        <v>23</v>
+      </c>
+      <c r="H179" s="30" t="s">
+        <v>404</v>
+      </c>
+      <c r="I179" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A180" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B180" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C180" s="29">
+        <v>46262</v>
+      </c>
+      <c r="D180" s="29">
+        <v>46324</v>
+      </c>
+      <c r="E180" s="28" t="s">
+        <v>405</v>
+      </c>
+      <c r="F180" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G180" s="30">
+        <v>16</v>
+      </c>
+      <c r="H180" s="30" t="s">
+        <v>406</v>
+      </c>
+      <c r="I180" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A181" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B181" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C181" s="29">
+        <v>46262</v>
+      </c>
+      <c r="D181" s="29">
+        <v>46324</v>
+      </c>
+      <c r="E181" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="F181" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G181" s="30">
+        <v>16</v>
+      </c>
+      <c r="H181" s="30" t="s">
+        <v>408</v>
+      </c>
+      <c r="I181" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A182" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B182" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C182" s="29">
+        <v>46262</v>
+      </c>
+      <c r="D182" s="29">
+        <v>46324</v>
+      </c>
+      <c r="E182" s="28" t="s">
+        <v>409</v>
+      </c>
+      <c r="F182" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G182" s="30">
+        <v>13</v>
+      </c>
+      <c r="H182" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="I182" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A183" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="B183" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C183" s="29">
+        <v>46265</v>
+      </c>
+      <c r="D183" s="29">
+        <v>46295</v>
+      </c>
+      <c r="E183" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="F183" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G183" s="30">
+        <v>28</v>
+      </c>
+      <c r="H183" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="I183" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A184" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B184" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C184" s="29">
+        <v>46265</v>
+      </c>
+      <c r="D184" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E184" s="28" t="s">
+        <v>413</v>
+      </c>
+      <c r="F184" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G184" s="30">
+        <v>70</v>
+      </c>
+      <c r="H184" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="I184" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A185" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B185" s="29">
+        <v>46265</v>
+      </c>
+      <c r="C185" s="29">
+        <v>46265</v>
+      </c>
+      <c r="D185" s="29">
+        <v>46372</v>
+      </c>
+      <c r="E185" s="28" t="s">
+        <v>415</v>
+      </c>
+      <c r="F185" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G185" s="30">
+        <v>128</v>
+      </c>
+      <c r="H185" s="30" t="s">
+        <v>416</v>
+      </c>
+      <c r="I185" s="32" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A186" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="B186" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C186" s="29">
+        <v>46265</v>
+      </c>
+      <c r="D186" s="29">
+        <v>46315</v>
+      </c>
+      <c r="E186" s="28" t="s">
+        <v>417</v>
+      </c>
+      <c r="F186" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G186" s="30">
+        <v>78</v>
+      </c>
+      <c r="H186" s="30" t="s">
+        <v>418</v>
+      </c>
+      <c r="I186" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A187" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B187" s="29">
+        <v>46265</v>
+      </c>
+      <c r="C187" s="29">
+        <v>46265</v>
+      </c>
+      <c r="D187" s="29">
+        <v>46280</v>
+      </c>
+      <c r="E187" s="28" t="s">
+        <v>419</v>
+      </c>
+      <c r="F187" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G187" s="30">
+        <v>738</v>
+      </c>
+      <c r="H187" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="I187" s="32" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -7512,7 +8541,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I157</xm:sqref>
+          <xm:sqref>I3:I187</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7633,7 +8662,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="98.5" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E1"/>
     </row>
@@ -8048,7 +9077,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21F0FBF6-0451-40C8-B423-889C41FA7726}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57352F60-0FA2-4515-85B2-A5D11A83DA02}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -8067,7 +9096,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADA0CAA6-D12E-4D7C-AAB9-4AA029DA1713}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53F2EFFE-C1BF-492E-A55D-4D62B857E2F2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -8075,18 +9104,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F72A2010-86B8-46BF-B92C-C618682A2A19}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737EBD67-6909-417A-9A96-7CE6BE680C99}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/warn_report.xlsx
+++ b/data/warn_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edd.sharepoint.com/sites/WSB-COWSD-380-PCU/Shared Documents/Website Management/3. Webpage Updates/Layoff Services WARN/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D8E4DB3A-3E82-4E0F-8548-C666ABE3A79E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{977414B1-1E03-445E-9029-4301A02576F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="751" xr2:uid="{3EA4B9A5-CE9D-4ACF-B45F-4158810915D4}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="434">
   <si>
     <t>County/Parish</t>
   </si>
@@ -1232,6 +1232,162 @@
     <t>Relocation Permanent</t>
   </si>
   <si>
+    <t>John Muir Physician Network - 5860 Owens Drive</t>
+  </si>
+  <si>
+    <t>5860 Owens Drive  Pleasanton CA 94588</t>
+  </si>
+  <si>
+    <t>John Muir Health - Treat Blvd.</t>
+  </si>
+  <si>
+    <t>1400 Treat Boulevard  Walnut Creek CA 94597</t>
+  </si>
+  <si>
+    <t>John Muir Health - 1450 Treat Blvd.</t>
+  </si>
+  <si>
+    <t>1450 Treat Boulevard  Walnut Creek CA 94597</t>
+  </si>
+  <si>
+    <t>John Muir Health - 1601 Ygnacio Valley Road</t>
+  </si>
+  <si>
+    <t>1601 Ygnacio Valley Road  Walnut Creek CA 94597</t>
+  </si>
+  <si>
+    <t>John Muir Health - 177 La Casa Via</t>
+  </si>
+  <si>
+    <t>177 La Casa Via  Walnut Creek CA 94598</t>
+  </si>
+  <si>
+    <t>John Muir Health - 2540 East Street</t>
+  </si>
+  <si>
+    <t>2540 East Street  Concord CA 94520</t>
+  </si>
+  <si>
+    <t>John Muir Health - 2740 Grant Street</t>
+  </si>
+  <si>
+    <t>2740 Grant Street  Concord CA 94520</t>
+  </si>
+  <si>
+    <t>John Muir Health - 3480 Buskirk Ave.</t>
+  </si>
+  <si>
+    <t>3480 Buskirk Avenue  Pleasant Hill CA 94523</t>
+  </si>
+  <si>
+    <t>John Muir Health - 5003 Commercial Circle</t>
+  </si>
+  <si>
+    <t>5003 Commercial Circle  Concord CA 94520</t>
+  </si>
+  <si>
+    <t>John Muir Physician Network - 1450 Treat Blvd.</t>
+  </si>
+  <si>
+    <t>John Muir Physician Network - 1601 Ygnacio Valley Road</t>
+  </si>
+  <si>
+    <t>John Muir Physician Network - 2700 Grant Street</t>
+  </si>
+  <si>
+    <t>2700 Grant Street  Concord CA 94520</t>
+  </si>
+  <si>
+    <t>John Muir Behavioral Health - 2740 Grant Street</t>
+  </si>
+  <si>
+    <t>John Muir Health - 2700 Grant Street</t>
+  </si>
+  <si>
+    <t>RTX</t>
+  </si>
+  <si>
+    <t>2012 E El Segundo Blvd BLDG E07  El Segundo CA 90245</t>
+  </si>
+  <si>
+    <t>Raley's Store No. 336</t>
+  </si>
+  <si>
+    <t>2400 Sand Creek Rd.  Brentwood CA 94513</t>
+  </si>
+  <si>
+    <t>Stanford Health Care - 1830 Embarcadero Rd.</t>
+  </si>
+  <si>
+    <t>1830 Embarcadero Rd  Palo Alto CA 94304</t>
+  </si>
+  <si>
+    <t>Stanford Health Care - 1840 Embarcadero Rd.</t>
+  </si>
+  <si>
+    <t>1840 Embarcadero Rd.  Palo Alto CA 94304</t>
+  </si>
+  <si>
+    <t>Power Safety Service, LLC</t>
+  </si>
+  <si>
+    <t>5440 E. Harney Lane  Lodi CA 95240</t>
+  </si>
+  <si>
+    <t>Telecare Corporation - Brighter Tomorrow, Program 162</t>
+  </si>
+  <si>
+    <t>1750 B South Lewis Road  Camarillo CA 93012</t>
+  </si>
+  <si>
+    <t>Telecare Corporation - House of Transitions</t>
+  </si>
+  <si>
+    <t>1750 C South Lewis Road  Camarillo CA 93012</t>
+  </si>
+  <si>
+    <t>Telecare Corporation - Recovery Starship</t>
+  </si>
+  <si>
+    <t>1760 South Lewis Road  Camarillo CA 93012</t>
+  </si>
+  <si>
+    <t>Telecare Corporation - Stonehedge</t>
+  </si>
+  <si>
+    <t>1758 South Lewis Road  Camarillo CA 93012</t>
+  </si>
+  <si>
+    <t>Astrion</t>
+  </si>
+  <si>
+    <t>305 E Popson Ave  Edwards CA 93524</t>
+  </si>
+  <si>
+    <t>Amazon - SJC13</t>
+  </si>
+  <si>
+    <t>1160 Enterprise Way  Sunnyvale CA 94089</t>
+  </si>
+  <si>
+    <t>Synopsys, Inc.</t>
+  </si>
+  <si>
+    <t>675 Almanor Ave  Sunnyvale CA 94085</t>
+  </si>
+  <si>
+    <t>Amazon - SF019</t>
+  </si>
+  <si>
+    <t>350 Bush Street  San Francisco CA 94104</t>
+  </si>
+  <si>
+    <t>24Hr Homecare, LLC</t>
+  </si>
+  <si>
+    <t>200 N. Pacific Coast Highway, Suite 300  El Segundo CA 90245</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1251,7 +1407,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-01/01/2023 - 08/31/2026
+01/01/2023 - 09/02/2026
 </t>
     </r>
     <r>
@@ -1265,160 +1421,40 @@
     </r>
   </si>
   <si>
-    <t>John Muir Physician Network - 5860 Owens Drive</t>
-  </si>
-  <si>
-    <t>5860 Owens Drive  Pleasanton CA 94588</t>
-  </si>
-  <si>
-    <t>John Muir Health - Treat Blvd.</t>
-  </si>
-  <si>
-    <t>1400 Treat Boulevard  Walnut Creek CA 94597</t>
-  </si>
-  <si>
-    <t>John Muir Health - 1450 Treat Blvd.</t>
-  </si>
-  <si>
-    <t>1450 Treat Boulevard  Walnut Creek CA 94597</t>
-  </si>
-  <si>
-    <t>John Muir Health - 1601 Ygnacio Valley Road</t>
-  </si>
-  <si>
-    <t>1601 Ygnacio Valley Road  Walnut Creek CA 94597</t>
-  </si>
-  <si>
-    <t>John Muir Health - 177 La Casa Via</t>
-  </si>
-  <si>
-    <t>177 La Casa Via  Walnut Creek CA 94598</t>
-  </si>
-  <si>
-    <t>John Muir Health - 2540 East Street</t>
-  </si>
-  <si>
-    <t>2540 East Street  Concord CA 94520</t>
-  </si>
-  <si>
-    <t>John Muir Health - 2740 Grant Street</t>
-  </si>
-  <si>
-    <t>2740 Grant Street  Concord CA 94520</t>
-  </si>
-  <si>
-    <t>John Muir Health - 3480 Buskirk Ave.</t>
-  </si>
-  <si>
-    <t>3480 Buskirk Avenue  Pleasant Hill CA 94523</t>
-  </si>
-  <si>
-    <t>John Muir Health - 5003 Commercial Circle</t>
-  </si>
-  <si>
-    <t>5003 Commercial Circle  Concord CA 94520</t>
-  </si>
-  <si>
-    <t>John Muir Physician Network - 1450 Treat Blvd.</t>
-  </si>
-  <si>
-    <t>John Muir Physician Network - 1601 Ygnacio Valley Road</t>
-  </si>
-  <si>
-    <t>John Muir Physician Network - 2700 Grant Street</t>
-  </si>
-  <si>
-    <t>2700 Grant Street  Concord CA 94520</t>
-  </si>
-  <si>
-    <t>John Muir Behavioral Health - 2740 Grant Street</t>
-  </si>
-  <si>
-    <t>John Muir Health - 2700 Grant Street</t>
-  </si>
-  <si>
-    <t>RTX</t>
-  </si>
-  <si>
-    <t>2012 E El Segundo Blvd BLDG E07  El Segundo CA 90245</t>
-  </si>
-  <si>
-    <t>Raley's Store No. 336</t>
-  </si>
-  <si>
-    <t>2400 Sand Creek Rd.  Brentwood CA 94513</t>
-  </si>
-  <si>
-    <t>Stanford Health Care - 1830 Embarcadero Rd.</t>
-  </si>
-  <si>
-    <t>1830 Embarcadero Rd  Palo Alto CA 94304</t>
-  </si>
-  <si>
-    <t>Stanford Health Care - 1840 Embarcadero Rd.</t>
-  </si>
-  <si>
-    <t>1840 Embarcadero Rd.  Palo Alto CA 94304</t>
-  </si>
-  <si>
-    <t>Power Safety Service, LLC</t>
-  </si>
-  <si>
-    <t>5440 E. Harney Lane  Lodi CA 95240</t>
-  </si>
-  <si>
-    <t>Telecare Corporation - Brighter Tomorrow, Program 162</t>
-  </si>
-  <si>
-    <t>1750 B South Lewis Road  Camarillo CA 93012</t>
-  </si>
-  <si>
-    <t>Telecare Corporation - House of Transitions</t>
-  </si>
-  <si>
-    <t>1750 C South Lewis Road  Camarillo CA 93012</t>
-  </si>
-  <si>
-    <t>Telecare Corporation - Recovery Starship</t>
-  </si>
-  <si>
-    <t>1760 South Lewis Road  Camarillo CA 93012</t>
-  </si>
-  <si>
-    <t>Telecare Corporation - Stonehedge</t>
-  </si>
-  <si>
-    <t>1758 South Lewis Road  Camarillo CA 93012</t>
-  </si>
-  <si>
-    <t>Astrion</t>
-  </si>
-  <si>
-    <t>305 E Popson Ave  Edwards CA 93524</t>
-  </si>
-  <si>
-    <t>Amazon - SJC13</t>
-  </si>
-  <si>
-    <t>1160 Enterprise Way  Sunnyvale CA 94089</t>
-  </si>
-  <si>
-    <t>Synopsys, Inc.</t>
-  </si>
-  <si>
-    <t>675 Almanor Ave  Sunnyvale CA 94085</t>
-  </si>
-  <si>
-    <t>Amazon - SF019</t>
-  </si>
-  <si>
-    <t>350 Bush Street  San Francisco CA 94104</t>
-  </si>
-  <si>
-    <t>24Hr Homecare, LLC</t>
-  </si>
-  <si>
-    <t>200 N. Pacific Coast Highway, Suite 300  El Segundo CA 90245</t>
+    <t>Renewal by Andersen LLC</t>
+  </si>
+  <si>
+    <t>18700 Crenshaw Blvd  Torrance CA 90504</t>
+  </si>
+  <si>
+    <t>PayPal</t>
+  </si>
+  <si>
+    <t>2211 N. First Street  San Jose CA 95131</t>
+  </si>
+  <si>
+    <t>22982 Alcalde Drive, Suite 100  Laguna Hills CA 92653</t>
+  </si>
+  <si>
+    <t>Clarmil Manufacturing Corporation</t>
+  </si>
+  <si>
+    <t>30865 San Clemente Street  Hayward CA 94544</t>
+  </si>
+  <si>
+    <t>Arsenal Biosciences, Inc.</t>
+  </si>
+  <si>
+    <t>329 Oyster Point Blvd  South San Francisco CA 94080</t>
+  </si>
+  <si>
+    <t>654 N Harington Dr.  Orange CA 92868</t>
+  </si>
+  <si>
+    <t>Foundation for California Community Colleges</t>
+  </si>
+  <si>
+    <t>1102 Q Street, Suite 4800  Sacramento CA 95811</t>
   </si>
   <si>
     <r>
@@ -1432,7 +1468,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>07/01/26 to 08/31/2026</t>
+      <t>07/01/26 to 09/02/2026</t>
     </r>
     <r>
       <rPr>
@@ -1452,7 +1488,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I187.</t>
+      <t>A detailed WARN summary by county and filtered according to processed date. Table Spans cells A2 through I194.</t>
     </r>
   </si>
 </sst>
@@ -1567,6 +1603,7 @@
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2618,8 +2655,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I187" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
-  <autoFilter ref="A2:I187" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}" name="DetailedWarnReport" displayName="DetailedWarnReport" ref="A2:I194" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+  <autoFilter ref="A2:I194" xr:uid="{1F69E8FD-21FF-4B81-951D-D7EC70F8E5F9}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I42">
     <sortCondition ref="C2:C42"/>
   </sortState>
@@ -2966,37 +3003,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D341DFFF-02D2-4572-95F5-BB3221952133}">
   <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="73.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="74" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" ht="135" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:1" ht="21" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>24</v>
       </c>
@@ -3015,18 +3052,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832896D-8AFB-4FFC-957E-910308F3BC0C}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.36328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="76.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>16</v>
       </c>
@@ -3034,25 +3071,25 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="11">
         <f>SUM('Detailed WARN Report '!G:G)</f>
-        <v>9425</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>10304</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Layoff Permanent")</f>
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -3061,7 +3098,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -3070,16 +3107,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="11">
         <f>COUNTIF('Detailed WARN Report '!F:F,"Closure Permanent")</f>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -3088,7 +3125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -3108,32 +3145,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E7117B-AC46-45AC-B2F3-AE611FA82488}">
-  <dimension ref="A1:I187"/>
-  <sheetFormatPr defaultColWidth="161.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I194"/>
+  <sheetFormatPr defaultColWidth="161.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.6328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="48.08984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="49.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.54296875" customWidth="1"/>
-    <col min="11" max="11" width="13.1796875" customWidth="1"/>
-    <col min="12" max="12" width="12.7265625" customWidth="1"/>
-    <col min="13" max="13" width="11.81640625" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="50.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="51.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" customWidth="1"/>
     <col min="14" max="14" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="100" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="102" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" ht="24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
@@ -3162,7 +3199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>5</v>
       </c>
@@ -3191,7 +3228,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
         <v>55</v>
       </c>
@@ -3220,7 +3257,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
         <v>54</v>
       </c>
@@ -3249,7 +3286,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>56</v>
       </c>
@@ -3278,7 +3315,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>5</v>
       </c>
@@ -3307,7 +3344,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>53</v>
       </c>
@@ -3336,7 +3373,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>53</v>
       </c>
@@ -3365,7 +3402,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>57</v>
       </c>
@@ -3394,7 +3431,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
         <v>55</v>
       </c>
@@ -3423,7 +3460,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>76</v>
       </c>
@@ -3452,7 +3489,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
         <v>79</v>
       </c>
@@ -3481,7 +3518,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>82</v>
       </c>
@@ -3510,7 +3547,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
         <v>53</v>
       </c>
@@ -3539,7 +3576,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
         <v>5</v>
       </c>
@@ -3568,7 +3605,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
         <v>54</v>
       </c>
@@ -3597,7 +3634,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>53</v>
       </c>
@@ -3626,7 +3663,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>53</v>
       </c>
@@ -3655,7 +3692,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>54</v>
       </c>
@@ -3684,7 +3721,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
         <v>79</v>
       </c>
@@ -3713,7 +3750,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
         <v>99</v>
       </c>
@@ -3742,7 +3779,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
         <v>103</v>
       </c>
@@ -3771,7 +3808,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
         <v>53</v>
       </c>
@@ -3800,7 +3837,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
         <v>103</v>
       </c>
@@ -3829,7 +3866,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
         <v>110</v>
       </c>
@@ -3858,7 +3895,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="28" t="s">
         <v>5</v>
       </c>
@@ -3887,7 +3924,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
         <v>5</v>
       </c>
@@ -3916,7 +3953,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
         <v>5</v>
       </c>
@@ -3945,7 +3982,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
         <v>5</v>
       </c>
@@ -3974,7 +4011,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
         <v>5</v>
       </c>
@@ -4003,7 +4040,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
         <v>54</v>
       </c>
@@ -4032,7 +4069,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
         <v>103</v>
       </c>
@@ -4061,7 +4098,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
         <v>127</v>
       </c>
@@ -4090,7 +4127,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
         <v>103</v>
       </c>
@@ -4119,7 +4156,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
         <v>53</v>
       </c>
@@ -4148,7 +4185,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
         <v>135</v>
       </c>
@@ -4177,7 +4214,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
         <v>138</v>
       </c>
@@ -4206,7 +4243,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="28" t="s">
         <v>103</v>
       </c>
@@ -4235,7 +4272,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
         <v>76</v>
       </c>
@@ -4264,7 +4301,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="28" t="s">
         <v>138</v>
       </c>
@@ -4293,7 +4330,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="28" t="s">
         <v>138</v>
       </c>
@@ -4322,7 +4359,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
         <v>149</v>
       </c>
@@ -4351,7 +4388,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
         <v>79</v>
       </c>
@@ -4380,7 +4417,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="33" t="s">
         <v>79</v>
       </c>
@@ -4409,7 +4446,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="33" t="s">
         <v>79</v>
       </c>
@@ -4438,7 +4475,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="33" t="s">
         <v>5</v>
       </c>
@@ -4467,7 +4504,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="33" t="s">
         <v>160</v>
       </c>
@@ -4496,7 +4533,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="33" t="s">
         <v>103</v>
       </c>
@@ -4525,7 +4562,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
         <v>103</v>
       </c>
@@ -4554,7 +4591,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="33" t="s">
         <v>103</v>
       </c>
@@ -4583,7 +4620,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="33" t="s">
         <v>103</v>
       </c>
@@ -4612,7 +4649,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="33" t="s">
         <v>171</v>
       </c>
@@ -4641,7 +4678,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="33" t="s">
         <v>171</v>
       </c>
@@ -4670,7 +4707,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="28" t="s">
         <v>53</v>
       </c>
@@ -4699,7 +4736,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="28" t="s">
         <v>76</v>
       </c>
@@ -4728,7 +4765,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="28" t="s">
         <v>180</v>
       </c>
@@ -4757,7 +4794,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="28" t="s">
         <v>5</v>
       </c>
@@ -4786,7 +4823,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="28" t="s">
         <v>5</v>
       </c>
@@ -4815,7 +4852,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="28" t="s">
         <v>53</v>
       </c>
@@ -4844,7 +4881,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="28" t="s">
         <v>189</v>
       </c>
@@ -4873,7 +4910,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="28" t="s">
         <v>56</v>
       </c>
@@ -4902,7 +4939,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="28" t="s">
         <v>55</v>
       </c>
@@ -4931,7 +4968,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="28" t="s">
         <v>110</v>
       </c>
@@ -4960,7 +4997,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="28" t="s">
         <v>110</v>
       </c>
@@ -4989,7 +5026,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="28" t="s">
         <v>199</v>
       </c>
@@ -5018,7 +5055,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="28" t="s">
         <v>138</v>
       </c>
@@ -5047,7 +5084,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="28" t="s">
         <v>138</v>
       </c>
@@ -5076,7 +5113,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="28" t="s">
         <v>103</v>
       </c>
@@ -5105,7 +5142,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="28" t="s">
         <v>207</v>
       </c>
@@ -5134,7 +5171,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="28" t="s">
         <v>171</v>
       </c>
@@ -5163,7 +5200,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="28" t="s">
         <v>53</v>
       </c>
@@ -5192,7 +5229,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="28" t="s">
         <v>189</v>
       </c>
@@ -5221,7 +5258,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="28" t="s">
         <v>54</v>
       </c>
@@ -5250,7 +5287,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="28" t="s">
         <v>216</v>
       </c>
@@ -5279,7 +5316,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="28" t="s">
         <v>56</v>
       </c>
@@ -5308,7 +5345,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="28" t="s">
         <v>171</v>
       </c>
@@ -5337,7 +5374,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="28" t="s">
         <v>180</v>
       </c>
@@ -5366,7 +5403,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="28" t="s">
         <v>180</v>
       </c>
@@ -5395,7 +5432,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="28" t="s">
         <v>180</v>
       </c>
@@ -5424,7 +5461,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="28" t="s">
         <v>180</v>
       </c>
@@ -5453,7 +5490,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="28" t="s">
         <v>180</v>
       </c>
@@ -5482,7 +5519,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="28" t="s">
         <v>55</v>
       </c>
@@ -5511,7 +5548,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="28" t="s">
         <v>53</v>
       </c>
@@ -5540,7 +5577,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="28" t="s">
         <v>53</v>
       </c>
@@ -5569,7 +5606,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="28" t="s">
         <v>54</v>
       </c>
@@ -5598,7 +5635,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="28" t="s">
         <v>54</v>
       </c>
@@ -5627,7 +5664,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="28" t="s">
         <v>79</v>
       </c>
@@ -5656,7 +5693,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="28" t="s">
         <v>79</v>
       </c>
@@ -5685,7 +5722,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="28" t="s">
         <v>103</v>
       </c>
@@ -5714,7 +5751,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="28" t="s">
         <v>54</v>
       </c>
@@ -5743,7 +5780,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="28" t="s">
         <v>79</v>
       </c>
@@ -5772,7 +5809,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="33" t="s">
         <v>5</v>
       </c>
@@ -5801,7 +5838,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="33" t="s">
         <v>5</v>
       </c>
@@ -5830,7 +5867,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="33" t="s">
         <v>5</v>
       </c>
@@ -5859,7 +5896,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="33" t="s">
         <v>5</v>
       </c>
@@ -5888,7 +5925,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="33" t="s">
         <v>189</v>
       </c>
@@ -5917,7 +5954,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="33" t="s">
         <v>56</v>
       </c>
@@ -5946,7 +5983,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="33" t="s">
         <v>171</v>
       </c>
@@ -5975,7 +6012,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="33" t="s">
         <v>260</v>
       </c>
@@ -6004,7 +6041,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="33" t="s">
         <v>171</v>
       </c>
@@ -6033,7 +6070,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="28" t="s">
         <v>5</v>
       </c>
@@ -6062,7 +6099,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="28" t="s">
         <v>189</v>
       </c>
@@ -6091,7 +6128,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="28" t="s">
         <v>207</v>
       </c>
@@ -6120,7 +6157,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="28" t="s">
         <v>207</v>
       </c>
@@ -6149,7 +6186,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="28" t="s">
         <v>207</v>
       </c>
@@ -6178,7 +6215,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="28" t="s">
         <v>207</v>
       </c>
@@ -6207,7 +6244,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="28" t="s">
         <v>207</v>
       </c>
@@ -6236,7 +6273,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="28" t="s">
         <v>5</v>
       </c>
@@ -6265,7 +6302,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="28" t="s">
         <v>76</v>
       </c>
@@ -6294,7 +6331,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="28" t="s">
         <v>76</v>
       </c>
@@ -6323,7 +6360,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="28" t="s">
         <v>76</v>
       </c>
@@ -6352,7 +6389,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="28" t="s">
         <v>76</v>
       </c>
@@ -6381,7 +6418,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="28" t="s">
         <v>76</v>
       </c>
@@ -6410,7 +6447,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="28" t="s">
         <v>76</v>
       </c>
@@ -6439,7 +6476,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="28" t="s">
         <v>76</v>
       </c>
@@ -6468,7 +6505,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="28" t="s">
         <v>76</v>
       </c>
@@ -6497,7 +6534,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="28" t="s">
         <v>76</v>
       </c>
@@ -6526,7 +6563,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="28" t="s">
         <v>76</v>
       </c>
@@ -6555,7 +6592,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="28" t="s">
         <v>76</v>
       </c>
@@ -6584,7 +6621,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="28" t="s">
         <v>76</v>
       </c>
@@ -6613,7 +6650,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="28" t="s">
         <v>76</v>
       </c>
@@ -6642,7 +6679,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="28" t="s">
         <v>76</v>
       </c>
@@ -6671,7 +6708,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="28" t="s">
         <v>76</v>
       </c>
@@ -6700,7 +6737,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="28" t="s">
         <v>76</v>
       </c>
@@ -6729,7 +6766,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="28" t="s">
         <v>76</v>
       </c>
@@ -6758,7 +6795,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="28" t="s">
         <v>57</v>
       </c>
@@ -6787,7 +6824,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="28" t="s">
         <v>57</v>
       </c>
@@ -6816,7 +6853,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="28" t="s">
         <v>5</v>
       </c>
@@ -6845,7 +6882,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="28" t="s">
         <v>5</v>
       </c>
@@ -6874,7 +6911,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="28" t="s">
         <v>5</v>
       </c>
@@ -6903,7 +6940,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="28" t="s">
         <v>55</v>
       </c>
@@ -6932,7 +6969,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="28" t="s">
         <v>57</v>
       </c>
@@ -6961,7 +6998,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="28" t="s">
         <v>323</v>
       </c>
@@ -6990,7 +7027,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="28" t="s">
         <v>326</v>
       </c>
@@ -7019,7 +7056,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="28" t="s">
         <v>207</v>
       </c>
@@ -7048,7 +7085,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="28" t="s">
         <v>207</v>
       </c>
@@ -7077,7 +7114,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="28" t="s">
         <v>207</v>
       </c>
@@ -7106,7 +7143,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="28" t="s">
         <v>55</v>
       </c>
@@ -7135,7 +7172,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="28" t="s">
         <v>171</v>
       </c>
@@ -7164,7 +7201,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="28" t="s">
         <v>326</v>
       </c>
@@ -7193,7 +7230,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="28" t="s">
         <v>76</v>
       </c>
@@ -7222,7 +7259,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="28" t="s">
         <v>342</v>
       </c>
@@ -7251,7 +7288,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="28" t="s">
         <v>342</v>
       </c>
@@ -7280,7 +7317,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="28" t="s">
         <v>5</v>
       </c>
@@ -7309,7 +7346,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="28" t="s">
         <v>5</v>
       </c>
@@ -7338,7 +7375,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="28" t="s">
         <v>56</v>
       </c>
@@ -7367,7 +7404,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="28" t="s">
         <v>207</v>
       </c>
@@ -7396,7 +7433,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="28" t="s">
         <v>323</v>
       </c>
@@ -7425,7 +7462,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="28" t="s">
         <v>55</v>
       </c>
@@ -7454,7 +7491,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="28" t="s">
         <v>103</v>
       </c>
@@ -7483,7 +7520,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="28" t="s">
         <v>103</v>
       </c>
@@ -7512,7 +7549,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="28" t="s">
         <v>103</v>
       </c>
@@ -7541,7 +7578,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="28" t="s">
         <v>103</v>
       </c>
@@ -7570,7 +7607,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="28" t="s">
         <v>54</v>
       </c>
@@ -7599,7 +7636,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="28" t="s">
         <v>99</v>
       </c>
@@ -7628,7 +7665,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="28" t="s">
         <v>5</v>
       </c>
@@ -7657,7 +7694,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="28" t="s">
         <v>76</v>
       </c>
@@ -7671,7 +7708,7 @@
         <v>46323</v>
       </c>
       <c r="E158" s="28" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F158" s="28" t="s">
         <v>6</v>
@@ -7680,13 +7717,13 @@
         <v>1</v>
       </c>
       <c r="H158" s="30" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I158" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="28" t="s">
         <v>57</v>
       </c>
@@ -7700,7 +7737,7 @@
         <v>46323</v>
       </c>
       <c r="E159" s="28" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F159" s="28" t="s">
         <v>6</v>
@@ -7709,13 +7746,13 @@
         <v>23</v>
       </c>
       <c r="H159" s="30" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I159" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="28" t="s">
         <v>57</v>
       </c>
@@ -7729,7 +7766,7 @@
         <v>46323</v>
       </c>
       <c r="E160" s="28" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F160" s="28" t="s">
         <v>6</v>
@@ -7738,13 +7775,13 @@
         <v>4</v>
       </c>
       <c r="H160" s="30" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I160" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="28" t="s">
         <v>57</v>
       </c>
@@ -7758,7 +7795,7 @@
         <v>46323</v>
       </c>
       <c r="E161" s="28" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F161" s="28" t="s">
         <v>6</v>
@@ -7767,13 +7804,13 @@
         <v>15</v>
       </c>
       <c r="H161" s="30" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I161" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="28" t="s">
         <v>57</v>
       </c>
@@ -7787,7 +7824,7 @@
         <v>46323</v>
       </c>
       <c r="E162" s="28" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F162" s="28" t="s">
         <v>6</v>
@@ -7796,13 +7833,13 @@
         <v>2</v>
       </c>
       <c r="H162" s="30" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I162" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="28" t="s">
         <v>57</v>
       </c>
@@ -7816,7 +7853,7 @@
         <v>46323</v>
       </c>
       <c r="E163" s="28" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F163" s="28" t="s">
         <v>6</v>
@@ -7825,13 +7862,13 @@
         <v>15</v>
       </c>
       <c r="H163" s="30" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I163" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="28" t="s">
         <v>57</v>
       </c>
@@ -7845,7 +7882,7 @@
         <v>46323</v>
       </c>
       <c r="E164" s="28" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F164" s="28" t="s">
         <v>6</v>
@@ -7854,13 +7891,13 @@
         <v>3</v>
       </c>
       <c r="H164" s="30" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I164" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="28" t="s">
         <v>57</v>
       </c>
@@ -7874,7 +7911,7 @@
         <v>46323</v>
       </c>
       <c r="E165" s="28" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F165" s="28" t="s">
         <v>6</v>
@@ -7883,13 +7920,13 @@
         <v>2</v>
       </c>
       <c r="H165" s="30" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I165" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="28" t="s">
         <v>57</v>
       </c>
@@ -7903,7 +7940,7 @@
         <v>46323</v>
       </c>
       <c r="E166" s="28" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F166" s="28" t="s">
         <v>6</v>
@@ -7912,13 +7949,13 @@
         <v>1</v>
       </c>
       <c r="H166" s="30" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I166" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="28" t="s">
         <v>57</v>
       </c>
@@ -7932,7 +7969,7 @@
         <v>46323</v>
       </c>
       <c r="E167" s="28" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F167" s="28" t="s">
         <v>6</v>
@@ -7941,13 +7978,13 @@
         <v>2</v>
       </c>
       <c r="H167" s="30" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I167" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="28" t="s">
         <v>57</v>
       </c>
@@ -7961,7 +7998,7 @@
         <v>46323</v>
       </c>
       <c r="E168" s="28" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F168" s="28" t="s">
         <v>6</v>
@@ -7970,13 +8007,13 @@
         <v>6</v>
       </c>
       <c r="H168" s="30" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I168" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="28" t="s">
         <v>57</v>
       </c>
@@ -7990,7 +8027,7 @@
         <v>46323</v>
       </c>
       <c r="E169" s="28" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F169" s="28" t="s">
         <v>6</v>
@@ -7999,13 +8036,13 @@
         <v>1</v>
       </c>
       <c r="H169" s="30" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I169" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="28" t="s">
         <v>57</v>
       </c>
@@ -8019,7 +8056,7 @@
         <v>46323</v>
       </c>
       <c r="E170" s="28" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F170" s="28" t="s">
         <v>6</v>
@@ -8028,13 +8065,13 @@
         <v>1</v>
       </c>
       <c r="H170" s="30" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I170" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="28" t="s">
         <v>57</v>
       </c>
@@ -8048,7 +8085,7 @@
         <v>46323</v>
       </c>
       <c r="E171" s="28" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F171" s="28" t="s">
         <v>6</v>
@@ -8057,13 +8094,13 @@
         <v>1</v>
       </c>
       <c r="H171" s="30" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I171" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="28" t="s">
         <v>57</v>
       </c>
@@ -8077,7 +8114,7 @@
         <v>46323</v>
       </c>
       <c r="E172" s="28" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F172" s="28" t="s">
         <v>6</v>
@@ -8086,13 +8123,13 @@
         <v>1</v>
       </c>
       <c r="H172" s="30" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I172" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="28" t="s">
         <v>5</v>
       </c>
@@ -8106,7 +8143,7 @@
         <v>46318</v>
       </c>
       <c r="E173" s="28" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F173" s="28" t="s">
         <v>6</v>
@@ -8115,13 +8152,13 @@
         <v>7</v>
       </c>
       <c r="H173" s="30" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I173" s="32" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="28" t="s">
         <v>57</v>
       </c>
@@ -8135,7 +8172,7 @@
         <v>46329</v>
       </c>
       <c r="E174" s="28" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F174" s="28" t="s">
         <v>52</v>
@@ -8144,13 +8181,13 @@
         <v>51</v>
       </c>
       <c r="H174" s="30" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I174" s="32" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="28" t="s">
         <v>103</v>
       </c>
@@ -8164,7 +8201,7 @@
         <v>46328</v>
       </c>
       <c r="E175" s="28" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F175" s="28" t="s">
         <v>6</v>
@@ -8173,13 +8210,13 @@
         <v>79</v>
       </c>
       <c r="H175" s="30" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I175" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="28" t="s">
         <v>103</v>
       </c>
@@ -8193,7 +8230,7 @@
         <v>46328</v>
       </c>
       <c r="E176" s="28" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F176" s="28" t="s">
         <v>6</v>
@@ -8202,13 +8239,13 @@
         <v>16</v>
       </c>
       <c r="H176" s="30" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I176" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="28" t="s">
         <v>56</v>
       </c>
@@ -8237,7 +8274,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="28" t="s">
         <v>323</v>
       </c>
@@ -8251,7 +8288,7 @@
         <v>46332</v>
       </c>
       <c r="E178" s="28" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F178" s="28" t="s">
         <v>52</v>
@@ -8260,13 +8297,13 @@
         <v>189</v>
       </c>
       <c r="H178" s="30" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I178" s="32" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="28" t="s">
         <v>326</v>
       </c>
@@ -8280,7 +8317,7 @@
         <v>46324</v>
       </c>
       <c r="E179" s="28" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F179" s="28" t="s">
         <v>6</v>
@@ -8289,13 +8326,13 @@
         <v>23</v>
       </c>
       <c r="H179" s="30" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I179" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="28" t="s">
         <v>326</v>
       </c>
@@ -8309,7 +8346,7 @@
         <v>46324</v>
       </c>
       <c r="E180" s="28" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F180" s="28" t="s">
         <v>6</v>
@@ -8318,13 +8355,13 @@
         <v>16</v>
       </c>
       <c r="H180" s="30" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I180" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="28" t="s">
         <v>326</v>
       </c>
@@ -8338,7 +8375,7 @@
         <v>46324</v>
       </c>
       <c r="E181" s="28" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F181" s="28" t="s">
         <v>6</v>
@@ -8347,13 +8384,13 @@
         <v>16</v>
       </c>
       <c r="H181" s="30" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I181" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="28" t="s">
         <v>326</v>
       </c>
@@ -8367,7 +8404,7 @@
         <v>46324</v>
       </c>
       <c r="E182" s="28" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F182" s="28" t="s">
         <v>6</v>
@@ -8376,13 +8413,13 @@
         <v>13</v>
       </c>
       <c r="H182" s="30" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I182" s="32" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="28" t="s">
         <v>180</v>
       </c>
@@ -8396,7 +8433,7 @@
         <v>46295</v>
       </c>
       <c r="E183" s="28" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F183" s="28" t="s">
         <v>6</v>
@@ -8405,13 +8442,13 @@
         <v>28</v>
       </c>
       <c r="H183" s="30" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I183" s="32" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="28" t="s">
         <v>103</v>
       </c>
@@ -8425,7 +8462,7 @@
         <v>46315</v>
       </c>
       <c r="E184" s="28" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F184" s="28" t="s">
         <v>6</v>
@@ -8434,13 +8471,13 @@
         <v>70</v>
       </c>
       <c r="H184" s="30" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I184" s="32" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="28" t="s">
         <v>103</v>
       </c>
@@ -8454,7 +8491,7 @@
         <v>46372</v>
       </c>
       <c r="E185" s="28" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F185" s="28" t="s">
         <v>6</v>
@@ -8463,13 +8500,13 @@
         <v>128</v>
       </c>
       <c r="H185" s="30" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I185" s="32" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="28" t="s">
         <v>79</v>
       </c>
@@ -8483,7 +8520,7 @@
         <v>46315</v>
       </c>
       <c r="E186" s="28" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F186" s="28" t="s">
         <v>6</v>
@@ -8492,13 +8529,13 @@
         <v>78</v>
       </c>
       <c r="H186" s="30" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I186" s="32" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="28" t="s">
         <v>5</v>
       </c>
@@ -8512,7 +8549,7 @@
         <v>46280</v>
       </c>
       <c r="E187" s="28" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F187" s="28" t="s">
         <v>6</v>
@@ -8521,10 +8558,213 @@
         <v>738</v>
       </c>
       <c r="H187" s="30" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I187" s="32" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="B188" s="29">
+        <v>46262</v>
+      </c>
+      <c r="C188" s="29">
+        <v>46266</v>
+      </c>
+      <c r="D188" s="29">
+        <v>46325</v>
+      </c>
+      <c r="E188" s="28" t="s">
+        <v>426</v>
+      </c>
+      <c r="F188" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G188" s="30">
+        <v>108</v>
+      </c>
+      <c r="H188" s="30" t="s">
+        <v>427</v>
+      </c>
+      <c r="I188" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B189" s="29">
+        <v>46265</v>
+      </c>
+      <c r="C189" s="29">
+        <v>46266</v>
+      </c>
+      <c r="D189" s="29">
+        <v>46324</v>
+      </c>
+      <c r="E189" s="28" t="s">
+        <v>428</v>
+      </c>
+      <c r="F189" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G189" s="30">
+        <v>58</v>
+      </c>
+      <c r="H189" s="30" t="s">
+        <v>429</v>
+      </c>
+      <c r="I189" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B190" s="29">
+        <v>46265</v>
+      </c>
+      <c r="C190" s="29">
+        <v>46266</v>
+      </c>
+      <c r="D190" s="29">
+        <v>46325</v>
+      </c>
+      <c r="E190" s="28" t="s">
+        <v>423</v>
+      </c>
+      <c r="F190" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G190" s="30">
+        <v>251</v>
+      </c>
+      <c r="H190" s="30" t="s">
+        <v>424</v>
+      </c>
+      <c r="I190" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B191" s="29">
+        <v>46266</v>
+      </c>
+      <c r="C191" s="29">
+        <v>46266</v>
+      </c>
+      <c r="D191" s="29">
+        <v>46328</v>
+      </c>
+      <c r="E191" s="28" t="s">
+        <v>421</v>
+      </c>
+      <c r="F191" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G191" s="30">
+        <v>153</v>
+      </c>
+      <c r="H191" s="30" t="s">
+        <v>422</v>
+      </c>
+      <c r="I191" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B192" s="29">
+        <v>46266</v>
+      </c>
+      <c r="C192" s="29">
+        <v>46266</v>
+      </c>
+      <c r="D192" s="29">
+        <v>46328</v>
+      </c>
+      <c r="E192" s="28" t="s">
+        <v>421</v>
+      </c>
+      <c r="F192" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G192" s="30">
+        <v>79</v>
+      </c>
+      <c r="H192" s="30" t="s">
+        <v>430</v>
+      </c>
+      <c r="I192" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B193" s="29">
+        <v>46266</v>
+      </c>
+      <c r="C193" s="29">
+        <v>46266</v>
+      </c>
+      <c r="D193" s="29">
+        <v>46328</v>
+      </c>
+      <c r="E193" s="28" t="s">
+        <v>421</v>
+      </c>
+      <c r="F193" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G193" s="30">
+        <v>52</v>
+      </c>
+      <c r="H193" s="30" t="s">
+        <v>425</v>
+      </c>
+      <c r="I193" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="B194" s="29">
+        <v>46267</v>
+      </c>
+      <c r="C194" s="29">
+        <v>46267</v>
+      </c>
+      <c r="D194" s="29">
+        <v>46325</v>
+      </c>
+      <c r="E194" s="28" t="s">
+        <v>431</v>
+      </c>
+      <c r="F194" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G194" s="30">
+        <v>178</v>
+      </c>
+      <c r="H194" s="30" t="s">
+        <v>432</v>
+      </c>
+      <c r="I194" s="32" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -8541,7 +8781,7 @@
           <x14:formula1>
             <xm:f>'Industry List'!$A$1:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>I3:I187</xm:sqref>
+          <xm:sqref>I3:I194</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8552,18 +8792,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC03875-3DF4-4258-8762-7FFE2A7D620D}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.453125" style="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="95" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="97.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>16</v>
       </c>
@@ -8571,7 +8811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>17</v>
       </c>
@@ -8580,7 +8820,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>9</v>
       </c>
@@ -8589,7 +8829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>10</v>
       </c>
@@ -8598,7 +8838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>11</v>
       </c>
@@ -8607,7 +8847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>12</v>
       </c>
@@ -8616,7 +8856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>13</v>
       </c>
@@ -8625,7 +8865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>14</v>
       </c>
@@ -8648,25 +8888,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE76718-798E-45ED-8CA1-01AA760CE5F1}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.1796875" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="98.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="99.75" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
-        <v>368</v>
+        <v>420</v>
       </c>
       <c r="E1"/>
     </row>
-    <row r="2" spans="1:8" ht="24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
@@ -8692,7 +8932,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -8729,117 +8969,117 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E81B0C9-EE0D-4672-99B4-ACA7D2D31E92}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="67.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="67.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -9077,7 +9317,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57352F60-0FA2-4515-85B2-A5D11A83DA02}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76B6A9E8-AD51-41FA-8B02-23E48CE4D608}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -9096,7 +9336,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53F2EFFE-C1BF-492E-A55D-4D62B857E2F2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA7AD1B3-404A-4EEA-9271-4F03D692E459}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -9104,18 +9344,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{737EBD67-6909-417A-9A96-7CE6BE680C99}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39B02763-705B-493C-839B-26A069D90AFA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="82b749e3-8208-459a-bfc0-9b428d09cbab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="9ac7e9dd-8d2d-4750-b54a-f534515ac3a2"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
